--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="151">
   <si>
     <t>GST Sales</t>
   </si>
@@ -507,6 +507,9 @@
   </si>
   <si>
     <t>65863</t>
+  </si>
+  <si>
+    <t>65848</t>
   </si>
 </sst>
 </file>
@@ -1181,43 +1184,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -1569,8 +1572,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>95</v>
+      <c r="AG5" t="s" s="36">
+        <v>150</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -1769,43 +1772,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -2343,44 +2346,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -2806,44 +2809,44 @@
   <dimension ref="A1:AM13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="18.85546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -3434,44 +3437,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -3897,44 +3900,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4360,43 +4363,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -4810,43 +4813,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -5260,43 +5263,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -5710,43 +5713,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -6160,43 +6163,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -6607,44 +6610,44 @@
   <dimension ref="A1:AM7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -7207,43 +7210,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -7666,42 +7669,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.42578125" style="29" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="15.42578125"/>
+    <col min="38" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
@@ -8113,43 +8116,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -8658,43 +8661,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -9209,43 +9212,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -9760,43 +9763,43 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -10180,43 +10183,43 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -10600,43 +10603,43 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="11.7109375"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -11020,44 +11023,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -11483,44 +11486,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -11946,43 +11949,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -12552,43 +12555,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13140,43 +13143,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13728,43 +13731,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -14316,43 +14319,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -14904,43 +14907,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -15492,43 +15495,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="151">
   <si>
     <t>GST Sales</t>
   </si>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="11" activeTab="13"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="28" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,12 @@
     <sheet name="CRNoteExportService" sheetId="28" r:id="rId28"/>
     <sheet name="CRNoteGateEntryExport" sheetId="31" r:id="rId29"/>
     <sheet name="CRNoteGateEntry" sheetId="30" r:id="rId30"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId31"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId32"/>
+    <sheet name="OP_S+I+P" sheetId="35" r:id="rId31"/>
+    <sheet name="OP_I+P" sheetId="36" r:id="rId32"/>
+    <sheet name="OP_S+P" sheetId="37" r:id="rId33"/>
+    <sheet name="OP_P" sheetId="38" r:id="rId34"/>
+    <sheet name="DirectSCO" sheetId="39" r:id="rId35"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId36"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -58,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="249">
   <si>
     <t>GST Sales</t>
   </si>
@@ -216,24 +220,12 @@
     <t>Domestic_RC_Item_ID_Disimilar</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>RC_Export_001</t>
   </si>
   <si>
     <t>Export_RC_Item_ID_Disimilar</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>9885</t>
-  </si>
-  <si>
     <t>299</t>
   </si>
   <si>
@@ -246,9 +238,6 @@
     <t>60</t>
   </si>
   <si>
-    <t>9870</t>
-  </si>
-  <si>
     <t>35</t>
   </si>
   <si>
@@ -309,9 +298,6 @@
     <t>200</t>
   </si>
   <si>
-    <t>9895</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -342,355 +328,487 @@
     <t>Sales Regular</t>
   </si>
   <si>
-    <t>9595</t>
-  </si>
-  <si>
-    <t>9933.992</t>
-  </si>
-  <si>
-    <t>9725</t>
-  </si>
-  <si>
-    <t>9707</t>
-  </si>
-  <si>
-    <t>9860</t>
-  </si>
-  <si>
-    <t>9785</t>
-  </si>
-  <si>
-    <t>9693</t>
-  </si>
-  <si>
-    <t>9847.5</t>
-  </si>
-  <si>
-    <t>9795</t>
-  </si>
-  <si>
-    <t>9900</t>
-  </si>
-  <si>
-    <t>9706</t>
+    <t>78119</t>
+  </si>
+  <si>
+    <t>9620</t>
+  </si>
+  <si>
+    <t>78104</t>
+  </si>
+  <si>
+    <t>PROD 100</t>
+  </si>
+  <si>
+    <t>UD_Disimilar_Domestic_002-so100-SO100/00391/24-25-1</t>
+  </si>
+  <si>
+    <t>TVSFG004-so100-SO100/00670/24-25-1</t>
+  </si>
+  <si>
+    <t>SO/Reference Domestic</t>
+  </si>
+  <si>
+    <t>SO100/00895/25-26</t>
+  </si>
+  <si>
+    <t>SO/Reference Export</t>
+  </si>
+  <si>
+    <t>CPC Code</t>
+  </si>
+  <si>
+    <t>CPC-100000001</t>
+  </si>
+  <si>
+    <t>FG WH-49</t>
+  </si>
+  <si>
+    <t>After Rtrn Inv Qty</t>
+  </si>
+  <si>
+    <t>After Stk Qty</t>
+  </si>
+  <si>
+    <t>HK-FIFO-LOT-BATCH-10001(FG)</t>
+  </si>
+  <si>
+    <t>49526</t>
+  </si>
+  <si>
+    <t>Charges</t>
+  </si>
+  <si>
+    <t>Sno</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Basiss</t>
+  </si>
+  <si>
+    <t>Pct</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>TVS-CH-00002</t>
+  </si>
+  <si>
+    <t>FRIEGHT CHARGES</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>TVS-CH-00003</t>
+  </si>
+  <si>
+    <t>PACKING CHARGES</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>FG_ShipSet_01</t>
+  </si>
+  <si>
+    <t>FG3100</t>
+  </si>
+  <si>
+    <t>FG3101</t>
+  </si>
+  <si>
+    <t>FG3102</t>
+  </si>
+  <si>
+    <t>FG3103</t>
+  </si>
+  <si>
+    <t>FG3104</t>
+  </si>
+  <si>
+    <t>FG3105</t>
+  </si>
+  <si>
+    <t>FG3106</t>
+  </si>
+  <si>
+    <t>FG3107</t>
+  </si>
+  <si>
+    <t>FG3108</t>
+  </si>
+  <si>
+    <t>Scrap W/H</t>
+  </si>
+  <si>
+    <t>R100</t>
+  </si>
+  <si>
+    <t>Scrap Item</t>
+  </si>
+  <si>
+    <t>Scarp Before Stk Qty</t>
+  </si>
+  <si>
+    <t>Scarp After Stk Qty</t>
+  </si>
+  <si>
+    <t>Scarp After MRV Stk Qty</t>
+  </si>
+  <si>
+    <t>99928</t>
+  </si>
+  <si>
+    <t>62718</t>
+  </si>
+  <si>
+    <t>99936</t>
+  </si>
+  <si>
+    <t>99932</t>
+  </si>
+  <si>
+    <t>99924</t>
+  </si>
+  <si>
+    <t>99920</t>
+  </si>
+  <si>
+    <t>99916</t>
+  </si>
+  <si>
+    <t>99912</t>
+  </si>
+  <si>
+    <t>99908</t>
+  </si>
+  <si>
+    <t>99904</t>
+  </si>
+  <si>
+    <t>105596</t>
+  </si>
+  <si>
+    <t>49151</t>
+  </si>
+  <si>
+    <t>64383</t>
+  </si>
+  <si>
+    <t>100001867</t>
+  </si>
+  <si>
+    <t>Scenario  : Open SCO Price Level Type - Supplier + Item + Process</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Batch Qty</t>
+  </si>
+  <si>
+    <t>Batch Cost</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>PROCESS-20</t>
+  </si>
+  <si>
+    <t>METAL FORMING PROCES</t>
+  </si>
+  <si>
+    <t>PACKINGS</t>
+  </si>
+  <si>
+    <t>POST CURING</t>
+  </si>
+  <si>
+    <t>Scenario  : Open SCO Price Level Type - Item + Process</t>
+  </si>
+  <si>
+    <t>63938</t>
+  </si>
+  <si>
+    <t>19275</t>
+  </si>
+  <si>
+    <t>63923</t>
+  </si>
+  <si>
+    <t>19270</t>
+  </si>
+  <si>
+    <t>9255</t>
+  </si>
+  <si>
+    <t>19808.992</t>
+  </si>
+  <si>
+    <t>109415</t>
+  </si>
+  <si>
+    <t>109755</t>
   </si>
   <si>
     <t>9765</t>
   </si>
   <si>
-    <t>78174</t>
-  </si>
-  <si>
-    <t>78144</t>
-  </si>
-  <si>
-    <t>78129</t>
-  </si>
-  <si>
-    <t>491512</t>
-  </si>
-  <si>
-    <t>78119</t>
-  </si>
-  <si>
-    <t>9620</t>
-  </si>
-  <si>
-    <t>78104</t>
-  </si>
-  <si>
-    <t>PROD 100</t>
-  </si>
-  <si>
-    <t>UD_Disimilar_Domestic_002-so100-SO100/00391/24-25-1</t>
-  </si>
-  <si>
-    <t>TVSFG004-so100-SO100/00670/24-25-1</t>
-  </si>
-  <si>
-    <t>SO/Reference Domestic</t>
-  </si>
-  <si>
-    <t>SO100/00895/25-26</t>
-  </si>
-  <si>
-    <t>SO/Reference Export</t>
-  </si>
-  <si>
-    <t>CPC Code</t>
-  </si>
-  <si>
-    <t>CPC-100000001</t>
-  </si>
-  <si>
-    <t>FG WH-49</t>
-  </si>
-  <si>
-    <t>After Rtrn Inv Qty</t>
-  </si>
-  <si>
-    <t>66208</t>
-  </si>
-  <si>
-    <t>After Stk Qty</t>
-  </si>
-  <si>
-    <t>66103</t>
-  </si>
-  <si>
-    <t>9515</t>
-  </si>
-  <si>
-    <t>HK-FIFO-LOT-BATCH-10001(FG)</t>
-  </si>
-  <si>
-    <t>797</t>
-  </si>
-  <si>
-    <t>49601</t>
-  </si>
-  <si>
-    <t>49526</t>
-  </si>
-  <si>
-    <t>Charges</t>
-  </si>
-  <si>
-    <t>Sno</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Basiss</t>
-  </si>
-  <si>
-    <t>Pct</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>TVS-CH-00002</t>
-  </si>
-  <si>
-    <t>FRIEGHT CHARGES</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>TVS-CH-00003</t>
-  </si>
-  <si>
-    <t>PACKING CHARGES</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>FG_ShipSet_01</t>
-  </si>
-  <si>
-    <t>19060</t>
-  </si>
-  <si>
-    <t>65788</t>
-  </si>
-  <si>
-    <t>9490</t>
-  </si>
-  <si>
-    <t>65398</t>
-  </si>
-  <si>
-    <t>65368</t>
-  </si>
-  <si>
-    <t>FG3100</t>
-  </si>
-  <si>
-    <t>FG3101</t>
-  </si>
-  <si>
-    <t>FG3102</t>
-  </si>
-  <si>
-    <t>FG3103</t>
-  </si>
-  <si>
-    <t>FG3104</t>
-  </si>
-  <si>
-    <t>FG3105</t>
-  </si>
-  <si>
-    <t>FG3106</t>
-  </si>
-  <si>
-    <t>FG3107</t>
-  </si>
-  <si>
-    <t>FG3108</t>
-  </si>
-  <si>
-    <t>FG3109</t>
-  </si>
-  <si>
-    <t>FG3110</t>
-  </si>
-  <si>
-    <t>FG3111</t>
-  </si>
-  <si>
-    <t>FG3112</t>
-  </si>
-  <si>
-    <t>FG3113</t>
-  </si>
-  <si>
-    <t>FG3114</t>
-  </si>
-  <si>
-    <t>FG3115</t>
-  </si>
-  <si>
-    <t>FG3116</t>
-  </si>
-  <si>
-    <t>FG3117</t>
-  </si>
-  <si>
-    <t>FG3118</t>
-  </si>
-  <si>
-    <t>FG3119</t>
-  </si>
-  <si>
-    <t>FG3120</t>
-  </si>
-  <si>
-    <t>FG3121</t>
-  </si>
-  <si>
-    <t>FG3122</t>
-  </si>
-  <si>
-    <t>FG3123</t>
-  </si>
-  <si>
-    <t>FG3124</t>
-  </si>
-  <si>
-    <t>FG3125</t>
-  </si>
-  <si>
-    <t>FG3126</t>
-  </si>
-  <si>
-    <t>FG3127</t>
-  </si>
-  <si>
-    <t>FG3128</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>65178</t>
-  </si>
-  <si>
-    <t>65163</t>
-  </si>
-  <si>
-    <t>99984</t>
-  </si>
-  <si>
-    <t>99983</t>
-  </si>
-  <si>
-    <t>99982</t>
-  </si>
-  <si>
-    <t>99981</t>
-  </si>
-  <si>
-    <t>99980</t>
-  </si>
-  <si>
-    <t>99979</t>
-  </si>
-  <si>
-    <t>99978</t>
-  </si>
-  <si>
-    <t>99977</t>
-  </si>
-  <si>
-    <t>99976</t>
-  </si>
-  <si>
-    <t>99975</t>
-  </si>
-  <si>
-    <t>99974</t>
-  </si>
-  <si>
-    <t>99973</t>
-  </si>
-  <si>
-    <t>99972</t>
-  </si>
-  <si>
-    <t>99971</t>
-  </si>
-  <si>
-    <t>99970</t>
-  </si>
-  <si>
-    <t>99969</t>
-  </si>
-  <si>
-    <t>99968</t>
-  </si>
-  <si>
-    <t>99967</t>
-  </si>
-  <si>
-    <t>99966</t>
-  </si>
-  <si>
-    <t>99965</t>
-  </si>
-  <si>
-    <t>99964</t>
-  </si>
-  <si>
-    <t>99963</t>
-  </si>
-  <si>
-    <t>99962</t>
-  </si>
-  <si>
-    <t>99961</t>
-  </si>
-  <si>
-    <t>99960</t>
-  </si>
-  <si>
-    <t>99959</t>
-  </si>
-  <si>
-    <t>99958</t>
-  </si>
-  <si>
-    <t>99957</t>
-  </si>
-  <si>
-    <t>99956</t>
+    <t>9307</t>
+  </si>
+  <si>
+    <t>9715</t>
+  </si>
+  <si>
+    <t>9415</t>
+  </si>
+  <si>
+    <t>9760</t>
+  </si>
+  <si>
+    <t>9293</t>
+  </si>
+  <si>
+    <t>9702.5</t>
+  </si>
+  <si>
+    <t>9425</t>
+  </si>
+  <si>
+    <t>109411</t>
+  </si>
+  <si>
+    <t>109750</t>
+  </si>
+  <si>
+    <t>109500</t>
+  </si>
+  <si>
+    <t>109785</t>
+  </si>
+  <si>
+    <t>63893</t>
+  </si>
+  <si>
+    <t>63878</t>
+  </si>
+  <si>
+    <t>63863</t>
+  </si>
+  <si>
+    <t>63848</t>
+  </si>
+  <si>
+    <t>488826</t>
+  </si>
+  <si>
+    <t>63838</t>
+  </si>
+  <si>
+    <t>18880</t>
+  </si>
+  <si>
+    <t>19265</t>
+  </si>
+  <si>
+    <t>Scenario  : Open SCO Price Level Type - Supplier + Process</t>
+  </si>
+  <si>
+    <t>Scenario  : Open SCO Price Level Type - Process</t>
+  </si>
+  <si>
+    <t>Scenario  : Direct SCO With BOM Standard Type</t>
+  </si>
+  <si>
+    <t>Vj-FIFO-LOT-BATCH-50001(FG)</t>
+  </si>
+  <si>
+    <t>SLICING</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>63823</t>
+  </si>
+  <si>
+    <t>19257.5</t>
+  </si>
+  <si>
+    <t>63808</t>
+  </si>
+  <si>
+    <t>19252.5</t>
+  </si>
+  <si>
+    <t>9240</t>
+  </si>
+  <si>
+    <t>19803.992</t>
+  </si>
+  <si>
+    <t>109400</t>
+  </si>
+  <si>
+    <t>63793</t>
+  </si>
+  <si>
+    <t>19247.5</t>
+  </si>
+  <si>
+    <t>9225</t>
+  </si>
+  <si>
+    <t>19798.992</t>
+  </si>
+  <si>
+    <t>109385</t>
+  </si>
+  <si>
+    <t>109745</t>
+  </si>
+  <si>
+    <t>9292</t>
+  </si>
+  <si>
+    <t>9710</t>
+  </si>
+  <si>
+    <t>9400</t>
+  </si>
+  <si>
+    <t>9755</t>
+  </si>
+  <si>
+    <t>9277</t>
+  </si>
+  <si>
+    <t>9705</t>
+  </si>
+  <si>
+    <t>9385</t>
+  </si>
+  <si>
+    <t>9750</t>
+  </si>
+  <si>
+    <t>9278</t>
+  </si>
+  <si>
+    <t>9697.5</t>
+  </si>
+  <si>
+    <t>9410</t>
+  </si>
+  <si>
+    <t>9263</t>
+  </si>
+  <si>
+    <t>9692.5</t>
+  </si>
+  <si>
+    <t>9395</t>
+  </si>
+  <si>
+    <t>109396</t>
+  </si>
+  <si>
+    <t>109485</t>
+  </si>
+  <si>
+    <t>109780</t>
+  </si>
+  <si>
+    <t>109381</t>
+  </si>
+  <si>
+    <t>109740</t>
+  </si>
+  <si>
+    <t>109470</t>
+  </si>
+  <si>
+    <t>109775</t>
+  </si>
+  <si>
+    <t>63778</t>
+  </si>
+  <si>
+    <t>63763</t>
+  </si>
+  <si>
+    <t>63748</t>
+  </si>
+  <si>
+    <t>63733</t>
+  </si>
+  <si>
+    <t>63718</t>
+  </si>
+  <si>
+    <t>488816</t>
+  </si>
+  <si>
+    <t>63708</t>
+  </si>
+  <si>
+    <t>18865</t>
+  </si>
+  <si>
+    <t>19242.5</t>
+  </si>
+  <si>
+    <t>9262</t>
+  </si>
+  <si>
+    <t>9700</t>
+  </si>
+  <si>
+    <t>63693</t>
+  </si>
+  <si>
+    <t>63678</t>
+  </si>
+  <si>
+    <t>63663</t>
+  </si>
+  <si>
+    <t>49136</t>
+  </si>
+  <si>
+    <t>49121</t>
+  </si>
+  <si>
+    <t>49106</t>
+  </si>
+  <si>
+    <t>49091</t>
+  </si>
+  <si>
+    <t>63648</t>
+  </si>
+  <si>
+    <t>63633</t>
+  </si>
+  <si>
+    <t>63618</t>
+  </si>
+  <si>
+    <t>63603</t>
+  </si>
+  <si>
+    <t>63588</t>
   </si>
 </sst>
 </file>
@@ -813,7 +931,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -836,11 +954,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1073,6 +1204,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1413,7 +1595,7 @@
     <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
     <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
     <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="29" width="26.85546875"/>
     <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
     <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
     <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
@@ -1421,36 +1603,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1497,10 +1679,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -1769,12 +1951,12 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>146</v>
+      <c r="AG5" t="s" s="36">
+        <v>199</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
-        <v>65788</v>
+        <v>-15</v>
       </c>
       <c r="AI5" s="10" t="s">
         <v>38</v>
@@ -1898,8 +2080,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>147</v>
+      <c r="AG6" t="s" s="36">
+        <v>200</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2009,36 +2191,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -2085,10 +2267,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2250,13 +2432,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2267,8 +2449,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>82</v>
+      <c r="H5" t="s" s="29">
+        <v>77</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -2353,8 +2535,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>105</v>
+      <c r="AG5" t="s" s="36">
+        <v>224</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2374,13 +2556,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -2391,8 +2573,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>84</v>
+      <c r="H6" t="s" s="29">
+        <v>78</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -2477,8 +2659,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>57</v>
+      <c r="AG6" t="s" s="36">
+        <v>225</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2584,36 +2766,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="80"/>
       <c r="AD1" s="80"/>
       <c r="AE1" s="80"/>
@@ -2660,10 +2842,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="79"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -2818,10 +3000,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -2830,13 +3012,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2933,8 +3115,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>128</v>
+      <c r="AG5" t="s" s="36">
+        <v>143</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3047,36 +3229,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="86"/>
       <c r="AD1" s="86"/>
       <c r="AE1" s="86"/>
@@ -3123,10 +3305,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="85"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3281,10 +3463,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -3397,7 +3579,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3456,7 +3638,7 @@
     </row>
     <row r="9" spans="1:39">
       <c r="C9" s="89" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
@@ -3473,7 +3655,7 @@
     </row>
     <row r="10" spans="1:39">
       <c r="C10" s="90" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>6</v>
@@ -3482,19 +3664,19 @@
         <v>7</v>
       </c>
       <c r="F10" s="90" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="G10" s="90" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H10" s="90" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="I10" s="90" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="J10" s="90" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="K10" s="90" t="s">
         <v>26</v>
@@ -3517,16 +3699,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="H11" s="10">
         <v>20</v>
@@ -3558,16 +3740,16 @@
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
@@ -3599,7 +3781,7 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="I13" s="10">
         <v>21477.41</v>
@@ -3675,36 +3857,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="88"/>
       <c r="AD1" s="88"/>
       <c r="AE1" s="88"/>
@@ -3751,10 +3933,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="87"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3909,10 +4091,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -3921,13 +4103,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4024,8 +4206,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>145</v>
+      <c r="AG5" t="s" s="36">
+        <v>233</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4138,36 +4320,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="93"/>
       <c r="AD1" s="93"/>
       <c r="AE1" s="93"/>
@@ -4214,10 +4396,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="92"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4372,10 +4554,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -4487,8 +4669,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>181</v>
+      <c r="AG5" s="36" t="s">
+        <v>134</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4515,13 +4697,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="97" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="97" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -4601,25 +4783,25 @@
         <v>144</v>
       </c>
       <c r="AB6" s="34">
-        <f t="shared" ref="AB6:AB34" si="3">U6+AA6</f>
+        <f t="shared" ref="AB6:AB14" si="3">U6+AA6</f>
         <v>944</v>
       </c>
       <c r="AC6" s="9">
         <v>120</v>
       </c>
       <c r="AD6" s="9">
-        <f t="shared" ref="AD6:AD34" si="4">U6*$N$3</f>
+        <f t="shared" ref="AD6:AD14" si="4">U6*$N$3</f>
         <v>800</v>
       </c>
       <c r="AE6" s="8">
         <v>1</v>
       </c>
       <c r="AF6" s="9">
-        <f t="shared" ref="AF6:AF34" si="5">G6/AE6</f>
+        <f t="shared" ref="AF6:AF14" si="5">G6/AE6</f>
         <v>16</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>182</v>
+      <c r="AG6" s="36" t="s">
+        <v>135</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
@@ -4645,13 +4827,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="97" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
       </c>
       <c r="D7" s="97" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -4666,46 +4848,46 @@
         <v>50</v>
       </c>
       <c r="I7" s="34">
-        <f t="shared" ref="I7:I34" si="6">G7*H7</f>
+        <f t="shared" ref="I7:I14" si="6">G7*H7</f>
         <v>850</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
       <c r="L7" s="34"/>
       <c r="M7" s="9">
-        <f t="shared" ref="M7:M34" si="7">I7</f>
+        <f t="shared" ref="M7:M14" si="7">I7</f>
         <v>850</v>
       </c>
       <c r="N7" s="9">
-        <f t="shared" ref="N7:N34" si="8">ROUND((M7*J7)/100,2)</f>
+        <f t="shared" ref="N7:N14" si="8">ROUND((M7*J7)/100,2)</f>
         <v>0</v>
       </c>
       <c r="O7" s="9">
-        <f t="shared" ref="O7:O34" si="9">I7-N7</f>
+        <f t="shared" ref="O7:O14" si="9">I7-N7</f>
         <v>850</v>
       </c>
       <c r="P7" s="9">
-        <f t="shared" ref="P7:P34" si="10">ROUND((O7*K7)/100,2)</f>
+        <f t="shared" ref="P7:P14" si="10">ROUND((O7*K7)/100,2)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="9">
-        <f t="shared" ref="Q7:Q34" si="11">ROUND(O7-P7,2)</f>
+        <f t="shared" ref="Q7:Q14" si="11">ROUND(O7-P7,2)</f>
         <v>850</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" ref="R7:R34" si="12">ROUND((Q7*L7)/100,2)</f>
+        <f t="shared" ref="R7:R14" si="12">ROUND((Q7*L7)/100,2)</f>
         <v>0</v>
       </c>
       <c r="S7" s="35">
-        <f t="shared" ref="S7:S34" si="13">N7+P7+R7</f>
+        <f t="shared" ref="S7:S14" si="13">N7+P7+R7</f>
         <v>0</v>
       </c>
       <c r="T7" s="35">
-        <f t="shared" ref="T7:T34" si="14">S7/G7</f>
+        <f t="shared" ref="T7:T14" si="14">S7/G7</f>
         <v>0</v>
       </c>
       <c r="U7" s="9">
-        <f t="shared" ref="U7:U34" si="15">(I7-S7)</f>
+        <f t="shared" ref="U7:U14" si="15">(I7-S7)</f>
         <v>850</v>
       </c>
       <c r="V7" s="33">
@@ -4715,19 +4897,19 @@
         <v>0.18</v>
       </c>
       <c r="X7" s="34">
-        <f t="shared" ref="X7:X34" si="16">IF($D$3=1,ROUND(((U7*W7)/2),2),0)</f>
+        <f t="shared" ref="X7:X14" si="16">IF($D$3=1,ROUND(((U7*W7)/2),2),0)</f>
         <v>76.5</v>
       </c>
       <c r="Y7" s="34">
-        <f t="shared" ref="Y7:Y34" si="17">IF($D$3=1,ROUND(((U7*W7)/2),2),0)</f>
+        <f t="shared" ref="Y7:Y14" si="17">IF($D$3=1,ROUND(((U7*W7)/2),2),0)</f>
         <v>76.5</v>
       </c>
       <c r="Z7" s="34">
-        <f t="shared" ref="Z7:Z34" si="18">IF($D$3=2,ROUND(((U7*W7)),2),0)</f>
+        <f t="shared" ref="Z7:Z14" si="18">IF($D$3=2,ROUND(((U7*W7)),2),0)</f>
         <v>0</v>
       </c>
       <c r="AA7" s="34">
-        <f t="shared" ref="AA7:AA34" si="19">X7+Y7+Z7</f>
+        <f t="shared" ref="AA7:AA14" si="19">X7+Y7+Z7</f>
         <v>153</v>
       </c>
       <c r="AB7" s="34">
@@ -4748,11 +4930,11 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="AG7" t="s" s="36">
-        <v>183</v>
+      <c r="AG7" s="36" t="s">
+        <v>136</v>
       </c>
       <c r="AH7" s="34">
-        <f t="shared" ref="AH7:AH34" si="20">AG7-AF7</f>
+        <f t="shared" ref="AH7:AH14" si="20">AG7-AF7</f>
         <v>99983</v>
       </c>
       <c r="AI7" s="10" t="s">
@@ -4762,11 +4944,11 @@
         <v>4010101001</v>
       </c>
       <c r="AK7" s="34">
-        <f t="shared" ref="AK7:AK34" si="21">AH7</f>
+        <f t="shared" ref="AK7:AK14" si="21">AH7</f>
         <v>99983</v>
       </c>
       <c r="AL7" s="34">
-        <f t="shared" ref="AL7:AL34" si="22">AK7+G7</f>
+        <f t="shared" ref="AL7:AL14" si="22">AK7+G7</f>
         <v>100000</v>
       </c>
     </row>
@@ -4775,13 +4957,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="97" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="97" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>32</v>
@@ -4878,8 +5060,8 @@
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="AG8" t="s" s="36">
-        <v>184</v>
+      <c r="AG8" s="36" t="s">
+        <v>133</v>
       </c>
       <c r="AH8" s="34">
         <f t="shared" si="20"/>
@@ -4905,13 +5087,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="97" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
       </c>
       <c r="D9" s="97" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>32</v>
@@ -5008,8 +5190,8 @@
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="AG9" t="s" s="36">
-        <v>185</v>
+      <c r="AG9" s="36" t="s">
+        <v>137</v>
       </c>
       <c r="AH9" s="34">
         <f t="shared" si="20"/>
@@ -5035,13 +5217,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="97" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>32</v>
@@ -5138,8 +5320,8 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="AG10" t="s" s="36">
-        <v>186</v>
+      <c r="AG10" s="36" t="s">
+        <v>138</v>
       </c>
       <c r="AH10" s="34">
         <f t="shared" si="20"/>
@@ -5165,13 +5347,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
       </c>
       <c r="D11" s="97" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>32</v>
@@ -5268,8 +5450,8 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="AG11" t="s" s="36">
-        <v>187</v>
+      <c r="AG11" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="AH11" s="34">
         <f t="shared" si="20"/>
@@ -5291,131 +5473,131 @@
       </c>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="10">
+      <c r="A12" s="99">
         <v>8</v>
       </c>
-      <c r="B12" s="97" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0</v>
-      </c>
-      <c r="D12" s="97" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="B12" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="99">
+        <v>0</v>
+      </c>
+      <c r="D12" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="101">
         <v>22</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="99">
         <v>50</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="102">
         <f t="shared" si="6"/>
         <v>1100</v>
       </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="9">
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103">
         <f t="shared" si="7"/>
         <v>1100</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="103">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="103">
         <f t="shared" si="9"/>
         <v>1100</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="103">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="103">
         <f t="shared" si="11"/>
         <v>1100</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S12" s="35">
+      <c r="S12" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T12" s="35">
+      <c r="T12" s="104">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U12" s="9">
+      <c r="U12" s="103">
         <f t="shared" si="15"/>
         <v>1100</v>
       </c>
-      <c r="V12" s="33">
+      <c r="V12" s="101">
         <v>88363222</v>
       </c>
-      <c r="W12" s="22">
+      <c r="W12" s="105">
         <v>0.18</v>
       </c>
-      <c r="X12" s="34">
+      <c r="X12" s="102">
         <f t="shared" si="16"/>
         <v>99</v>
       </c>
-      <c r="Y12" s="34">
+      <c r="Y12" s="102">
         <f t="shared" si="17"/>
         <v>99</v>
       </c>
-      <c r="Z12" s="34">
+      <c r="Z12" s="102">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="34">
+      <c r="AA12" s="102">
         <f t="shared" si="19"/>
         <v>198</v>
       </c>
-      <c r="AB12" s="34">
+      <c r="AB12" s="102">
         <f t="shared" si="3"/>
         <v>1298</v>
       </c>
-      <c r="AC12" s="9">
+      <c r="AC12" s="103">
         <v>120</v>
       </c>
-      <c r="AD12" s="9">
+      <c r="AD12" s="103">
         <f t="shared" si="4"/>
         <v>1100</v>
       </c>
-      <c r="AE12" s="8">
+      <c r="AE12" s="106">
         <v>1</v>
       </c>
-      <c r="AF12" s="9">
+      <c r="AF12" s="103">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="AG12" t="s" s="36">
-        <v>188</v>
-      </c>
-      <c r="AH12" s="34">
+      <c r="AG12" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH12" s="102">
         <f t="shared" si="20"/>
         <v>99978</v>
       </c>
-      <c r="AI12" s="10" t="s">
+      <c r="AI12" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="AJ12" s="10">
+      <c r="AJ12" s="99">
         <v>4010101001</v>
       </c>
-      <c r="AK12" s="34">
+      <c r="AK12" s="102">
         <f t="shared" si="21"/>
         <v>99978</v>
       </c>
-      <c r="AL12" s="34">
+      <c r="AL12" s="102">
         <f t="shared" si="22"/>
         <v>100000</v>
       </c>
@@ -5425,13 +5607,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>32</v>
@@ -5528,8 +5710,8 @@
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="AG13" t="s" s="36">
-        <v>189</v>
+      <c r="AG13" s="36" t="s">
+        <v>141</v>
       </c>
       <c r="AH13" s="34">
         <f t="shared" si="20"/>
@@ -5555,13 +5737,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="97" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>32</v>
@@ -5658,8 +5840,8 @@
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="AG14" t="s" s="36">
-        <v>190</v>
+      <c r="AG14" s="36" t="s">
+        <v>142</v>
       </c>
       <c r="AH14" s="34">
         <f t="shared" si="20"/>
@@ -5680,2607 +5862,667 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="15" spans="1:39">
-      <c r="A15" s="10">
-        <v>11</v>
-      </c>
-      <c r="B15" s="97" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="10">
-        <v>0</v>
-      </c>
-      <c r="D15" s="97" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="33">
-        <v>25</v>
-      </c>
-      <c r="H15" s="10">
-        <v>50</v>
-      </c>
-      <c r="I15" s="34">
-        <f t="shared" si="6"/>
-        <v>1250</v>
-      </c>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="9">
-        <f t="shared" si="7"/>
-        <v>1250</v>
-      </c>
-      <c r="N15" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
-        <f t="shared" si="9"/>
-        <v>1250</v>
-      </c>
-      <c r="P15" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
-        <f t="shared" si="11"/>
-        <v>1250</v>
-      </c>
-      <c r="R15" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="9">
-        <f t="shared" si="15"/>
-        <v>1250</v>
-      </c>
-      <c r="V15" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W15" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X15" s="34">
-        <f t="shared" si="16"/>
-        <v>112.5</v>
-      </c>
-      <c r="Y15" s="34">
-        <f t="shared" si="17"/>
-        <v>112.5</v>
-      </c>
-      <c r="Z15" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="34">
-        <f t="shared" si="19"/>
-        <v>225</v>
-      </c>
-      <c r="AB15" s="34">
-        <f t="shared" si="3"/>
-        <v>1475</v>
-      </c>
-      <c r="AC15" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD15" s="9">
-        <f t="shared" si="4"/>
-        <v>1250</v>
-      </c>
-      <c r="AE15" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="9">
-        <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="AG15" t="s" s="36">
-        <v>191</v>
-      </c>
-      <c r="AH15" s="34">
-        <f t="shared" si="20"/>
-        <v>99975</v>
-      </c>
-      <c r="AI15" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ15" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK15" s="34">
-        <f t="shared" si="21"/>
-        <v>99975</v>
-      </c>
-      <c r="AL15" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:39">
-      <c r="A16" s="10">
-        <v>12</v>
-      </c>
-      <c r="B16" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="10">
-        <v>0</v>
-      </c>
-      <c r="D16" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="33">
-        <v>26</v>
-      </c>
-      <c r="H16" s="10">
-        <v>50</v>
-      </c>
-      <c r="I16" s="34">
-        <f t="shared" si="6"/>
-        <v>1300</v>
-      </c>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="9">
-        <f t="shared" si="7"/>
-        <v>1300</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="9"/>
-        <v>1300</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="11"/>
-        <v>1300</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="9">
-        <f t="shared" si="15"/>
-        <v>1300</v>
-      </c>
-      <c r="V16" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W16" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X16" s="34">
-        <f t="shared" si="16"/>
-        <v>117</v>
-      </c>
-      <c r="Y16" s="34">
-        <f t="shared" si="17"/>
-        <v>117</v>
-      </c>
-      <c r="Z16" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="34">
-        <f>X16+Y16+Z16</f>
-        <v>234</v>
-      </c>
-      <c r="AB16" s="34">
-        <f t="shared" si="3"/>
-        <v>1534</v>
-      </c>
-      <c r="AC16" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD16" s="9">
-        <f t="shared" si="4"/>
-        <v>1300</v>
-      </c>
-      <c r="AE16" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="9">
-        <f t="shared" si="5"/>
-        <v>26</v>
-      </c>
-      <c r="AG16" t="s" s="36">
-        <v>192</v>
-      </c>
-      <c r="AH16" s="34">
-        <f t="shared" si="20"/>
-        <v>99974</v>
-      </c>
-      <c r="AI16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ16" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK16" s="34">
-        <f t="shared" si="21"/>
-        <v>99974</v>
-      </c>
-      <c r="AL16" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:38">
-      <c r="A17" s="10">
-        <v>13</v>
-      </c>
-      <c r="B17" s="97" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="10">
-        <v>0</v>
-      </c>
-      <c r="D17" s="97" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="33">
-        <v>27</v>
-      </c>
-      <c r="H17" s="10">
-        <v>50</v>
-      </c>
-      <c r="I17" s="34">
-        <f t="shared" si="6"/>
-        <v>1350</v>
-      </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="9">
-        <f t="shared" si="7"/>
-        <v>1350</v>
-      </c>
-      <c r="N17" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="9">
-        <f t="shared" si="9"/>
-        <v>1350</v>
-      </c>
-      <c r="P17" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="9">
-        <f t="shared" si="11"/>
-        <v>1350</v>
-      </c>
-      <c r="R17" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="9">
-        <f t="shared" si="15"/>
-        <v>1350</v>
-      </c>
-      <c r="V17" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W17" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X17" s="34">
-        <f t="shared" si="16"/>
-        <v>121.5</v>
-      </c>
-      <c r="Y17" s="34">
-        <f t="shared" si="17"/>
-        <v>121.5</v>
-      </c>
-      <c r="Z17" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="34">
-        <f t="shared" si="19"/>
-        <v>243</v>
-      </c>
-      <c r="AB17" s="34">
-        <f t="shared" si="3"/>
-        <v>1593</v>
-      </c>
-      <c r="AC17" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD17" s="9">
-        <f t="shared" si="4"/>
-        <v>1350</v>
-      </c>
-      <c r="AE17" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="9">
-        <f t="shared" si="5"/>
-        <v>27</v>
-      </c>
-      <c r="AG17" t="s" s="36">
-        <v>193</v>
-      </c>
-      <c r="AH17" s="34">
-        <f t="shared" si="20"/>
-        <v>99973</v>
-      </c>
-      <c r="AI17" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ17" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK17" s="34">
-        <f t="shared" si="21"/>
-        <v>99973</v>
-      </c>
-      <c r="AL17" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:38">
-      <c r="A18" s="10">
-        <v>14</v>
-      </c>
-      <c r="B18" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="10">
-        <v>0</v>
-      </c>
-      <c r="D18" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="33">
-        <v>28</v>
-      </c>
-      <c r="H18" s="10">
-        <v>50</v>
-      </c>
-      <c r="I18" s="34">
-        <f t="shared" si="6"/>
-        <v>1400</v>
-      </c>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="9">
-        <f t="shared" si="7"/>
-        <v>1400</v>
-      </c>
-      <c r="N18" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="9">
-        <f t="shared" si="9"/>
-        <v>1400</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="11"/>
-        <v>1400</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="9">
-        <f t="shared" si="15"/>
-        <v>1400</v>
-      </c>
-      <c r="V18" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W18" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X18" s="34">
-        <f t="shared" si="16"/>
-        <v>126</v>
-      </c>
-      <c r="Y18" s="34">
-        <f t="shared" si="17"/>
-        <v>126</v>
-      </c>
-      <c r="Z18" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="34">
-        <f t="shared" si="19"/>
-        <v>252</v>
-      </c>
-      <c r="AB18" s="34">
-        <f t="shared" si="3"/>
-        <v>1652</v>
-      </c>
-      <c r="AC18" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD18" s="9">
-        <f t="shared" si="4"/>
-        <v>1400</v>
-      </c>
-      <c r="AE18" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="9">
-        <f t="shared" si="5"/>
-        <v>28</v>
-      </c>
-      <c r="AG18" t="s" s="36">
-        <v>194</v>
-      </c>
-      <c r="AH18" s="34">
-        <f t="shared" si="20"/>
-        <v>99972</v>
-      </c>
-      <c r="AI18" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ18" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK18" s="34">
-        <f t="shared" si="21"/>
-        <v>99972</v>
-      </c>
-      <c r="AL18" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:38">
-      <c r="A19" s="10">
-        <v>15</v>
-      </c>
-      <c r="B19" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="10">
-        <v>0</v>
-      </c>
-      <c r="D19" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="33">
-        <v>29</v>
-      </c>
-      <c r="H19" s="10">
-        <v>50</v>
-      </c>
-      <c r="I19" s="34">
-        <f t="shared" si="6"/>
-        <v>1450</v>
-      </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="9">
-        <f t="shared" si="7"/>
-        <v>1450</v>
-      </c>
-      <c r="N19" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="9">
-        <f t="shared" si="9"/>
-        <v>1450</v>
-      </c>
-      <c r="P19" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="11"/>
-        <v>1450</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="9">
-        <f t="shared" si="15"/>
-        <v>1450</v>
-      </c>
-      <c r="V19" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W19" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X19" s="34">
-        <f t="shared" si="16"/>
-        <v>130.5</v>
-      </c>
-      <c r="Y19" s="34">
-        <f t="shared" si="17"/>
-        <v>130.5</v>
-      </c>
-      <c r="Z19" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="34">
-        <f t="shared" si="19"/>
-        <v>261</v>
-      </c>
-      <c r="AB19" s="34">
-        <f t="shared" si="3"/>
-        <v>1711</v>
-      </c>
-      <c r="AC19" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD19" s="9">
-        <f t="shared" si="4"/>
-        <v>1450</v>
-      </c>
-      <c r="AE19" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="9">
-        <f t="shared" si="5"/>
-        <v>29</v>
-      </c>
-      <c r="AG19" t="s" s="36">
-        <v>195</v>
-      </c>
-      <c r="AH19" s="34">
-        <f t="shared" si="20"/>
-        <v>99971</v>
-      </c>
-      <c r="AI19" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ19" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK19" s="34">
-        <f t="shared" si="21"/>
-        <v>99971</v>
-      </c>
-      <c r="AL19" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:38">
-      <c r="A20" s="10">
-        <v>16</v>
-      </c>
-      <c r="B20" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="10">
-        <v>0</v>
-      </c>
-      <c r="D20" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="33">
-        <v>30</v>
-      </c>
-      <c r="H20" s="10">
-        <v>50</v>
-      </c>
-      <c r="I20" s="34">
-        <f t="shared" si="6"/>
-        <v>1500</v>
-      </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="9">
-        <f t="shared" si="7"/>
-        <v>1500</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" si="9"/>
-        <v>1500</v>
-      </c>
-      <c r="P20" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" si="11"/>
-        <v>1500</v>
-      </c>
-      <c r="R20" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="9">
-        <f t="shared" si="15"/>
-        <v>1500</v>
-      </c>
-      <c r="V20" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W20" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X20" s="34">
-        <f t="shared" si="16"/>
-        <v>135</v>
-      </c>
-      <c r="Y20" s="34">
-        <f t="shared" si="17"/>
-        <v>135</v>
-      </c>
-      <c r="Z20" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="34">
-        <f t="shared" si="19"/>
-        <v>270</v>
-      </c>
-      <c r="AB20" s="34">
-        <f t="shared" si="3"/>
-        <v>1770</v>
-      </c>
-      <c r="AC20" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="4"/>
-        <v>1500</v>
-      </c>
-      <c r="AE20" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="5"/>
-        <v>30</v>
-      </c>
-      <c r="AG20" t="s" s="36">
-        <v>196</v>
-      </c>
-      <c r="AH20" s="34">
-        <f t="shared" si="20"/>
-        <v>99970</v>
-      </c>
-      <c r="AI20" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ20" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK20" s="34">
-        <f t="shared" si="21"/>
-        <v>99970</v>
-      </c>
-      <c r="AL20" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:38">
-      <c r="A21" s="10">
-        <v>17</v>
-      </c>
-      <c r="B21" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0</v>
-      </c>
-      <c r="D21" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="33">
-        <v>31</v>
-      </c>
-      <c r="H21" s="10">
-        <v>50</v>
-      </c>
-      <c r="I21" s="34">
-        <f t="shared" si="6"/>
-        <v>1550</v>
-      </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="9">
-        <f t="shared" si="7"/>
-        <v>1550</v>
-      </c>
-      <c r="N21" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" si="9"/>
-        <v>1550</v>
-      </c>
-      <c r="P21" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" si="11"/>
-        <v>1550</v>
-      </c>
-      <c r="R21" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="9">
-        <f t="shared" si="15"/>
-        <v>1550</v>
-      </c>
-      <c r="V21" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W21" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X21" s="34">
-        <f t="shared" si="16"/>
-        <v>139.5</v>
-      </c>
-      <c r="Y21" s="34">
-        <f t="shared" si="17"/>
-        <v>139.5</v>
-      </c>
-      <c r="Z21" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="34">
-        <f t="shared" si="19"/>
-        <v>279</v>
-      </c>
-      <c r="AB21" s="34">
-        <f t="shared" si="3"/>
-        <v>1829</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="4"/>
-        <v>1550</v>
-      </c>
-      <c r="AE21" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="5"/>
-        <v>31</v>
-      </c>
-      <c r="AG21" t="s" s="36">
-        <v>197</v>
-      </c>
-      <c r="AH21" s="34">
-        <f t="shared" si="20"/>
-        <v>99969</v>
-      </c>
-      <c r="AI21" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ21" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK21" s="34">
-        <f t="shared" si="21"/>
-        <v>99969</v>
-      </c>
-      <c r="AL21" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:38">
-      <c r="A22" s="10">
-        <v>18</v>
-      </c>
-      <c r="B22" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22" s="10">
-        <v>0</v>
-      </c>
-      <c r="D22" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="33">
-        <v>32</v>
-      </c>
-      <c r="H22" s="10">
-        <v>50</v>
-      </c>
-      <c r="I22" s="34">
-        <f t="shared" si="6"/>
-        <v>1600</v>
-      </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="9">
-        <f t="shared" si="7"/>
-        <v>1600</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" si="9"/>
-        <v>1600</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="11"/>
-        <v>1600</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="15"/>
-        <v>1600</v>
-      </c>
-      <c r="V22" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W22" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X22" s="34">
-        <f t="shared" si="16"/>
-        <v>144</v>
-      </c>
-      <c r="Y22" s="34">
-        <f t="shared" si="17"/>
-        <v>144</v>
-      </c>
-      <c r="Z22" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="34">
-        <f t="shared" si="19"/>
-        <v>288</v>
-      </c>
-      <c r="AB22" s="34">
-        <f t="shared" si="3"/>
-        <v>1888</v>
-      </c>
-      <c r="AC22" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="4"/>
-        <v>1600</v>
-      </c>
-      <c r="AE22" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-      <c r="AG22" t="s" s="36">
-        <v>198</v>
-      </c>
-      <c r="AH22" s="34">
-        <f t="shared" si="20"/>
-        <v>99968</v>
-      </c>
-      <c r="AI22" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ22" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK22" s="34">
-        <f t="shared" si="21"/>
-        <v>99968</v>
-      </c>
-      <c r="AL22" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:38">
-      <c r="A23" s="10">
-        <v>19</v>
-      </c>
-      <c r="B23" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="10">
-        <v>0</v>
-      </c>
-      <c r="D23" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="33">
-        <v>33</v>
-      </c>
-      <c r="H23" s="10">
-        <v>50</v>
-      </c>
-      <c r="I23" s="34">
-        <f t="shared" si="6"/>
-        <v>1650</v>
-      </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="9">
-        <f t="shared" si="7"/>
-        <v>1650</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" si="9"/>
-        <v>1650</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="11"/>
-        <v>1650</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="15"/>
-        <v>1650</v>
-      </c>
-      <c r="V23" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W23" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X23" s="34">
-        <f t="shared" si="16"/>
-        <v>148.5</v>
-      </c>
-      <c r="Y23" s="34">
-        <f t="shared" si="17"/>
-        <v>148.5</v>
-      </c>
-      <c r="Z23" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="34">
-        <f t="shared" si="19"/>
-        <v>297</v>
-      </c>
-      <c r="AB23" s="34">
-        <f t="shared" si="3"/>
-        <v>1947</v>
-      </c>
-      <c r="AC23" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="4"/>
-        <v>1650</v>
-      </c>
-      <c r="AE23" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="5"/>
-        <v>33</v>
-      </c>
-      <c r="AG23" t="s" s="36">
-        <v>199</v>
-      </c>
-      <c r="AH23" s="34">
-        <f t="shared" si="20"/>
-        <v>99967</v>
-      </c>
-      <c r="AI23" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ23" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK23" s="34">
-        <f t="shared" si="21"/>
-        <v>99967</v>
-      </c>
-      <c r="AL23" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:38">
-      <c r="A24" s="10">
-        <v>20</v>
-      </c>
-      <c r="B24" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="C24" s="10">
-        <v>0</v>
-      </c>
-      <c r="D24" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="33">
-        <v>34</v>
-      </c>
-      <c r="H24" s="10">
-        <v>50</v>
-      </c>
-      <c r="I24" s="34">
-        <f t="shared" si="6"/>
-        <v>1700</v>
-      </c>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="9">
-        <f t="shared" si="7"/>
-        <v>1700</v>
-      </c>
-      <c r="N24" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" si="9"/>
-        <v>1700</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="11"/>
-        <v>1700</v>
-      </c>
-      <c r="R24" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" si="15"/>
-        <v>1700</v>
-      </c>
-      <c r="V24" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W24" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X24" s="34">
-        <f t="shared" si="16"/>
-        <v>153</v>
-      </c>
-      <c r="Y24" s="34">
-        <f t="shared" si="17"/>
-        <v>153</v>
-      </c>
-      <c r="Z24" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="34">
-        <f t="shared" si="19"/>
-        <v>306</v>
-      </c>
-      <c r="AB24" s="34">
-        <f t="shared" si="3"/>
-        <v>2006</v>
-      </c>
-      <c r="AC24" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="4"/>
-        <v>1700</v>
-      </c>
-      <c r="AE24" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="5"/>
-        <v>34</v>
-      </c>
-      <c r="AG24" t="s" s="36">
-        <v>200</v>
-      </c>
-      <c r="AH24" s="34">
-        <f t="shared" si="20"/>
-        <v>99966</v>
-      </c>
-      <c r="AI24" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ24" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK24" s="34">
-        <f t="shared" si="21"/>
-        <v>99966</v>
-      </c>
-      <c r="AL24" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:38">
-      <c r="A25" s="10">
-        <v>21</v>
-      </c>
-      <c r="B25" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="10">
-        <v>0</v>
-      </c>
-      <c r="D25" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="33">
-        <v>35</v>
-      </c>
-      <c r="H25" s="10">
-        <v>50</v>
-      </c>
-      <c r="I25" s="34">
-        <f t="shared" si="6"/>
-        <v>1750</v>
-      </c>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="9">
-        <f t="shared" si="7"/>
-        <v>1750</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" si="9"/>
-        <v>1750</v>
-      </c>
-      <c r="P25" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="11"/>
-        <v>1750</v>
-      </c>
-      <c r="R25" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="15"/>
-        <v>1750</v>
-      </c>
-      <c r="V25" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W25" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X25" s="34">
-        <f t="shared" si="16"/>
-        <v>157.5</v>
-      </c>
-      <c r="Y25" s="34">
-        <f t="shared" si="17"/>
-        <v>157.5</v>
-      </c>
-      <c r="Z25" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="34">
-        <f t="shared" si="19"/>
-        <v>315</v>
-      </c>
-      <c r="AB25" s="34">
-        <f t="shared" si="3"/>
-        <v>2065</v>
-      </c>
-      <c r="AC25" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="4"/>
-        <v>1750</v>
-      </c>
-      <c r="AE25" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="5"/>
-        <v>35</v>
-      </c>
-      <c r="AG25" t="s" s="36">
-        <v>201</v>
-      </c>
-      <c r="AH25" s="34">
-        <f t="shared" si="20"/>
-        <v>99965</v>
-      </c>
-      <c r="AI25" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ25" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK25" s="34">
-        <f t="shared" si="21"/>
-        <v>99965</v>
-      </c>
-      <c r="AL25" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:38">
-      <c r="A26" s="10">
-        <v>22</v>
-      </c>
-      <c r="B26" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="10">
-        <v>0</v>
-      </c>
-      <c r="D26" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="33">
-        <v>36</v>
-      </c>
-      <c r="H26" s="10">
-        <v>50</v>
-      </c>
-      <c r="I26" s="34">
-        <f t="shared" si="6"/>
-        <v>1800</v>
-      </c>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="9">
-        <f t="shared" si="7"/>
-        <v>1800</v>
-      </c>
-      <c r="N26" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="9">
-        <f t="shared" si="9"/>
-        <v>1800</v>
-      </c>
-      <c r="P26" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="9">
-        <f t="shared" si="11"/>
-        <v>1800</v>
-      </c>
-      <c r="R26" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="9">
-        <f t="shared" si="15"/>
-        <v>1800</v>
-      </c>
-      <c r="V26" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W26" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X26" s="34">
-        <f t="shared" si="16"/>
-        <v>162</v>
-      </c>
-      <c r="Y26" s="34">
-        <f t="shared" si="17"/>
-        <v>162</v>
-      </c>
-      <c r="Z26" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA26" s="34">
-        <f t="shared" si="19"/>
-        <v>324</v>
-      </c>
-      <c r="AB26" s="34">
-        <f t="shared" si="3"/>
-        <v>2124</v>
-      </c>
-      <c r="AC26" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="4"/>
-        <v>1800</v>
-      </c>
-      <c r="AE26" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="9">
-        <f t="shared" si="5"/>
-        <v>36</v>
-      </c>
-      <c r="AG26" t="s" s="36">
-        <v>202</v>
-      </c>
-      <c r="AH26" s="34">
-        <f t="shared" si="20"/>
-        <v>99964</v>
-      </c>
-      <c r="AI26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ26" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK26" s="34">
-        <f t="shared" si="21"/>
-        <v>99964</v>
-      </c>
-      <c r="AL26" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:38">
-      <c r="A27" s="10">
-        <v>23</v>
-      </c>
-      <c r="B27" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="C27" s="10">
-        <v>0</v>
-      </c>
-      <c r="D27" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="33">
-        <v>37</v>
-      </c>
-      <c r="H27" s="10">
-        <v>50</v>
-      </c>
-      <c r="I27" s="34">
-        <f t="shared" si="6"/>
-        <v>1850</v>
-      </c>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="9">
-        <f t="shared" si="7"/>
-        <v>1850</v>
-      </c>
-      <c r="N27" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" si="9"/>
-        <v>1850</v>
-      </c>
-      <c r="P27" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="11"/>
-        <v>1850</v>
-      </c>
-      <c r="R27" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="9">
-        <f t="shared" si="15"/>
-        <v>1850</v>
-      </c>
-      <c r="V27" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W27" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X27" s="34">
-        <f t="shared" si="16"/>
-        <v>166.5</v>
-      </c>
-      <c r="Y27" s="34">
-        <f t="shared" si="17"/>
-        <v>166.5</v>
-      </c>
-      <c r="Z27" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="34">
-        <f t="shared" si="19"/>
-        <v>333</v>
-      </c>
-      <c r="AB27" s="34">
-        <f t="shared" si="3"/>
-        <v>2183</v>
-      </c>
-      <c r="AC27" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="4"/>
-        <v>1850</v>
-      </c>
-      <c r="AE27" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="AG27" t="s" s="36">
-        <v>203</v>
-      </c>
-      <c r="AH27" s="34">
-        <f t="shared" si="20"/>
-        <v>99963</v>
-      </c>
-      <c r="AI27" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ27" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK27" s="34">
-        <f t="shared" si="21"/>
-        <v>99963</v>
-      </c>
-      <c r="AL27" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:38">
-      <c r="A28" s="10">
-        <v>24</v>
-      </c>
-      <c r="B28" s="97" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" s="10">
-        <v>0</v>
-      </c>
-      <c r="D28" s="97" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="33">
-        <v>38</v>
-      </c>
-      <c r="H28" s="10">
-        <v>50</v>
-      </c>
-      <c r="I28" s="34">
-        <f t="shared" si="6"/>
-        <v>1900</v>
-      </c>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="9">
-        <f t="shared" si="7"/>
-        <v>1900</v>
-      </c>
-      <c r="N28" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="9">
-        <f t="shared" si="9"/>
-        <v>1900</v>
-      </c>
-      <c r="P28" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="11"/>
-        <v>1900</v>
-      </c>
-      <c r="R28" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="9">
-        <f t="shared" si="15"/>
-        <v>1900</v>
-      </c>
-      <c r="V28" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W28" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X28" s="34">
-        <f t="shared" si="16"/>
-        <v>171</v>
-      </c>
-      <c r="Y28" s="34">
-        <f t="shared" si="17"/>
-        <v>171</v>
-      </c>
-      <c r="Z28" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="34">
-        <f t="shared" si="19"/>
-        <v>342</v>
-      </c>
-      <c r="AB28" s="34">
-        <f t="shared" si="3"/>
-        <v>2242</v>
-      </c>
-      <c r="AC28" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="4"/>
-        <v>1900</v>
-      </c>
-      <c r="AE28" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="5"/>
-        <v>38</v>
-      </c>
-      <c r="AG28" t="s" s="36">
-        <v>204</v>
-      </c>
-      <c r="AH28" s="34">
-        <f t="shared" si="20"/>
-        <v>99962</v>
-      </c>
-      <c r="AI28" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ28" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK28" s="34">
-        <f t="shared" si="21"/>
-        <v>99962</v>
-      </c>
-      <c r="AL28" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:38">
-      <c r="A29" s="10">
-        <v>25</v>
-      </c>
-      <c r="B29" s="97" t="s">
-        <v>173</v>
-      </c>
-      <c r="C29" s="10">
-        <v>0</v>
-      </c>
-      <c r="D29" s="97" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" s="33">
-        <v>39</v>
-      </c>
-      <c r="H29" s="10">
-        <v>50</v>
-      </c>
-      <c r="I29" s="34">
-        <f t="shared" si="6"/>
-        <v>1950</v>
-      </c>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="9">
-        <f t="shared" si="7"/>
-        <v>1950</v>
-      </c>
-      <c r="N29" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="9">
-        <f t="shared" si="9"/>
-        <v>1950</v>
-      </c>
-      <c r="P29" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="9">
-        <f t="shared" si="11"/>
-        <v>1950</v>
-      </c>
-      <c r="R29" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="9">
-        <f t="shared" si="15"/>
-        <v>1950</v>
-      </c>
-      <c r="V29" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W29" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X29" s="34">
-        <f t="shared" si="16"/>
-        <v>175.5</v>
-      </c>
-      <c r="Y29" s="34">
-        <f t="shared" si="17"/>
-        <v>175.5</v>
-      </c>
-      <c r="Z29" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="34">
-        <f t="shared" si="19"/>
-        <v>351</v>
-      </c>
-      <c r="AB29" s="34">
-        <f t="shared" si="3"/>
-        <v>2301</v>
-      </c>
-      <c r="AC29" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD29" s="9">
-        <f t="shared" si="4"/>
-        <v>1950</v>
-      </c>
-      <c r="AE29" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF29" s="9">
-        <f t="shared" si="5"/>
-        <v>39</v>
-      </c>
-      <c r="AG29" t="s" s="36">
-        <v>205</v>
-      </c>
-      <c r="AH29" s="34">
-        <f t="shared" si="20"/>
-        <v>99961</v>
-      </c>
-      <c r="AI29" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ29" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK29" s="34">
-        <f t="shared" si="21"/>
-        <v>99961</v>
-      </c>
-      <c r="AL29" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:38">
-      <c r="A30" s="10">
-        <v>26</v>
-      </c>
-      <c r="B30" s="97" t="s">
-        <v>174</v>
-      </c>
-      <c r="C30" s="10">
-        <v>0</v>
-      </c>
-      <c r="D30" s="97" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="33">
-        <v>40</v>
-      </c>
-      <c r="H30" s="10">
-        <v>50</v>
-      </c>
-      <c r="I30" s="34">
-        <f t="shared" si="6"/>
-        <v>2000</v>
-      </c>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="9">
-        <f t="shared" si="7"/>
-        <v>2000</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" si="9"/>
-        <v>2000</v>
-      </c>
-      <c r="P30" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="11"/>
-        <v>2000</v>
-      </c>
-      <c r="R30" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="15"/>
-        <v>2000</v>
-      </c>
-      <c r="V30" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W30" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X30" s="34">
-        <f t="shared" si="16"/>
-        <v>180</v>
-      </c>
-      <c r="Y30" s="34">
-        <f t="shared" si="17"/>
-        <v>180</v>
-      </c>
-      <c r="Z30" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA30" s="34">
-        <f t="shared" si="19"/>
-        <v>360</v>
-      </c>
-      <c r="AB30" s="34">
-        <f t="shared" si="3"/>
-        <v>2360</v>
-      </c>
-      <c r="AC30" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD30" s="9">
-        <f t="shared" si="4"/>
-        <v>2000</v>
-      </c>
-      <c r="AE30" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-      <c r="AG30" t="s" s="36">
-        <v>206</v>
-      </c>
-      <c r="AH30" s="34">
-        <f t="shared" si="20"/>
-        <v>99960</v>
-      </c>
-      <c r="AI30" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ30" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK30" s="34">
-        <f t="shared" si="21"/>
-        <v>99960</v>
-      </c>
-      <c r="AL30" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:38">
-      <c r="A31" s="10">
-        <v>27</v>
-      </c>
-      <c r="B31" s="97" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="10">
-        <v>0</v>
-      </c>
-      <c r="D31" s="97" t="s">
-        <v>175</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" s="33">
-        <v>41</v>
-      </c>
-      <c r="H31" s="10">
-        <v>50</v>
-      </c>
-      <c r="I31" s="34">
-        <f t="shared" si="6"/>
-        <v>2050</v>
-      </c>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="9">
-        <f t="shared" si="7"/>
-        <v>2050</v>
-      </c>
-      <c r="N31" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="9">
-        <f t="shared" si="9"/>
-        <v>2050</v>
-      </c>
-      <c r="P31" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="9">
-        <f t="shared" si="11"/>
-        <v>2050</v>
-      </c>
-      <c r="R31" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="9">
-        <f t="shared" si="15"/>
-        <v>2050</v>
-      </c>
-      <c r="V31" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W31" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X31" s="34">
-        <f t="shared" si="16"/>
-        <v>184.5</v>
-      </c>
-      <c r="Y31" s="34">
-        <f t="shared" si="17"/>
-        <v>184.5</v>
-      </c>
-      <c r="Z31" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA31" s="34">
-        <f t="shared" si="19"/>
-        <v>369</v>
-      </c>
-      <c r="AB31" s="34">
-        <f t="shared" si="3"/>
-        <v>2419</v>
-      </c>
-      <c r="AC31" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD31" s="9">
-        <f t="shared" si="4"/>
-        <v>2050</v>
-      </c>
-      <c r="AE31" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="9">
-        <f t="shared" si="5"/>
-        <v>41</v>
-      </c>
-      <c r="AG31" t="s" s="36">
-        <v>207</v>
-      </c>
-      <c r="AH31" s="34">
-        <f t="shared" si="20"/>
-        <v>99959</v>
-      </c>
-      <c r="AI31" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ31" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK31" s="34">
-        <f t="shared" si="21"/>
-        <v>99959</v>
-      </c>
-      <c r="AL31" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:38">
-      <c r="A32" s="10">
-        <v>28</v>
-      </c>
-      <c r="B32" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="C32" s="10">
-        <v>0</v>
-      </c>
-      <c r="D32" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" s="33">
-        <v>42</v>
-      </c>
-      <c r="H32" s="10">
-        <v>50</v>
-      </c>
-      <c r="I32" s="34">
-        <f t="shared" si="6"/>
-        <v>2100</v>
-      </c>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="9">
-        <f t="shared" si="7"/>
-        <v>2100</v>
-      </c>
-      <c r="N32" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O32" s="9">
-        <f t="shared" si="9"/>
-        <v>2100</v>
-      </c>
-      <c r="P32" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="9">
-        <f t="shared" si="11"/>
-        <v>2100</v>
-      </c>
-      <c r="R32" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="9">
-        <f t="shared" si="15"/>
-        <v>2100</v>
-      </c>
-      <c r="V32" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W32" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X32" s="34">
-        <f t="shared" si="16"/>
-        <v>189</v>
-      </c>
-      <c r="Y32" s="34">
-        <f t="shared" si="17"/>
-        <v>189</v>
-      </c>
-      <c r="Z32" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA32" s="34">
-        <f t="shared" si="19"/>
-        <v>378</v>
-      </c>
-      <c r="AB32" s="34">
-        <f t="shared" si="3"/>
-        <v>2478</v>
-      </c>
-      <c r="AC32" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="4"/>
-        <v>2100</v>
-      </c>
-      <c r="AE32" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="9">
-        <f t="shared" si="5"/>
-        <v>42</v>
-      </c>
-      <c r="AG32" t="s" s="36">
-        <v>208</v>
-      </c>
-      <c r="AH32" s="34">
-        <f t="shared" si="20"/>
-        <v>99958</v>
-      </c>
-      <c r="AI32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ32" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK32" s="34">
-        <f t="shared" si="21"/>
-        <v>99958</v>
-      </c>
-      <c r="AL32" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:38">
-      <c r="A33" s="10">
-        <v>29</v>
-      </c>
-      <c r="B33" s="97" t="s">
-        <v>177</v>
-      </c>
-      <c r="C33" s="10">
-        <v>0</v>
-      </c>
-      <c r="D33" s="97" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" s="33">
-        <v>43</v>
-      </c>
-      <c r="H33" s="10">
-        <v>50</v>
-      </c>
-      <c r="I33" s="34">
-        <f t="shared" si="6"/>
-        <v>2150</v>
-      </c>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="9">
-        <f t="shared" si="7"/>
-        <v>2150</v>
-      </c>
-      <c r="N33" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O33" s="9">
-        <f t="shared" si="9"/>
-        <v>2150</v>
-      </c>
-      <c r="P33" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="11"/>
-        <v>2150</v>
-      </c>
-      <c r="R33" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="9">
-        <f t="shared" si="15"/>
-        <v>2150</v>
-      </c>
-      <c r="V33" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W33" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X33" s="34">
-        <f t="shared" si="16"/>
-        <v>193.5</v>
-      </c>
-      <c r="Y33" s="34">
-        <f t="shared" si="17"/>
-        <v>193.5</v>
-      </c>
-      <c r="Z33" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA33" s="34">
-        <f t="shared" si="19"/>
-        <v>387</v>
-      </c>
-      <c r="AB33" s="34">
-        <f t="shared" si="3"/>
-        <v>2537</v>
-      </c>
-      <c r="AC33" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD33" s="9">
-        <f t="shared" si="4"/>
-        <v>2150</v>
-      </c>
-      <c r="AE33" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="9">
-        <f t="shared" si="5"/>
-        <v>43</v>
-      </c>
-      <c r="AG33" t="s" s="36">
-        <v>209</v>
-      </c>
-      <c r="AH33" s="34">
-        <f t="shared" si="20"/>
-        <v>99957</v>
-      </c>
-      <c r="AI33" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ33" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK33" s="34">
-        <f t="shared" si="21"/>
-        <v>99957</v>
-      </c>
-      <c r="AL33" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:38">
-      <c r="A34" s="10">
-        <v>30</v>
-      </c>
-      <c r="B34" s="97" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="10">
-        <v>0</v>
-      </c>
-      <c r="D34" s="97" t="s">
-        <v>178</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" s="33">
-        <v>44</v>
-      </c>
-      <c r="H34" s="10">
-        <v>50</v>
-      </c>
-      <c r="I34" s="34">
-        <f t="shared" si="6"/>
-        <v>2200</v>
-      </c>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="9">
-        <f t="shared" si="7"/>
-        <v>2200</v>
-      </c>
-      <c r="N34" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="9">
-        <f t="shared" si="9"/>
-        <v>2200</v>
-      </c>
-      <c r="P34" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="9">
-        <f t="shared" si="11"/>
-        <v>2200</v>
-      </c>
-      <c r="R34" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="35">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T34" s="35">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="9">
-        <f t="shared" si="15"/>
-        <v>2200</v>
-      </c>
-      <c r="V34" s="33">
-        <v>88363222</v>
-      </c>
-      <c r="W34" s="22">
-        <v>0.18</v>
-      </c>
-      <c r="X34" s="34">
-        <f t="shared" si="16"/>
-        <v>198</v>
-      </c>
-      <c r="Y34" s="34">
-        <f t="shared" si="17"/>
-        <v>198</v>
-      </c>
-      <c r="Z34" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA34" s="34">
-        <f t="shared" si="19"/>
-        <v>396</v>
-      </c>
-      <c r="AB34" s="34">
-        <f t="shared" si="3"/>
-        <v>2596</v>
-      </c>
-      <c r="AC34" s="9">
-        <v>120</v>
-      </c>
-      <c r="AD34" s="9">
-        <f t="shared" si="4"/>
-        <v>2200</v>
-      </c>
-      <c r="AE34" s="8">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="9">
-        <f t="shared" si="5"/>
-        <v>44</v>
-      </c>
-      <c r="AG34" t="s" s="36">
-        <v>210</v>
-      </c>
-      <c r="AH34" s="34">
-        <f t="shared" si="20"/>
-        <v>99956</v>
-      </c>
-      <c r="AI34" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ34" s="10">
-        <v>4010101001</v>
-      </c>
-      <c r="AK34" s="34">
-        <f t="shared" si="21"/>
-        <v>99956</v>
-      </c>
-      <c r="AL34" s="34">
-        <f t="shared" si="22"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:38">
+    <row r="15" spans="1:39" s="23" customFormat="1">
+      <c r="B15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="G15" s="94"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="96"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="94"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="95"/>
+      <c r="Y15" s="95"/>
+      <c r="Z15" s="95"/>
+      <c r="AA15" s="95"/>
+      <c r="AB15" s="95"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="95"/>
+      <c r="AK15" s="95"/>
+      <c r="AL15" s="95"/>
+    </row>
+    <row r="16" spans="1:39" s="23" customFormat="1">
+      <c r="B16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="G16" s="94"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="96"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="94"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="95"/>
+      <c r="AK16" s="95"/>
+      <c r="AL16" s="95"/>
+    </row>
+    <row r="17" spans="2:38" s="23" customFormat="1">
+      <c r="B17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="G17" s="94"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="95"/>
+      <c r="AK17" s="95"/>
+      <c r="AL17" s="95"/>
+    </row>
+    <row r="18" spans="2:38" s="23" customFormat="1">
+      <c r="B18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="G18" s="94"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="95"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="96"/>
+      <c r="T18" s="96"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="95"/>
+      <c r="Y18" s="95"/>
+      <c r="Z18" s="95"/>
+      <c r="AA18" s="95"/>
+      <c r="AB18" s="95"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="95"/>
+      <c r="AK18" s="95"/>
+      <c r="AL18" s="95"/>
+    </row>
+    <row r="19" spans="2:38" s="23" customFormat="1">
+      <c r="B19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="G19" s="94"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="95"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="96"/>
+      <c r="T19" s="96"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="94"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="95"/>
+      <c r="Y19" s="95"/>
+      <c r="Z19" s="95"/>
+      <c r="AA19" s="95"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="24"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="95"/>
+      <c r="AK19" s="95"/>
+      <c r="AL19" s="95"/>
+    </row>
+    <row r="20" spans="2:38" s="23" customFormat="1">
+      <c r="B20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="G20" s="94"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="95"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="24"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="95"/>
+      <c r="AK20" s="95"/>
+      <c r="AL20" s="95"/>
+    </row>
+    <row r="21" spans="2:38" s="23" customFormat="1">
+      <c r="B21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="G21" s="94"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="95"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="96"/>
+      <c r="T21" s="96"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="26"/>
+      <c r="X21" s="95"/>
+      <c r="Y21" s="95"/>
+      <c r="Z21" s="95"/>
+      <c r="AA21" s="95"/>
+      <c r="AB21" s="95"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="24"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="95"/>
+      <c r="AK21" s="95"/>
+      <c r="AL21" s="95"/>
+    </row>
+    <row r="22" spans="2:38" s="23" customFormat="1">
+      <c r="B22" s="107"/>
+      <c r="D22" s="107"/>
+      <c r="G22" s="94"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="95"/>
+      <c r="L22" s="95"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="96"/>
+      <c r="T22" s="96"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="95"/>
+      <c r="Y22" s="95"/>
+      <c r="Z22" s="95"/>
+      <c r="AA22" s="95"/>
+      <c r="AB22" s="95"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="95"/>
+      <c r="AK22" s="95"/>
+      <c r="AL22" s="95"/>
+    </row>
+    <row r="23" spans="2:38" s="23" customFormat="1">
+      <c r="B23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="G23" s="94"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="96"/>
+      <c r="T23" s="96"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="95"/>
+      <c r="Y23" s="95"/>
+      <c r="Z23" s="95"/>
+      <c r="AA23" s="95"/>
+      <c r="AB23" s="95"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="24"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="95"/>
+      <c r="AK23" s="95"/>
+      <c r="AL23" s="95"/>
+    </row>
+    <row r="24" spans="2:38" s="23" customFormat="1">
+      <c r="B24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="G24" s="94"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="96"/>
+      <c r="T24" s="96"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="94"/>
+      <c r="W24" s="26"/>
+      <c r="X24" s="95"/>
+      <c r="Y24" s="95"/>
+      <c r="Z24" s="95"/>
+      <c r="AA24" s="95"/>
+      <c r="AB24" s="95"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="24"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="95"/>
+      <c r="AK24" s="95"/>
+      <c r="AL24" s="95"/>
+    </row>
+    <row r="25" spans="2:38" s="23" customFormat="1">
+      <c r="B25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="G25" s="94"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="96"/>
+      <c r="T25" s="96"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="94"/>
+      <c r="W25" s="26"/>
+      <c r="X25" s="95"/>
+      <c r="Y25" s="95"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="95"/>
+      <c r="AB25" s="95"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="24"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="95"/>
+      <c r="AK25" s="95"/>
+      <c r="AL25" s="95"/>
+    </row>
+    <row r="26" spans="2:38" s="23" customFormat="1">
+      <c r="B26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="G26" s="94"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="96"/>
+      <c r="T26" s="96"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="94"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="95"/>
+      <c r="Z26" s="95"/>
+      <c r="AA26" s="95"/>
+      <c r="AB26" s="95"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="24"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="95"/>
+      <c r="AK26" s="95"/>
+      <c r="AL26" s="95"/>
+    </row>
+    <row r="27" spans="2:38" s="23" customFormat="1">
+      <c r="B27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="G27" s="94"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="96"/>
+      <c r="T27" s="96"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="94"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="95"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="95"/>
+      <c r="AA27" s="95"/>
+      <c r="AB27" s="95"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="24"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="95"/>
+      <c r="AK27" s="95"/>
+      <c r="AL27" s="95"/>
+    </row>
+    <row r="28" spans="2:38" s="23" customFormat="1">
+      <c r="B28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="G28" s="94"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="96"/>
+      <c r="T28" s="96"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="94"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="95"/>
+      <c r="Y28" s="95"/>
+      <c r="Z28" s="95"/>
+      <c r="AA28" s="95"/>
+      <c r="AB28" s="95"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="24"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="95"/>
+      <c r="AK28" s="95"/>
+      <c r="AL28" s="95"/>
+    </row>
+    <row r="29" spans="2:38" s="23" customFormat="1">
+      <c r="B29" s="107"/>
+      <c r="D29" s="107"/>
+      <c r="G29" s="94"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="96"/>
+      <c r="T29" s="96"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="94"/>
+      <c r="W29" s="26"/>
+      <c r="X29" s="95"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="95"/>
+      <c r="AB29" s="95"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="24"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="95"/>
+      <c r="AK29" s="95"/>
+      <c r="AL29" s="95"/>
+    </row>
+    <row r="30" spans="2:38" s="23" customFormat="1">
+      <c r="B30" s="107"/>
+      <c r="D30" s="107"/>
+      <c r="G30" s="94"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="96"/>
+      <c r="T30" s="96"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="94"/>
+      <c r="W30" s="26"/>
+      <c r="X30" s="95"/>
+      <c r="Y30" s="95"/>
+      <c r="Z30" s="95"/>
+      <c r="AA30" s="95"/>
+      <c r="AB30" s="95"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="24"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+      <c r="AH30" s="95"/>
+      <c r="AK30" s="95"/>
+      <c r="AL30" s="95"/>
+    </row>
+    <row r="31" spans="2:38" s="23" customFormat="1">
+      <c r="B31" s="107"/>
+      <c r="D31" s="107"/>
+      <c r="G31" s="94"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="96"/>
+      <c r="T31" s="96"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="94"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="95"/>
+      <c r="Y31" s="95"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="95"/>
+      <c r="AB31" s="95"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="24"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25"/>
+      <c r="AH31" s="95"/>
+      <c r="AK31" s="95"/>
+      <c r="AL31" s="95"/>
+    </row>
+    <row r="32" spans="2:38" s="23" customFormat="1">
+      <c r="B32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="G32" s="94"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="95"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="96"/>
+      <c r="T32" s="96"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="95"/>
+      <c r="Y32" s="95"/>
+      <c r="Z32" s="95"/>
+      <c r="AA32" s="95"/>
+      <c r="AB32" s="95"/>
+      <c r="AC32" s="25"/>
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="24"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="25"/>
+      <c r="AH32" s="95"/>
+      <c r="AK32" s="95"/>
+      <c r="AL32" s="95"/>
+    </row>
+    <row r="33" spans="2:38" s="23" customFormat="1">
+      <c r="B33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="G33" s="94"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="96"/>
+      <c r="T33" s="96"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="94"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="95"/>
+      <c r="Y33" s="95"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="95"/>
+      <c r="AB33" s="95"/>
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="24"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+      <c r="AH33" s="95"/>
+      <c r="AK33" s="95"/>
+      <c r="AL33" s="95"/>
+    </row>
+    <row r="34" spans="2:38" s="23" customFormat="1">
+      <c r="B34" s="107"/>
+      <c r="D34" s="107"/>
+      <c r="G34" s="94"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="96"/>
+      <c r="T34" s="96"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="94"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="95"/>
+      <c r="Y34" s="95"/>
+      <c r="Z34" s="95"/>
+      <c r="AA34" s="95"/>
+      <c r="AB34" s="95"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="24"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="95"/>
+      <c r="AK34" s="95"/>
+      <c r="AL34" s="95"/>
+    </row>
+    <row r="35" spans="2:38">
       <c r="E35" s="23"/>
       <c r="F35" s="23"/>
       <c r="G35" s="94"/>
@@ -8316,7 +6558,7 @@
       <c r="AK35" s="95"/>
       <c r="AL35" s="95"/>
     </row>
-    <row r="36" spans="1:38">
+    <row r="36" spans="2:38">
       <c r="E36" s="23"/>
       <c r="F36" s="23"/>
       <c r="G36" s="94"/>
@@ -8364,7 +6606,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
@@ -8403,48 +6645,52 @@
     <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
     <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
     <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="36.0"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="41" customWidth="true" style="29" width="14.140625"/>
+    <col min="42" max="42" customWidth="true" style="29" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="29" width="16.5703125"/>
+    <col min="44" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:43" ht="27.75" customHeight="1">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
       <c r="AF1" s="54"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:43" ht="18">
       <c r="A2" s="29" t="s">
         <v>47</v>
       </c>
@@ -8483,11 +6729,11 @@
       <c r="AF2" s="54"/>
       <c r="AG2" s="27"/>
     </row>
-    <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+    <row r="3" spans="1:43" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8532,7 +6778,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:43" s="31" customFormat="1" ht="42.75">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -8642,14 +6888,28 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM4" s="58"/>
-    </row>
-    <row r="5" spans="1:39" ht="15">
+        <v>100</v>
+      </c>
+      <c r="AM4" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN4" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO4" s="98" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP4" s="98" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ4" s="98" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -8754,15 +7014,15 @@
         <v>1</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" ref="AF5" si="2">G5/AE5</f>
+        <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>149</v>
+      <c r="AG5" t="s" s="36">
+        <v>248</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
-        <v>66013</v>
+        <v>63093</v>
       </c>
       <c r="AI5" s="10" t="s">
         <v>38</v>
@@ -8772,15 +7032,31 @@
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
-        <v>66013</v>
-      </c>
-      <c r="AL5" s="34">
+        <v>63093</v>
+      </c>
+      <c r="AL5" s="33">
         <f>AK5+G5</f>
-        <v>66028</v>
-      </c>
-      <c r="AM5" s="59"/>
-    </row>
-    <row r="6" spans="1:39" ht="14.25" customHeight="1">
+        <v>63108</v>
+      </c>
+      <c r="AM5" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN5" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO5" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="AP5" s="34">
+        <f>AO5+AF5</f>
+        <v>100001600</v>
+      </c>
+      <c r="AQ5" s="28">
+        <f>AO5+AF5</f>
+        <v>100001600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" ht="14.25" customHeight="1">
       <c r="A6" s="23"/>
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
@@ -8870,36 +7146,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -8946,10 +7222,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -9214,8 +7490,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>106</v>
+      <c r="AG5" t="s" s="36">
+        <v>227</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9320,36 +7596,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9396,10 +7672,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -9664,8 +7940,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>107</v>
+      <c r="AG5" t="s" s="36">
+        <v>229</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9770,36 +8046,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9846,10 +8122,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -10114,8 +8390,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>108</v>
+      <c r="AG5" t="s" s="36">
+        <v>230</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -10220,36 +8496,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -10296,10 +8572,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -10461,13 +8737,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10564,15 +8840,15 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>109</v>
+      <c r="AG5" t="s" s="36">
+        <v>231</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -10671,36 +8947,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="39"/>
       <c r="AE1" s="39"/>
@@ -10747,10 +9023,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="38"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -10911,7 +9187,7 @@
         <v>36</v>
       </c>
       <c r="AM4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:39" ht="15">
@@ -11022,8 +9298,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>125</v>
+      <c r="AG5" t="s" s="36">
+        <v>194</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -11155,8 +9431,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>126</v>
+      <c r="AG6" t="s" s="36">
+        <v>195</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -11270,36 +9546,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -11346,10 +9622,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -11511,13 +9787,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11619,7 +9895,7 @@
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -11717,36 +9993,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -11793,10 +10069,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -11951,10 +10227,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -12026,7 +10302,7 @@
         <v>600</v>
       </c>
       <c r="V5" s="33" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="W5" s="22">
         <v>0.12</v>
@@ -12066,7 +10342,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -12175,36 +10451,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -12251,10 +10527,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:37" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -12518,8 +10794,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>123</v>
+      <c r="AG5" t="s" s="36">
+        <v>228</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -12623,36 +10899,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="65"/>
       <c r="AD1" s="65"/>
       <c r="AE1" s="65"/>
@@ -12699,10 +10975,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="64"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -12857,7 +11133,7 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="AL4" s="58"/>
     </row>
@@ -12969,8 +11245,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>7.5</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>111</v>
+      <c r="AG5" t="s" s="36">
+        <v>234</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -12983,7 +11259,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="66" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="AL5" s="59"/>
     </row>
@@ -13095,8 +11371,8 @@
         <f t="shared" ref="AF6" si="5">G6/AE6</f>
         <v>15</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>110</v>
+      <c r="AG6" t="s" s="36">
+        <v>232</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -13109,7 +11385,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="AL6" s="59"/>
     </row>
@@ -13168,36 +11444,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="69"/>
       <c r="AD1" s="69"/>
       <c r="AE1" s="69"/>
@@ -13244,10 +11520,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="68"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -13402,10 +11678,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -13517,9 +11793,9 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH5" s="9">
+        <v>89</v>
+      </c>
+      <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>9612.5</v>
       </c>
@@ -13530,10 +11806,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -13645,9 +11921,9 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH6" s="9">
+        <v>88</v>
+      </c>
+      <c r="AH6" s="34">
         <f>AG6-AF6</f>
         <v>78104</v>
       </c>
@@ -13658,10 +11934,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="AL6" s="66" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -13719,36 +11995,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="71"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
@@ -13795,10 +12071,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13953,10 +12229,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -14068,9 +12344,9 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH5" s="9">
+        <v>89</v>
+      </c>
+      <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>9612.5</v>
       </c>
@@ -14081,10 +12357,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -14196,9 +12472,9 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH6" s="9">
+        <v>88</v>
+      </c>
+      <c r="AH6" s="34">
         <f>AG6-AF6</f>
         <v>78104</v>
       </c>
@@ -14209,10 +12485,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="AL6" s="66" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -14270,36 +12546,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="74"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
@@ -14346,10 +12622,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="73"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -14504,10 +12780,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -14515,13 +12791,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -14629,10 +12905,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -14690,36 +12966,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="76"/>
       <c r="AD1" s="76"/>
       <c r="AE1" s="76"/>
@@ -14766,10 +13042,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="75"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -14924,10 +13200,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -14935,13 +13211,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15049,10 +13325,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -15110,36 +13386,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="78"/>
       <c r="AD1" s="78"/>
       <c r="AE1" s="78"/>
@@ -15186,10 +13462,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="77"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -15344,10 +13620,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -15355,13 +13631,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15469,10 +13745,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -15531,36 +13807,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="84"/>
       <c r="AD1" s="84"/>
       <c r="AE1" s="84"/>
@@ -15607,10 +13883,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="83"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -15765,10 +14041,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -15880,15 +14156,15 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>130</v>
+      <c r="AG5" t="s" s="36">
+        <v>243</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>49586</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -15993,36 +14269,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="41"/>
       <c r="AD1" s="41"/>
       <c r="AE1" s="41"/>
@@ -16069,10 +14345,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="40"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -16255,8 +14531,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>52</v>
+      <c r="H5" t="s" s="29">
+        <v>58</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -16341,8 +14617,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>94</v>
+      <c r="AG5" t="s" s="36">
+        <v>201</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16384,8 +14660,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>53</v>
+      <c r="H6" t="s" s="29">
+        <v>68</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -16470,8 +14746,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>95</v>
+      <c r="AG6" t="s" s="36">
+        <v>202</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16582,36 +14858,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
       <c r="AE1" s="82"/>
@@ -16658,10 +14934,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="81"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -16816,10 +15092,10 @@
         <v>45</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -16931,15 +15207,15 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>129</v>
+      <c r="AG5" t="s" s="36">
+        <v>241</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -17001,14 +15277,415 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="122" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="58"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="59"/>
+    </row>
+    <row r="6" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="D6" s="113">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="122" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="58"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="59"/>
+    </row>
+    <row r="6" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="D6" s="113">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="122" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="58"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="59"/>
+    </row>
+    <row r="6" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="D6" s="113">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="122" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="58"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="59"/>
+    </row>
+    <row r="6" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="D6" s="113">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="122" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="D2" s="119"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="118"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="58"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -17062,36 +15739,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="44"/>
       <c r="AD1" s="44"/>
       <c r="AE1" s="44"/>
@@ -17138,10 +15815,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="43"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -17307,13 +15984,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -17324,8 +16001,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>56</v>
+      <c r="H5" t="s" s="29">
+        <v>62</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17410,8 +16087,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>96</v>
+      <c r="AG5" t="s" s="36">
+        <v>203</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17436,13 +16113,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -17453,8 +16130,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>58</v>
+      <c r="H6" t="s" s="29">
+        <v>54</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -17539,8 +16216,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>62</v>
+      <c r="AG6" t="s" s="36">
+        <v>204</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17650,36 +16327,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="46"/>
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
@@ -17726,10 +16403,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="45"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -17895,13 +16572,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -17912,8 +16589,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>61</v>
+      <c r="H5" t="s" s="29">
+        <v>57</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17998,8 +16675,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>97</v>
+      <c r="AG5" t="s" s="36">
+        <v>235</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18024,13 +16701,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -18041,8 +16718,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>63</v>
+      <c r="H6" t="s" s="29">
+        <v>58</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -18127,8 +16804,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>98</v>
+      <c r="AG6" t="s" s="36">
+        <v>236</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18238,36 +16915,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
@@ -18314,10 +16991,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="47"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -18483,13 +17160,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -18500,8 +17177,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>66</v>
+      <c r="H5" t="s" s="29">
+        <v>61</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -18586,8 +17263,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>99</v>
+      <c r="AG5" t="s" s="36">
+        <v>211</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18612,13 +17289,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -18629,8 +17306,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>67</v>
+      <c r="H6" t="s" s="29">
+        <v>62</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -18715,8 +17392,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>83</v>
+      <c r="AG6" t="s" s="36">
+        <v>212</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18826,36 +17503,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -18902,10 +17579,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -19071,13 +17748,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -19088,8 +17765,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>72</v>
+      <c r="H5" t="s" s="29">
+        <v>67</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -19174,8 +17851,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>100</v>
+      <c r="AG5" t="s" s="36">
+        <v>216</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -19200,13 +17877,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -19217,8 +17894,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>73</v>
+      <c r="H6" t="s" s="29">
+        <v>68</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -19303,8 +17980,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>101</v>
+      <c r="AG6" t="s" s="36">
+        <v>217</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -19414,36 +18091,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -19490,10 +18167,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -19659,13 +18336,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -19676,8 +18353,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>74</v>
+      <c r="H5" t="s" s="29">
+        <v>69</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -19762,8 +18439,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>102</v>
+      <c r="AG5" t="s" s="36">
+        <v>218</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -19788,13 +18465,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -19805,8 +18482,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>75</v>
+      <c r="H6" t="s" s="29">
+        <v>70</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -19891,8 +18568,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>103</v>
+      <c r="AG6" t="s" s="36">
+        <v>208</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -20002,36 +18679,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -20078,10 +18755,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="98"/>
+      <c r="A3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -20247,13 +18924,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -20264,8 +18941,8 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>80</v>
+      <c r="H5" t="s" s="29">
+        <v>75</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -20350,8 +19027,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>104</v>
+      <c r="AG5" t="s" s="36">
+        <v>222</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -20376,13 +19053,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -20393,8 +19070,8 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>81</v>
+      <c r="H6" t="s" s="29">
+        <v>76</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -20479,8 +19156,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" s="36" t="s">
-        <v>98</v>
+      <c r="AG6" t="s" s="36">
+        <v>223</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="28" activeTab="34"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="28" activeTab="31"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="279">
   <si>
     <t>GST Sales</t>
   </si>
@@ -373,9 +373,6 @@
     <t>HK-FIFO-LOT-BATCH-10001(FG)</t>
   </si>
   <si>
-    <t>49526</t>
-  </si>
-  <si>
     <t>Charges</t>
   </si>
   <si>
@@ -496,9 +493,6 @@
     <t>105596</t>
   </si>
   <si>
-    <t>49151</t>
-  </si>
-  <si>
     <t>64383</t>
   </si>
   <si>
@@ -535,90 +529,6 @@
     <t>Scenario  : Open SCO Price Level Type - Item + Process</t>
   </si>
   <si>
-    <t>63938</t>
-  </si>
-  <si>
-    <t>19275</t>
-  </si>
-  <si>
-    <t>63923</t>
-  </si>
-  <si>
-    <t>19270</t>
-  </si>
-  <si>
-    <t>9255</t>
-  </si>
-  <si>
-    <t>19808.992</t>
-  </si>
-  <si>
-    <t>109415</t>
-  </si>
-  <si>
-    <t>109755</t>
-  </si>
-  <si>
-    <t>9765</t>
-  </si>
-  <si>
-    <t>9307</t>
-  </si>
-  <si>
-    <t>9715</t>
-  </si>
-  <si>
-    <t>9415</t>
-  </si>
-  <si>
-    <t>9760</t>
-  </si>
-  <si>
-    <t>9293</t>
-  </si>
-  <si>
-    <t>9702.5</t>
-  </si>
-  <si>
-    <t>9425</t>
-  </si>
-  <si>
-    <t>109411</t>
-  </si>
-  <si>
-    <t>109750</t>
-  </si>
-  <si>
-    <t>109500</t>
-  </si>
-  <si>
-    <t>109785</t>
-  </si>
-  <si>
-    <t>63893</t>
-  </si>
-  <si>
-    <t>63878</t>
-  </si>
-  <si>
-    <t>63863</t>
-  </si>
-  <si>
-    <t>63848</t>
-  </si>
-  <si>
-    <t>488826</t>
-  </si>
-  <si>
-    <t>63838</t>
-  </si>
-  <si>
-    <t>18880</t>
-  </si>
-  <si>
-    <t>19265</t>
-  </si>
-  <si>
     <t>Scenario  : Open SCO Price Level Type - Supplier + Process</t>
   </si>
   <si>
@@ -640,27 +550,12 @@
     <t>7</t>
   </si>
   <si>
-    <t>63823</t>
-  </si>
-  <si>
-    <t>19257.5</t>
-  </si>
-  <si>
     <t>63808</t>
   </si>
   <si>
     <t>19252.5</t>
   </si>
   <si>
-    <t>9240</t>
-  </si>
-  <si>
-    <t>19803.992</t>
-  </si>
-  <si>
-    <t>109400</t>
-  </si>
-  <si>
     <t>63793</t>
   </si>
   <si>
@@ -679,39 +574,15 @@
     <t>109745</t>
   </si>
   <si>
-    <t>9292</t>
-  </si>
-  <si>
-    <t>9710</t>
-  </si>
-  <si>
-    <t>9400</t>
-  </si>
-  <si>
     <t>9755</t>
   </si>
   <si>
-    <t>9277</t>
-  </si>
-  <si>
-    <t>9705</t>
-  </si>
-  <si>
     <t>9385</t>
   </si>
   <si>
     <t>9750</t>
   </si>
   <si>
-    <t>9278</t>
-  </si>
-  <si>
-    <t>9697.5</t>
-  </si>
-  <si>
-    <t>9410</t>
-  </si>
-  <si>
     <t>9263</t>
   </si>
   <si>
@@ -721,15 +592,6 @@
     <t>9395</t>
   </si>
   <si>
-    <t>109396</t>
-  </si>
-  <si>
-    <t>109485</t>
-  </si>
-  <si>
-    <t>109780</t>
-  </si>
-  <si>
     <t>109381</t>
   </si>
   <si>
@@ -742,9 +604,6 @@
     <t>109775</t>
   </si>
   <si>
-    <t>63778</t>
-  </si>
-  <si>
     <t>63763</t>
   </si>
   <si>
@@ -775,40 +634,271 @@
     <t>9700</t>
   </si>
   <si>
-    <t>63693</t>
-  </si>
-  <si>
-    <t>63678</t>
-  </si>
-  <si>
-    <t>63663</t>
-  </si>
-  <si>
-    <t>49136</t>
-  </si>
-  <si>
     <t>49121</t>
   </si>
   <si>
-    <t>49106</t>
-  </si>
-  <si>
     <t>49091</t>
   </si>
   <si>
-    <t>63648</t>
-  </si>
-  <si>
-    <t>63633</t>
-  </si>
-  <si>
-    <t>63618</t>
-  </si>
-  <si>
-    <t>63603</t>
-  </si>
-  <si>
     <t>63588</t>
+  </si>
+  <si>
+    <t>63573</t>
+  </si>
+  <si>
+    <t>19235</t>
+  </si>
+  <si>
+    <t>9210</t>
+  </si>
+  <si>
+    <t>19793.992</t>
+  </si>
+  <si>
+    <t>63558</t>
+  </si>
+  <si>
+    <t>19230</t>
+  </si>
+  <si>
+    <t>9195</t>
+  </si>
+  <si>
+    <t>19788.992</t>
+  </si>
+  <si>
+    <t>9247</t>
+  </si>
+  <si>
+    <t>9695</t>
+  </si>
+  <si>
+    <t>9232</t>
+  </si>
+  <si>
+    <t>9690</t>
+  </si>
+  <si>
+    <t>9248</t>
+  </si>
+  <si>
+    <t>9687.5</t>
+  </si>
+  <si>
+    <t>9233</t>
+  </si>
+  <si>
+    <t>9682.5</t>
+  </si>
+  <si>
+    <t>109366</t>
+  </si>
+  <si>
+    <t>109735</t>
+  </si>
+  <si>
+    <t>109351</t>
+  </si>
+  <si>
+    <t>109730</t>
+  </si>
+  <si>
+    <t>63543</t>
+  </si>
+  <si>
+    <t>63528</t>
+  </si>
+  <si>
+    <t>63513</t>
+  </si>
+  <si>
+    <t>63498</t>
+  </si>
+  <si>
+    <t>488806</t>
+  </si>
+  <si>
+    <t>63488</t>
+  </si>
+  <si>
+    <t>18850</t>
+  </si>
+  <si>
+    <t>19225</t>
+  </si>
+  <si>
+    <t>63473</t>
+  </si>
+  <si>
+    <t>63458</t>
+  </si>
+  <si>
+    <t>63443</t>
+  </si>
+  <si>
+    <t>49076</t>
+  </si>
+  <si>
+    <t>63428</t>
+  </si>
+  <si>
+    <t>63413</t>
+  </si>
+  <si>
+    <t>63398</t>
+  </si>
+  <si>
+    <t>63383</t>
+  </si>
+  <si>
+    <t>63368</t>
+  </si>
+  <si>
+    <t>63338</t>
+  </si>
+  <si>
+    <t>63323</t>
+  </si>
+  <si>
+    <t>63308</t>
+  </si>
+  <si>
+    <t>63293</t>
+  </si>
+  <si>
+    <t>63278</t>
+  </si>
+  <si>
+    <t>63263</t>
+  </si>
+  <si>
+    <t>49061</t>
+  </si>
+  <si>
+    <t>63248</t>
+  </si>
+  <si>
+    <t>63233</t>
+  </si>
+  <si>
+    <t>63218</t>
+  </si>
+  <si>
+    <t>63203</t>
+  </si>
+  <si>
+    <t>63188</t>
+  </si>
+  <si>
+    <t>63173</t>
+  </si>
+  <si>
+    <t>63158</t>
+  </si>
+  <si>
+    <t>63143</t>
+  </si>
+  <si>
+    <t>63128</t>
+  </si>
+  <si>
+    <t>63113</t>
+  </si>
+  <si>
+    <t>63098</t>
+  </si>
+  <si>
+    <t>63083</t>
+  </si>
+  <si>
+    <t>63068</t>
+  </si>
+  <si>
+    <t>63053</t>
+  </si>
+  <si>
+    <t>63038</t>
+  </si>
+  <si>
+    <t>63023</t>
+  </si>
+  <si>
+    <t>63008</t>
+  </si>
+  <si>
+    <t>62993</t>
+  </si>
+  <si>
+    <t>62978</t>
+  </si>
+  <si>
+    <t>19217.5</t>
+  </si>
+  <si>
+    <t>9180</t>
+  </si>
+  <si>
+    <t>19783.992</t>
+  </si>
+  <si>
+    <t>62963</t>
+  </si>
+  <si>
+    <t>19212.5</t>
+  </si>
+  <si>
+    <t>9165</t>
+  </si>
+  <si>
+    <t>19778.992</t>
+  </si>
+  <si>
+    <t>9217</t>
+  </si>
+  <si>
+    <t>9685</t>
+  </si>
+  <si>
+    <t>9202</t>
+  </si>
+  <si>
+    <t>9680</t>
+  </si>
+  <si>
+    <t>9218</t>
+  </si>
+  <si>
+    <t>9677.5</t>
+  </si>
+  <si>
+    <t>9203</t>
+  </si>
+  <si>
+    <t>9672.5</t>
+  </si>
+  <si>
+    <t>109336</t>
+  </si>
+  <si>
+    <t>109725</t>
+  </si>
+  <si>
+    <t>109321</t>
+  </si>
+  <si>
+    <t>109720</t>
+  </si>
+  <si>
+    <t>62948</t>
+  </si>
+  <si>
+    <t>49046</t>
+  </si>
+  <si>
+    <t>49031</t>
+  </si>
+  <si>
+    <t>62933</t>
   </si>
 </sst>
 </file>
@@ -1952,7 +2042,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>199</v>
+        <v>259</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2081,7 +2171,7 @@
         <v>5</v>
       </c>
       <c r="AG6" t="s" s="36">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2449,7 +2539,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="9">
@@ -2535,8 +2625,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>224</v>
+      <c r="AG5" s="36" t="s">
+        <v>178</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2573,7 +2663,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>78</v>
       </c>
       <c r="I6" s="9">
@@ -2659,8 +2749,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>225</v>
+      <c r="AG6" s="36" t="s">
+        <v>179</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -3116,7 +3206,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3578,8 +3668,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>145</v>
+      <c r="AG5" t="s" s="36">
+        <v>246</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3638,7 +3728,7 @@
     </row>
     <row r="9" spans="1:39">
       <c r="C9" s="89" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
@@ -3655,7 +3745,7 @@
     </row>
     <row r="10" spans="1:39">
       <c r="C10" s="90" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>6</v>
@@ -3664,19 +3754,19 @@
         <v>7</v>
       </c>
       <c r="F10" s="90" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="90" t="s">
+      <c r="H10" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="90" t="s">
+      <c r="I10" s="90" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="90" t="s">
+      <c r="J10" s="90" t="s">
         <v>109</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>110</v>
       </c>
       <c r="K10" s="90" t="s">
         <v>26</v>
@@ -3699,16 +3789,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="G11" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="H11" s="10">
         <v>20</v>
@@ -3740,16 +3830,16 @@
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="10">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>115</v>
-      </c>
       <c r="G12" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
@@ -3781,7 +3871,7 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I13" s="10">
         <v>21477.41</v>
@@ -4103,13 +4193,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4207,7 +4297,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4670,7 +4760,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4697,13 +4787,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="97" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="97" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -4801,7 +4891,7 @@
         <v>16</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
@@ -4827,13 +4917,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="97" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
       </c>
       <c r="D7" s="97" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -4931,7 +5021,7 @@
         <v>17</v>
       </c>
       <c r="AG7" s="36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AH7" s="34">
         <f t="shared" ref="AH7:AH14" si="20">AG7-AF7</f>
@@ -4957,13 +5047,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>32</v>
@@ -5061,7 +5151,7 @@
         <v>18</v>
       </c>
       <c r="AG8" s="36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AH8" s="34">
         <f t="shared" si="20"/>
@@ -5087,13 +5177,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="97" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
       </c>
       <c r="D9" s="97" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>32</v>
@@ -5191,7 +5281,7 @@
         <v>19</v>
       </c>
       <c r="AG9" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AH9" s="34">
         <f t="shared" si="20"/>
@@ -5217,13 +5307,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>32</v>
@@ -5321,7 +5411,7 @@
         <v>20</v>
       </c>
       <c r="AG10" s="36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AH10" s="34">
         <f t="shared" si="20"/>
@@ -5347,13 +5437,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
       </c>
       <c r="D11" s="97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>32</v>
@@ -5451,7 +5541,7 @@
         <v>21</v>
       </c>
       <c r="AG11" s="36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AH11" s="34">
         <f t="shared" si="20"/>
@@ -5477,13 +5567,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12" s="99">
         <v>0</v>
       </c>
       <c r="D12" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" s="99" t="s">
         <v>32</v>
@@ -5581,7 +5671,7 @@
         <v>22</v>
       </c>
       <c r="AG12" s="36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AH12" s="102">
         <f t="shared" si="20"/>
@@ -5607,13 +5697,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>32</v>
@@ -5711,7 +5801,7 @@
         <v>23</v>
       </c>
       <c r="AG13" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AH13" s="34">
         <f t="shared" si="20"/>
@@ -5737,13 +5827,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>32</v>
@@ -5841,7 +5931,7 @@
         <v>24</v>
       </c>
       <c r="AG14" s="36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AH14" s="34">
         <f t="shared" si="20"/>
@@ -6894,19 +6984,19 @@
         <v>100</v>
       </c>
       <c r="AM4" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN4" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO4" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="AN4" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="AO4" s="98" t="s">
+      <c r="AP4" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="AP4" s="98" t="s">
+      <c r="AQ4" s="98" t="s">
         <v>131</v>
-      </c>
-      <c r="AQ4" s="98" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="15">
@@ -7018,7 +7108,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -7042,10 +7132,10 @@
         <v>79</v>
       </c>
       <c r="AN5" s="67" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AO5" s="29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7491,7 +7581,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -7941,7 +8031,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8391,7 +8481,7 @@
         <v>10</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8841,7 +8931,7 @@
         <v>10</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9299,7 +9389,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>194</v>
+        <v>275</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9431,8 +9521,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>195</v>
+      <c r="AG6" s="36" t="s">
+        <v>163</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -10794,8 +10884,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>228</v>
+      <c r="AG5" s="36" t="s">
+        <v>181</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -11246,7 +11336,7 @@
         <v>7.5</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -11372,7 +11462,7 @@
         <v>15</v>
       </c>
       <c r="AG6" t="s" s="36">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -14156,8 +14246,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>243</v>
+      <c r="AG5" s="36" t="s">
+        <v>191</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -14618,7 +14708,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -14747,7 +14837,7 @@
         <v>5</v>
       </c>
       <c r="AG6" t="s" s="36">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -15208,7 +15298,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -15290,7 +15380,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="122" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="122"/>
@@ -15311,13 +15401,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15326,13 +15416,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
       </c>
       <c r="D5" s="112" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E5" s="59"/>
     </row>
@@ -15341,7 +15431,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -15375,7 +15465,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="122" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="122"/>
@@ -15396,13 +15486,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15411,13 +15501,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
       </c>
       <c r="D5" s="112" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E5" s="59"/>
     </row>
@@ -15426,7 +15516,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -15460,7 +15550,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="122" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="122"/>
@@ -15481,13 +15571,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15496,13 +15586,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
       </c>
       <c r="D5" s="112" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E5" s="59"/>
     </row>
@@ -15511,7 +15601,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -15545,7 +15635,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="122" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="122"/>
@@ -15566,13 +15656,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15581,13 +15671,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
       </c>
       <c r="D5" s="112" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E5" s="59"/>
     </row>
@@ -15596,7 +15686,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -15630,7 +15720,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="122" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="122"/>
@@ -15653,10 +15743,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15665,13 +15755,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="E5" s="59"/>
     </row>
@@ -16001,7 +16091,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>62</v>
       </c>
       <c r="I5" s="9">
@@ -16087,8 +16177,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>203</v>
+      <c r="AG5" s="36" t="s">
+        <v>168</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16130,7 +16220,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I6" s="9">
@@ -16216,8 +16306,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>204</v>
+      <c r="AG6" s="36" t="s">
+        <v>169</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16676,7 +16766,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16805,7 +16895,7 @@
         <v>5</v>
       </c>
       <c r="AG6" t="s" s="36">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17177,7 +17267,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>61</v>
       </c>
       <c r="I5" s="9">
@@ -17263,8 +17353,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>211</v>
+      <c r="AG5" s="36" t="s">
+        <v>171</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17306,7 +17396,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>62</v>
       </c>
       <c r="I6" s="9">
@@ -17392,8 +17482,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>212</v>
+      <c r="AG6" s="36" t="s">
+        <v>172</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17852,7 +17942,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17981,7 +18071,7 @@
         <v>5</v>
       </c>
       <c r="AG6" t="s" s="36">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18353,7 +18443,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>69</v>
       </c>
       <c r="I5" s="9">
@@ -18439,8 +18529,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>218</v>
+      <c r="AG5" s="36" t="s">
+        <v>175</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18482,7 +18572,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="9">
@@ -18568,8 +18658,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>208</v>
+      <c r="AG6" s="36" t="s">
+        <v>170</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -19028,7 +19118,7 @@
         <v>15</v>
       </c>
       <c r="AG5" t="s" s="36">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -19157,7 +19247,7 @@
         <v>5</v>
       </c>
       <c r="AG6" t="s" s="36">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="28" activeTab="31"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="32" activeTab="36"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,14 @@
     <sheet name="CRNoteExportService" sheetId="28" r:id="rId28"/>
     <sheet name="CRNoteGateEntryExport" sheetId="31" r:id="rId29"/>
     <sheet name="CRNoteGateEntry" sheetId="30" r:id="rId30"/>
-    <sheet name="OP_S+I+P" sheetId="35" r:id="rId31"/>
-    <sheet name="OP_I+P" sheetId="36" r:id="rId32"/>
-    <sheet name="OP_S+P" sheetId="37" r:id="rId33"/>
-    <sheet name="OP_P" sheetId="38" r:id="rId34"/>
-    <sheet name="DirectSCO" sheetId="39" r:id="rId35"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId36"/>
+    <sheet name="OpenSCORevise" sheetId="41" r:id="rId31"/>
+    <sheet name="OpenSCO" sheetId="40" r:id="rId32"/>
+    <sheet name="DirectSCOWithSO" sheetId="43" r:id="rId33"/>
+    <sheet name="DirectSCOWithProject" sheetId="45" r:id="rId34"/>
+    <sheet name="DirectSCOWithSOandConv" sheetId="44" r:id="rId35"/>
+    <sheet name="DirectSCOWithConv" sheetId="42" r:id="rId36"/>
+    <sheet name="DirectSCO" sheetId="39" r:id="rId37"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId38"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="200">
   <si>
     <t>GST Sales</t>
   </si>
@@ -493,412 +495,175 @@
     <t>105596</t>
   </si>
   <si>
-    <t>64383</t>
-  </si>
-  <si>
     <t>100001867</t>
   </si>
   <si>
-    <t>Scenario  : Open SCO Price Level Type - Supplier + Item + Process</t>
-  </si>
-  <si>
     <t>Process</t>
   </si>
   <si>
-    <t>Batch Qty</t>
-  </si>
-  <si>
-    <t>Batch Cost</t>
+    <t>Scenario  : Direct SCO With BOM Standard Type</t>
+  </si>
+  <si>
+    <t>Vj-FIFO-LOT-BATCH-50001(FG)</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>19252.5</t>
+  </si>
+  <si>
+    <t>109385</t>
+  </si>
+  <si>
+    <t>109745</t>
+  </si>
+  <si>
+    <t>9755</t>
+  </si>
+  <si>
+    <t>9385</t>
+  </si>
+  <si>
+    <t>9750</t>
+  </si>
+  <si>
+    <t>9395</t>
+  </si>
+  <si>
+    <t>109470</t>
+  </si>
+  <si>
+    <t>109775</t>
+  </si>
+  <si>
+    <t>63748</t>
+  </si>
+  <si>
+    <t>49091</t>
+  </si>
+  <si>
+    <t>63528</t>
+  </si>
+  <si>
+    <t>63513</t>
+  </si>
+  <si>
+    <t>63498</t>
+  </si>
+  <si>
+    <t>488806</t>
+  </si>
+  <si>
+    <t>63488</t>
+  </si>
+  <si>
+    <t>18850</t>
+  </si>
+  <si>
+    <t>19225</t>
+  </si>
+  <si>
+    <t>63113</t>
+  </si>
+  <si>
+    <t>62963</t>
+  </si>
+  <si>
+    <t>19212.5</t>
+  </si>
+  <si>
+    <t>9165</t>
+  </si>
+  <si>
+    <t>19778.992</t>
+  </si>
+  <si>
+    <t>9202</t>
+  </si>
+  <si>
+    <t>9680</t>
+  </si>
+  <si>
+    <t>9203</t>
+  </si>
+  <si>
+    <t>9672.5</t>
+  </si>
+  <si>
+    <t>109321</t>
+  </si>
+  <si>
+    <t>109720</t>
+  </si>
+  <si>
+    <t>62948</t>
+  </si>
+  <si>
+    <t>49031</t>
+  </si>
+  <si>
+    <t>62933</t>
+  </si>
+  <si>
+    <t>PROC-003</t>
+  </si>
+  <si>
+    <t>BatchQty</t>
+  </si>
+  <si>
+    <t>BatchCost</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Scenario  : Open SCO Revise</t>
+  </si>
+  <si>
+    <t>Scenario  : Open SCO Price</t>
+  </si>
+  <si>
+    <t>FG0004</t>
+  </si>
+  <si>
+    <t>MOULDING</t>
+  </si>
+  <si>
+    <t>GLACCT</t>
+  </si>
+  <si>
+    <t>CHARGES ACCOUNT</t>
+  </si>
+  <si>
+    <t>Scenario  : Direct SCO With Conv. Factor</t>
+  </si>
+  <si>
+    <t>FG20001</t>
+  </si>
+  <si>
+    <t>SO Ref</t>
+  </si>
+  <si>
+    <t>SO100/05696/25-26</t>
+  </si>
+  <si>
+    <t>FG30001</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>PROCESS-20</t>
-  </si>
-  <si>
-    <t>METAL FORMING PROCES</t>
-  </si>
-  <si>
-    <t>PACKINGS</t>
-  </si>
-  <si>
-    <t>POST CURING</t>
-  </si>
-  <si>
-    <t>Scenario  : Open SCO Price Level Type - Item + Process</t>
-  </si>
-  <si>
-    <t>Scenario  : Open SCO Price Level Type - Supplier + Process</t>
-  </si>
-  <si>
-    <t>Scenario  : Open SCO Price Level Type - Process</t>
-  </si>
-  <si>
-    <t>Scenario  : Direct SCO With BOM Standard Type</t>
-  </si>
-  <si>
-    <t>Vj-FIFO-LOT-BATCH-50001(FG)</t>
-  </si>
-  <si>
-    <t>SLICING</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>63808</t>
-  </si>
-  <si>
-    <t>19252.5</t>
-  </si>
-  <si>
-    <t>63793</t>
-  </si>
-  <si>
-    <t>19247.5</t>
-  </si>
-  <si>
-    <t>9225</t>
-  </si>
-  <si>
-    <t>19798.992</t>
-  </si>
-  <si>
-    <t>109385</t>
-  </si>
-  <si>
-    <t>109745</t>
-  </si>
-  <si>
-    <t>9755</t>
-  </si>
-  <si>
-    <t>9385</t>
-  </si>
-  <si>
-    <t>9750</t>
-  </si>
-  <si>
-    <t>9263</t>
-  </si>
-  <si>
-    <t>9692.5</t>
-  </si>
-  <si>
-    <t>9395</t>
-  </si>
-  <si>
-    <t>109381</t>
-  </si>
-  <si>
-    <t>109740</t>
-  </si>
-  <si>
-    <t>109470</t>
-  </si>
-  <si>
-    <t>109775</t>
-  </si>
-  <si>
-    <t>63763</t>
-  </si>
-  <si>
-    <t>63748</t>
-  </si>
-  <si>
-    <t>63733</t>
-  </si>
-  <si>
-    <t>63718</t>
-  </si>
-  <si>
-    <t>488816</t>
-  </si>
-  <si>
-    <t>63708</t>
-  </si>
-  <si>
-    <t>18865</t>
-  </si>
-  <si>
-    <t>19242.5</t>
-  </si>
-  <si>
-    <t>9262</t>
-  </si>
-  <si>
-    <t>9700</t>
-  </si>
-  <si>
-    <t>49121</t>
-  </si>
-  <si>
-    <t>49091</t>
-  </si>
-  <si>
-    <t>63588</t>
-  </si>
-  <si>
-    <t>63573</t>
-  </si>
-  <si>
-    <t>19235</t>
-  </si>
-  <si>
-    <t>9210</t>
-  </si>
-  <si>
-    <t>19793.992</t>
-  </si>
-  <si>
-    <t>63558</t>
-  </si>
-  <si>
-    <t>19230</t>
-  </si>
-  <si>
-    <t>9195</t>
-  </si>
-  <si>
-    <t>19788.992</t>
-  </si>
-  <si>
-    <t>9247</t>
-  </si>
-  <si>
-    <t>9695</t>
-  </si>
-  <si>
-    <t>9232</t>
-  </si>
-  <si>
-    <t>9690</t>
-  </si>
-  <si>
-    <t>9248</t>
-  </si>
-  <si>
-    <t>9687.5</t>
-  </si>
-  <si>
-    <t>9233</t>
-  </si>
-  <si>
-    <t>9682.5</t>
-  </si>
-  <si>
-    <t>109366</t>
-  </si>
-  <si>
-    <t>109735</t>
-  </si>
-  <si>
-    <t>109351</t>
-  </si>
-  <si>
-    <t>109730</t>
-  </si>
-  <si>
-    <t>63543</t>
-  </si>
-  <si>
-    <t>63528</t>
-  </si>
-  <si>
-    <t>63513</t>
-  </si>
-  <si>
-    <t>63498</t>
-  </si>
-  <si>
-    <t>488806</t>
-  </si>
-  <si>
-    <t>63488</t>
-  </si>
-  <si>
-    <t>18850</t>
-  </si>
-  <si>
-    <t>19225</t>
-  </si>
-  <si>
-    <t>63473</t>
-  </si>
-  <si>
-    <t>63458</t>
-  </si>
-  <si>
-    <t>63443</t>
-  </si>
-  <si>
-    <t>49076</t>
-  </si>
-  <si>
-    <t>63428</t>
-  </si>
-  <si>
-    <t>63413</t>
-  </si>
-  <si>
-    <t>63398</t>
-  </si>
-  <si>
-    <t>63383</t>
-  </si>
-  <si>
-    <t>63368</t>
-  </si>
-  <si>
-    <t>63338</t>
-  </si>
-  <si>
-    <t>63323</t>
-  </si>
-  <si>
-    <t>63308</t>
-  </si>
-  <si>
-    <t>63293</t>
-  </si>
-  <si>
-    <t>63278</t>
-  </si>
-  <si>
-    <t>63263</t>
-  </si>
-  <si>
-    <t>49061</t>
-  </si>
-  <si>
-    <t>63248</t>
-  </si>
-  <si>
-    <t>63233</t>
-  </si>
-  <si>
-    <t>63218</t>
-  </si>
-  <si>
-    <t>63203</t>
-  </si>
-  <si>
-    <t>63188</t>
-  </si>
-  <si>
-    <t>63173</t>
-  </si>
-  <si>
-    <t>63158</t>
-  </si>
-  <si>
-    <t>63143</t>
-  </si>
-  <si>
-    <t>63128</t>
-  </si>
-  <si>
-    <t>63113</t>
-  </si>
-  <si>
-    <t>63098</t>
-  </si>
-  <si>
-    <t>63083</t>
-  </si>
-  <si>
-    <t>63068</t>
-  </si>
-  <si>
-    <t>63053</t>
-  </si>
-  <si>
-    <t>63038</t>
-  </si>
-  <si>
-    <t>63023</t>
-  </si>
-  <si>
-    <t>63008</t>
-  </si>
-  <si>
-    <t>62993</t>
-  </si>
-  <si>
-    <t>62978</t>
-  </si>
-  <si>
-    <t>19217.5</t>
-  </si>
-  <si>
-    <t>9180</t>
-  </si>
-  <si>
-    <t>19783.992</t>
-  </si>
-  <si>
-    <t>62963</t>
-  </si>
-  <si>
-    <t>19212.5</t>
-  </si>
-  <si>
-    <t>9165</t>
-  </si>
-  <si>
-    <t>19778.992</t>
-  </si>
-  <si>
-    <t>9217</t>
-  </si>
-  <si>
-    <t>9685</t>
-  </si>
-  <si>
-    <t>9202</t>
-  </si>
-  <si>
-    <t>9680</t>
-  </si>
-  <si>
-    <t>9218</t>
-  </si>
-  <si>
-    <t>9677.5</t>
-  </si>
-  <si>
-    <t>9203</t>
-  </si>
-  <si>
-    <t>9672.5</t>
-  </si>
-  <si>
-    <t>109336</t>
-  </si>
-  <si>
-    <t>109725</t>
-  </si>
-  <si>
-    <t>109321</t>
-  </si>
-  <si>
-    <t>109720</t>
-  </si>
-  <si>
-    <t>62948</t>
-  </si>
-  <si>
-    <t>49046</t>
-  </si>
-  <si>
-    <t>49031</t>
-  </si>
-  <si>
-    <t>62933</t>
+    <t>SO100/05697/25-26</t>
+  </si>
+  <si>
+    <t>VJ-PROJECT</t>
   </si>
 </sst>
 </file>
@@ -908,7 +673,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -975,6 +740,12 @@
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1061,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1315,35 +1086,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1653,76 +1409,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="29" width="26.85546875"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="26.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1769,10 +1525,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2041,8 +1797,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>259</v>
+      <c r="AG5" s="36" t="s">
+        <v>168</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2170,8 +1926,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>260</v>
+      <c r="AG6" s="36" t="s">
+        <v>169</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2241,76 +1997,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -2357,10 +2113,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2626,7 +2382,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2750,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2815,77 +2571,77 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="80"/>
       <c r="AD1" s="80"/>
       <c r="AE1" s="80"/>
@@ -2932,10 +2688,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="79"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -3205,7 +2961,7 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
+      <c r="AG5" s="36" t="s">
         <v>142</v>
       </c>
       <c r="AH5" s="34">
@@ -3278,77 +3034,77 @@
   <dimension ref="A1:AM13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="18.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="86"/>
       <c r="AD1" s="86"/>
       <c r="AE1" s="86"/>
@@ -3395,10 +3151,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="85"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3668,8 +3424,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>246</v>
+      <c r="AG5" s="36" t="s">
+        <v>167</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3906,77 +3662,77 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="88"/>
       <c r="AD1" s="88"/>
       <c r="AE1" s="88"/>
@@ -4023,10 +3779,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="87"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4296,8 +4052,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>219</v>
+      <c r="AG5" s="36" t="s">
+        <v>165</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4369,77 +4125,77 @@
   <dimension ref="A1:AM36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="93"/>
       <c r="AD1" s="93"/>
       <c r="AE1" s="93"/>
@@ -4486,10 +4242,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="92"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -6699,81 +6455,81 @@
   <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="28" width="36.0"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="41" customWidth="true" style="29" width="14.140625"/>
-    <col min="42" max="42" customWidth="true" style="29" width="15.0"/>
-    <col min="43" max="43" customWidth="true" style="29" width="16.5703125"/>
-    <col min="44" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="36" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
+    <col min="41" max="41" width="14.140625" style="29" customWidth="1"/>
+    <col min="42" max="42" width="15" style="29" customWidth="1"/>
+    <col min="43" max="43" width="16.5703125" style="29" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -6820,10 +6576,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -7107,8 +6863,8 @@
         <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>278</v>
+      <c r="AG5" s="36" t="s">
+        <v>180</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -7135,7 +6891,7 @@
         <v>127</v>
       </c>
       <c r="AO5" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7196,76 +6952,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -7312,10 +7068,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -7580,8 +7336,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>214</v>
+      <c r="AG5" s="36" t="s">
+        <v>160</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -7646,76 +7402,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7762,10 +7518,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8030,8 +7786,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>215</v>
+      <c r="AG5" s="36" t="s">
+        <v>161</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8096,76 +7852,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -8212,10 +7968,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8480,8 +8236,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>216</v>
+      <c r="AG5" s="36" t="s">
+        <v>162</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8546,76 +8302,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -8662,10 +8418,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8930,8 +8686,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>217</v>
+      <c r="AG5" s="36" t="s">
+        <v>163</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8996,77 +8752,77 @@
   <dimension ref="A1:AM7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="39"/>
       <c r="AE1" s="39"/>
@@ -9113,10 +8869,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="38"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -9388,8 +9144,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>275</v>
+      <c r="AG5" s="36" t="s">
+        <v>178</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9522,7 +9278,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -9596,76 +9352,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9712,10 +9468,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -10043,76 +9799,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -10159,10 +9915,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -10502,75 +10258,75 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="15.42578125"/>
-    <col min="38" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.42578125" style="29" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -10617,10 +10373,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:37" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -10885,7 +10641,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -10949,76 +10705,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="65"/>
       <c r="AD1" s="65"/>
       <c r="AE1" s="65"/>
@@ -11065,10 +10821,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="64"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -11335,8 +11091,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>7.5</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>220</v>
+      <c r="AG5" s="36" t="s">
+        <v>166</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -11461,8 +11217,8 @@
         <f t="shared" ref="AF6" si="5">G6/AE6</f>
         <v>15</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>218</v>
+      <c r="AG6" s="36" t="s">
+        <v>164</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -11494,76 +11250,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="69"/>
       <c r="AD1" s="69"/>
       <c r="AE1" s="69"/>
@@ -11610,10 +11366,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="68"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -12045,76 +11801,76 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="71"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
@@ -12161,10 +11917,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -12596,76 +12352,76 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="74"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
@@ -12712,10 +12468,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="73"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -13016,76 +12772,76 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="76"/>
       <c r="AD1" s="76"/>
       <c r="AE1" s="76"/>
@@ -13132,10 +12888,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="75"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13436,76 +13192,76 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="11.7109375"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="78"/>
       <c r="AD1" s="78"/>
       <c r="AE1" s="78"/>
@@ -13552,10 +13308,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="77"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13856,77 +13612,77 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="84"/>
       <c r="AD1" s="84"/>
       <c r="AE1" s="84"/>
@@ -13973,10 +13729,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="83"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -14247,7 +14003,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -14319,76 +14075,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="41"/>
       <c r="AD1" s="41"/>
       <c r="AE1" s="41"/>
@@ -14435,10 +14191,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="40"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -14621,7 +14377,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>58</v>
       </c>
       <c r="I5" s="9">
@@ -14707,8 +14463,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>261</v>
+      <c r="AG5" s="36" t="s">
+        <v>170</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -14750,7 +14506,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>68</v>
       </c>
       <c r="I6" s="9">
@@ -14836,8 +14592,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>262</v>
+      <c r="AG6" s="36" t="s">
+        <v>171</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -14907,77 +14663,77 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
       <c r="AE1" s="82"/>
@@ -15024,10 +14780,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="81"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -15297,8 +15053,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>277</v>
+      <c r="AG5" s="36" t="s">
+        <v>179</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -15367,47 +15123,46 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
+      <c r="A1" s="117" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
     </row>
     <row r="4" spans="1:5" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15416,29 +15171,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="10">
-        <v>2</v>
-      </c>
-      <c r="D5" s="112" t="s">
-        <v>149</v>
+        <v>146</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="10">
+        <v>40</v>
       </c>
       <c r="E5" s="59"/>
-    </row>
-    <row r="6" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="10">
-        <v>3</v>
-      </c>
-      <c r="D6" s="113">
-        <v>45</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15452,47 +15193,46 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
+      <c r="A1" s="117" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
     </row>
     <row r="4" spans="1:5" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15501,29 +15241,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="10">
-        <v>2</v>
-      </c>
-      <c r="D5" s="112" t="s">
-        <v>149</v>
+        <v>146</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="10">
+        <v>30</v>
       </c>
       <c r="E5" s="59"/>
-    </row>
-    <row r="6" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="10">
-        <v>3</v>
-      </c>
-      <c r="D6" s="113">
-        <v>45</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15537,77 +15263,73 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A1" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+    </row>
+    <row r="2" spans="1:6" ht="18">
+      <c r="D2" s="112"/>
+    </row>
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+    </row>
+    <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>147</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4" s="58"/>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>144</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="10">
-        <v>2</v>
-      </c>
-      <c r="D5" s="112" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="59"/>
-    </row>
-    <row r="6" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="10">
-        <v>3</v>
-      </c>
-      <c r="D6" s="113">
-        <v>45</v>
+      <c r="B5" s="114" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -15622,77 +15344,73 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="18.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="37.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A1" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+    </row>
+    <row r="2" spans="1:6" ht="18">
+      <c r="D2" s="112"/>
+    </row>
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+    </row>
+    <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>147</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4" s="58"/>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>144</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="10">
-        <v>2</v>
-      </c>
-      <c r="D5" s="112" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="59"/>
-    </row>
-    <row r="6" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="10">
-        <v>3</v>
-      </c>
-      <c r="D6" s="113">
-        <v>45</v>
+      <c r="B5" s="114" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="114" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -15707,35 +15425,36 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="119"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="118"/>
-    </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A1" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+    </row>
+    <row r="2" spans="1:6" ht="18">
+      <c r="D2" s="112"/>
+    </row>
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+    </row>
+    <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15743,27 +15462,37 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="58"/>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>144</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>161</v>
+      <c r="B5" s="114" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="114" t="s">
+        <v>197</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="59"/>
+        <v>189</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>198</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15776,6 +15505,154 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="D2" s="112"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="D2" s="109"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="108"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -15789,76 +15666,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="44"/>
       <c r="AD1" s="44"/>
       <c r="AE1" s="44"/>
@@ -15905,10 +15782,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="43"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -16178,7 +16055,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16307,7 +16184,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16377,76 +16254,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="46"/>
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
@@ -16493,10 +16370,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="45"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -16679,7 +16556,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>57</v>
       </c>
       <c r="I5" s="9">
@@ -16765,8 +16642,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>265</v>
+      <c r="AG5" s="36" t="s">
+        <v>172</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16808,7 +16685,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>58</v>
       </c>
       <c r="I6" s="9">
@@ -16894,8 +16771,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>266</v>
+      <c r="AG6" s="36" t="s">
+        <v>173</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16965,76 +16842,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
@@ -17081,10 +16958,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="47"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -17354,7 +17231,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17483,7 +17360,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17553,76 +17430,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -17669,10 +17546,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -17855,7 +17732,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>67</v>
       </c>
       <c r="I5" s="9">
@@ -17941,8 +17818,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>269</v>
+      <c r="AG5" s="36" t="s">
+        <v>174</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17984,7 +17861,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>68</v>
       </c>
       <c r="I6" s="9">
@@ -18070,8 +17947,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>270</v>
+      <c r="AG6" s="36" t="s">
+        <v>175</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18141,76 +18018,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -18257,10 +18134,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -18530,7 +18407,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18659,7 +18536,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18729,76 +18606,76 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="29"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="122"/>
-      <c r="AA1" s="122"/>
-      <c r="AB1" s="122"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -18845,10 +18722,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="121"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -19031,7 +18908,7 @@
       <c r="G5" s="33">
         <v>15</v>
       </c>
-      <c r="H5" t="s" s="29">
+      <c r="H5" s="29" t="s">
         <v>75</v>
       </c>
       <c r="I5" s="9">
@@ -19117,8 +18994,8 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>273</v>
+      <c r="AG5" s="36" t="s">
+        <v>176</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -19160,7 +19037,7 @@
       <c r="G6" s="33">
         <v>10</v>
       </c>
-      <c r="H6" t="s" s="29">
+      <c r="H6" s="29" t="s">
         <v>76</v>
       </c>
       <c r="I6" s="9">
@@ -19246,8 +19123,8 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>5</v>
       </c>
-      <c r="AG6" t="s" s="36">
-        <v>274</v>
+      <c r="AG6" s="36" t="s">
+        <v>177</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="32" activeTab="36"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="33" activeTab="36"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -43,8 +43,9 @@
     <sheet name="DirectSCOWithProject" sheetId="45" r:id="rId34"/>
     <sheet name="DirectSCOWithSOandConv" sheetId="44" r:id="rId35"/>
     <sheet name="DirectSCOWithConv" sheetId="42" r:id="rId36"/>
-    <sheet name="DirectSCO" sheetId="39" r:id="rId37"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId38"/>
+    <sheet name="DirectSCOSerial" sheetId="46" r:id="rId37"/>
+    <sheet name="DirectSCO" sheetId="39" r:id="rId38"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId39"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="203">
   <si>
     <t>GST Sales</t>
   </si>
@@ -664,6 +665,15 @@
   </si>
   <si>
     <t>VJ-PROJECT</t>
+  </si>
+  <si>
+    <t>PROC-004</t>
+  </si>
+  <si>
+    <t>VR-SERIAL-FIFO-BATCH-90001</t>
+  </si>
+  <si>
+    <t>Scenario  : Direct SCO Serial With BOM Standard Type</t>
   </si>
 </sst>
 </file>
@@ -832,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1100,6 +1110,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1449,36 +1465,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1525,10 +1541,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2037,36 +2053,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -2113,10 +2129,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2612,36 +2628,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="80"/>
       <c r="AD1" s="80"/>
       <c r="AE1" s="80"/>
@@ -2688,10 +2704,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="79"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -3075,36 +3091,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="86"/>
       <c r="AD1" s="86"/>
       <c r="AE1" s="86"/>
@@ -3151,10 +3167,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="85"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3703,36 +3719,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="88"/>
       <c r="AD1" s="88"/>
       <c r="AE1" s="88"/>
@@ -3779,10 +3795,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="87"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4166,36 +4182,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="93"/>
       <c r="AD1" s="93"/>
       <c r="AE1" s="93"/>
@@ -4242,10 +4258,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="92"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -6500,36 +6516,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -6576,10 +6592,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -6992,36 +7008,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -7068,10 +7084,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -7442,36 +7458,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7518,10 +7534,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -7892,36 +7908,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7968,10 +7984,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8342,36 +8358,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -8418,10 +8434,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8793,36 +8809,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="39"/>
       <c r="AE1" s="39"/>
@@ -8869,10 +8885,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="38"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -9392,36 +9408,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9468,10 +9484,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -9839,36 +9855,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -9915,10 +9931,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -10297,36 +10313,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -10373,10 +10389,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:37" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -10745,36 +10761,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="65"/>
       <c r="AD1" s="65"/>
       <c r="AE1" s="65"/>
@@ -10821,10 +10837,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="64"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -11290,36 +11306,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="69"/>
       <c r="AD1" s="69"/>
       <c r="AE1" s="69"/>
@@ -11366,10 +11382,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="68"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -11841,36 +11857,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="71"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
@@ -11917,10 +11933,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -12392,36 +12408,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="74"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
@@ -12468,10 +12484,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="73"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -12812,36 +12828,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="76"/>
       <c r="AD1" s="76"/>
       <c r="AE1" s="76"/>
@@ -12888,10 +12904,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="75"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13232,36 +13248,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="78"/>
       <c r="AD1" s="78"/>
       <c r="AE1" s="78"/>
@@ -13308,10 +13324,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="77"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13653,36 +13669,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="84"/>
       <c r="AD1" s="84"/>
       <c r="AE1" s="84"/>
@@ -13729,10 +13745,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="83"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -14115,36 +14131,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="41"/>
       <c r="AD1" s="41"/>
       <c r="AE1" s="41"/>
@@ -14191,10 +14207,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="40"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -14704,36 +14720,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
       <c r="AE1" s="82"/>
@@ -14780,10 +14796,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="81"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -15135,19 +15151,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15205,19 +15221,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15276,19 +15292,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15357,19 +15373,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15438,19 +15454,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15518,19 +15534,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15592,21 +15608,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="A1" s="119" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="109"/>
+      <c r="D2" s="117"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="108"/>
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
     </row>
     <row r="4" spans="1:5" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
@@ -15630,13 +15646,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="E5" s="67" t="s">
         <v>191</v>
@@ -15653,6 +15669,80 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="119" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="D2" s="109"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="118"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="108"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -15706,36 +15796,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="44"/>
       <c r="AD1" s="44"/>
       <c r="AE1" s="44"/>
@@ -15782,10 +15872,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="43"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -16294,36 +16384,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="46"/>
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
@@ -16370,10 +16460,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="45"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -16882,36 +16972,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
@@ -16958,10 +17048,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="47"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -17470,36 +17560,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -17546,10 +17636,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -18058,36 +18148,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -18134,10 +18224,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -18646,36 +18736,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -18722,10 +18812,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="116"/>
+      <c r="A3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="33" activeTab="36"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="32" activeTab="36"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,8 @@
     <sheet name="DirectSCOWithProject" sheetId="45" r:id="rId34"/>
     <sheet name="DirectSCOWithSOandConv" sheetId="44" r:id="rId35"/>
     <sheet name="DirectSCOWithConv" sheetId="42" r:id="rId36"/>
-    <sheet name="DirectSCOSerial" sheetId="46" r:id="rId37"/>
-    <sheet name="DirectSCO" sheetId="39" r:id="rId38"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId39"/>
+    <sheet name="DirectSCO" sheetId="39" r:id="rId37"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId38"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -65,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="200">
   <si>
     <t>GST Sales</t>
   </si>
@@ -665,15 +664,6 @@
   </si>
   <si>
     <t>VJ-PROJECT</t>
-  </si>
-  <si>
-    <t>PROC-004</t>
-  </si>
-  <si>
-    <t>VR-SERIAL-FIFO-BATCH-90001</t>
-  </si>
-  <si>
-    <t>Scenario  : Direct SCO Serial With BOM Standard Type</t>
   </si>
 </sst>
 </file>
@@ -842,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1110,12 +1100,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1465,36 +1449,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1541,10 +1525,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2053,36 +2037,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -2129,10 +2113,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2628,36 +2612,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="80"/>
       <c r="AD1" s="80"/>
       <c r="AE1" s="80"/>
@@ -2704,10 +2688,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="79"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -3091,36 +3075,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="86"/>
       <c r="AD1" s="86"/>
       <c r="AE1" s="86"/>
@@ -3167,10 +3151,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="85"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3719,36 +3703,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="88"/>
       <c r="AD1" s="88"/>
       <c r="AE1" s="88"/>
@@ -3795,10 +3779,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="87"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4182,36 +4166,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="93"/>
       <c r="AD1" s="93"/>
       <c r="AE1" s="93"/>
@@ -4258,10 +4242,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="92"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -6516,36 +6500,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -6592,10 +6576,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -7008,36 +6992,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -7084,10 +7068,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -7458,36 +7442,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7534,10 +7518,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -7908,36 +7892,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7984,10 +7968,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8358,36 +8342,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -8434,10 +8418,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8809,36 +8793,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="39"/>
       <c r="AE1" s="39"/>
@@ -8885,10 +8869,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="38"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -9408,36 +9392,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9484,10 +9468,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -9855,36 +9839,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -9931,10 +9915,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -10313,36 +10297,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -10389,10 +10373,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:37" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -10761,36 +10745,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="65"/>
       <c r="AD1" s="65"/>
       <c r="AE1" s="65"/>
@@ -10837,10 +10821,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="64"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -11306,36 +11290,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="69"/>
       <c r="AD1" s="69"/>
       <c r="AE1" s="69"/>
@@ -11382,10 +11366,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="68"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -11857,36 +11841,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="71"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
@@ -11933,10 +11917,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -12408,36 +12392,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="74"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
@@ -12484,10 +12468,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="73"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -12828,36 +12812,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="76"/>
       <c r="AD1" s="76"/>
       <c r="AE1" s="76"/>
@@ -12904,10 +12888,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="75"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13248,36 +13232,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="78"/>
       <c r="AD1" s="78"/>
       <c r="AE1" s="78"/>
@@ -13324,10 +13308,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="77"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13669,36 +13653,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="84"/>
       <c r="AD1" s="84"/>
       <c r="AE1" s="84"/>
@@ -13745,10 +13729,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="83"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -14131,36 +14115,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="41"/>
       <c r="AD1" s="41"/>
       <c r="AE1" s="41"/>
@@ -14207,10 +14191,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="40"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -14720,36 +14704,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
       <c r="AE1" s="82"/>
@@ -14796,10 +14780,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="81"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -15151,19 +15135,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15221,19 +15205,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15292,19 +15276,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15373,19 +15357,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15454,19 +15438,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15534,19 +15518,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15608,21 +15592,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="117"/>
+      <c r="D2" s="109"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="108"/>
     </row>
     <row r="4" spans="1:5" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
@@ -15646,13 +15630,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E5" s="67" t="s">
         <v>191</v>
@@ -15669,80 +15653,6 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="109"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="108"/>
-    </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
-      <c r="A4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="113" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="10">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="67" t="s">
-        <v>191</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:B3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -15796,36 +15706,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="44"/>
       <c r="AD1" s="44"/>
       <c r="AE1" s="44"/>
@@ -15872,10 +15782,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="43"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -16384,36 +16294,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="46"/>
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
@@ -16460,10 +16370,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="45"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -16972,36 +16882,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
@@ -17048,10 +16958,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="47"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -17560,36 +17470,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -17636,10 +17546,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -18148,36 +18058,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -18224,10 +18134,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -18736,36 +18646,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -18812,10 +18722,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="33" activeTab="36"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="31" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -41,11 +41,12 @@
     <sheet name="OpenSCO" sheetId="40" r:id="rId32"/>
     <sheet name="DirectSCOWithSO" sheetId="43" r:id="rId33"/>
     <sheet name="DirectSCOWithProject" sheetId="45" r:id="rId34"/>
-    <sheet name="DirectSCOWithSOandConv" sheetId="44" r:id="rId35"/>
-    <sheet name="DirectSCOWithConv" sheetId="42" r:id="rId36"/>
-    <sheet name="DirectSCOSerial" sheetId="46" r:id="rId37"/>
-    <sheet name="DirectSCO" sheetId="39" r:id="rId38"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId39"/>
+    <sheet name="DirectSCOSerialWithSO" sheetId="47" r:id="rId35"/>
+    <sheet name="DirectSCOWithSOandConv" sheetId="44" r:id="rId36"/>
+    <sheet name="DirectSCOWithConv" sheetId="42" r:id="rId37"/>
+    <sheet name="DirectSCOSerial" sheetId="46" r:id="rId38"/>
+    <sheet name="DirectSCO" sheetId="39" r:id="rId39"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId40"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="204">
   <si>
     <t>GST Sales</t>
   </si>
@@ -196,12 +197,6 @@
     <t>Sales Amt (BC)</t>
   </si>
   <si>
-    <t>NUYI-9090</t>
-  </si>
-  <si>
-    <t>TVSFG004</t>
-  </si>
-  <si>
     <t>Sales GL Acct</t>
   </si>
   <si>
@@ -674,6 +669,15 @@
   </si>
   <si>
     <t>Scenario  : Direct SCO Serial With BOM Standard Type</t>
+  </si>
+  <si>
+    <t>FG50011</t>
+  </si>
+  <si>
+    <t>SO100/05832/25-26</t>
+  </si>
+  <si>
+    <t>FG40001-SERIAL-SO</t>
   </si>
 </sst>
 </file>
@@ -842,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1110,6 +1114,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1465,36 +1475,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1503,10 +1513,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1541,10 +1551,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -1696,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -1710,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -1814,7 +1824,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -1839,13 +1849,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -1943,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -1956,7 +1966,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -2053,36 +2063,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -2091,10 +2101,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="52"/>
       <c r="D2" s="52"/>
@@ -2129,10 +2139,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2284,7 +2294,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
@@ -2294,13 +2304,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2312,7 +2322,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -2398,7 +2408,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2418,13 +2428,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -2436,7 +2446,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -2522,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2628,36 +2638,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="80"/>
       <c r="AD1" s="80"/>
       <c r="AE1" s="80"/>
@@ -2666,10 +2676,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="80"/>
       <c r="D2" s="80"/>
@@ -2704,10 +2714,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="79"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -2859,13 +2869,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -2874,13 +2884,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2978,7 +2988,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3091,36 +3101,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="86"/>
       <c r="AD1" s="86"/>
       <c r="AE1" s="86"/>
@@ -3129,10 +3139,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="86"/>
       <c r="D2" s="86"/>
@@ -3167,10 +3177,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="85"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3322,13 +3332,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -3337,13 +3347,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3441,7 +3451,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3500,7 +3510,7 @@
     </row>
     <row r="9" spans="1:39">
       <c r="C9" s="89" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
@@ -3517,7 +3527,7 @@
     </row>
     <row r="10" spans="1:39">
       <c r="C10" s="90" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>6</v>
@@ -3526,19 +3536,19 @@
         <v>7</v>
       </c>
       <c r="F10" s="90" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="90" t="s">
+      <c r="I10" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="90" t="s">
+      <c r="J10" s="90" t="s">
         <v>107</v>
-      </c>
-      <c r="I10" s="90" t="s">
-        <v>108</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>109</v>
       </c>
       <c r="K10" s="90" t="s">
         <v>26</v>
@@ -3561,16 +3571,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="H11" s="10">
         <v>20</v>
@@ -3602,16 +3612,16 @@
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
@@ -3643,7 +3653,7 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I13" s="10">
         <v>21477.41</v>
@@ -3719,36 +3729,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="88"/>
       <c r="AD1" s="88"/>
       <c r="AE1" s="88"/>
@@ -3757,10 +3767,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="88"/>
       <c r="D2" s="88"/>
@@ -3795,10 +3805,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="87"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3950,13 +3960,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -3965,13 +3975,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4069,7 +4079,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4182,36 +4192,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="93"/>
       <c r="AD1" s="93"/>
       <c r="AE1" s="93"/>
@@ -4220,10 +4230,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
@@ -4258,10 +4268,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="92"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4413,13 +4423,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -4428,13 +4438,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4532,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4559,13 +4569,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="97" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="97" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -4663,7 +4673,7 @@
         <v>16</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
@@ -4689,13 +4699,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="97" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
       </c>
       <c r="D7" s="97" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -4793,7 +4803,7 @@
         <v>17</v>
       </c>
       <c r="AG7" s="36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH7" s="34">
         <f t="shared" ref="AH7:AH14" si="20">AG7-AF7</f>
@@ -4819,13 +4829,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="97" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="97" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>32</v>
@@ -4923,7 +4933,7 @@
         <v>18</v>
       </c>
       <c r="AG8" s="36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AH8" s="34">
         <f t="shared" si="20"/>
@@ -4949,13 +4959,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="97" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
       </c>
       <c r="D9" s="97" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>32</v>
@@ -5053,7 +5063,7 @@
         <v>19</v>
       </c>
       <c r="AG9" s="36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AH9" s="34">
         <f t="shared" si="20"/>
@@ -5079,13 +5089,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>32</v>
@@ -5183,7 +5193,7 @@
         <v>20</v>
       </c>
       <c r="AG10" s="36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AH10" s="34">
         <f t="shared" si="20"/>
@@ -5209,13 +5219,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
       </c>
       <c r="D11" s="97" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>32</v>
@@ -5313,7 +5323,7 @@
         <v>21</v>
       </c>
       <c r="AG11" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AH11" s="34">
         <f t="shared" si="20"/>
@@ -5339,13 +5349,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="99">
         <v>0</v>
       </c>
       <c r="D12" s="100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E12" s="99" t="s">
         <v>32</v>
@@ -5443,7 +5453,7 @@
         <v>22</v>
       </c>
       <c r="AG12" s="36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AH12" s="102">
         <f t="shared" si="20"/>
@@ -5469,13 +5479,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>32</v>
@@ -5573,7 +5583,7 @@
         <v>23</v>
       </c>
       <c r="AG13" s="36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AH13" s="34">
         <f t="shared" si="20"/>
@@ -5599,13 +5609,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="97" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>32</v>
@@ -5703,7 +5713,7 @@
         <v>24</v>
       </c>
       <c r="AG14" s="36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AH14" s="34">
         <f t="shared" si="20"/>
@@ -6516,36 +6526,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -6554,10 +6564,10 @@
     </row>
     <row r="2" spans="1:43" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="54"/>
@@ -6592,10 +6602,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -6747,28 +6757,28 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN4" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO4" s="98" t="s">
+        <v>127</v>
+      </c>
+      <c r="AP4" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="AN4" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="AO4" s="98" t="s">
+      <c r="AQ4" s="98" t="s">
         <v>129</v>
-      </c>
-      <c r="AP4" s="98" t="s">
-        <v>130</v>
-      </c>
-      <c r="AQ4" s="98" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="15">
@@ -6776,13 +6786,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -6880,7 +6890,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -6901,13 +6911,13 @@
         <v>63108</v>
       </c>
       <c r="AM5" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN5" s="67" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AO5" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7008,36 +7018,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -7046,10 +7056,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="54"/>
@@ -7084,10 +7094,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -7239,7 +7249,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
@@ -7249,13 +7259,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7353,7 +7363,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -7458,36 +7468,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7496,10 +7506,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
@@ -7534,10 +7544,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -7689,7 +7699,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
@@ -7699,13 +7709,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7803,7 +7813,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -7908,36 +7918,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7946,10 +7956,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
@@ -7984,10 +7994,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8139,7 +8149,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
@@ -8149,13 +8159,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8253,7 +8263,7 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8358,36 +8368,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -8396,10 +8406,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
@@ -8434,10 +8444,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8589,7 +8599,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
@@ -8599,13 +8609,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8703,14 +8713,14 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -8809,36 +8819,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="39"/>
       <c r="AE1" s="39"/>
@@ -8847,10 +8857,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="39"/>
       <c r="D2" s="39"/>
@@ -8885,10 +8895,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="38"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -9040,7 +9050,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -9049,7 +9059,7 @@
         <v>36</v>
       </c>
       <c r="AM4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:39" ht="15">
@@ -9057,13 +9067,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9161,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9174,7 +9184,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -9190,13 +9200,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -9294,7 +9304,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -9307,7 +9317,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -9408,36 +9418,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9446,10 +9456,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
@@ -9484,10 +9494,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -9639,7 +9649,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
@@ -9649,13 +9659,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9757,7 +9767,7 @@
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -9855,36 +9865,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -9893,10 +9903,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -9931,10 +9941,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -10086,13 +10096,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -10100,13 +10110,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10164,7 +10174,7 @@
         <v>600</v>
       </c>
       <c r="V5" s="33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W5" s="22">
         <v>0.12</v>
@@ -10204,7 +10214,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -10313,36 +10323,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -10351,10 +10361,10 @@
     </row>
     <row r="2" spans="1:37" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -10389,10 +10399,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:37" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -10544,7 +10554,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="58"/>
     </row>
@@ -10553,13 +10563,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10657,7 +10667,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -10761,36 +10771,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="65"/>
       <c r="AD1" s="65"/>
       <c r="AE1" s="65"/>
@@ -10799,10 +10809,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="65"/>
       <c r="D2" s="65"/>
@@ -10837,10 +10847,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="64"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -10992,10 +11002,10 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AL4" s="58"/>
     </row>
@@ -11004,13 +11014,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11108,7 +11118,7 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -11121,7 +11131,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AL5" s="59"/>
     </row>
@@ -11130,13 +11140,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -11234,7 +11244,7 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -11247,7 +11257,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AL6" s="59"/>
     </row>
@@ -11306,36 +11316,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="69"/>
       <c r="AD1" s="69"/>
       <c r="AE1" s="69"/>
@@ -11344,10 +11354,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="69"/>
       <c r="D2" s="69"/>
@@ -11382,10 +11392,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="68"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -11537,13 +11547,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL4" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="AL4" s="19" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -11551,13 +11561,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11655,7 +11665,7 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -11668,10 +11678,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -11679,13 +11689,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -11783,7 +11793,7 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
@@ -11796,10 +11806,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL6" s="66" t="s">
         <v>93</v>
-      </c>
-      <c r="AL6" s="66" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -11857,36 +11867,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="71"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
@@ -11895,10 +11905,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
@@ -11933,10 +11943,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -12088,13 +12098,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL4" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="AL4" s="19" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -12102,13 +12112,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -12206,7 +12216,7 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -12219,10 +12229,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -12230,13 +12240,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12334,7 +12344,7 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
@@ -12347,10 +12357,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL6" s="66" t="s">
         <v>93</v>
-      </c>
-      <c r="AL6" s="66" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -12408,36 +12418,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="74"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
@@ -12446,10 +12456,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="74"/>
       <c r="D2" s="74"/>
@@ -12484,10 +12494,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="73"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -12639,13 +12649,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -12653,13 +12663,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -12767,10 +12777,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -12828,36 +12838,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="76"/>
       <c r="AD1" s="76"/>
       <c r="AE1" s="76"/>
@@ -12866,10 +12876,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="76"/>
       <c r="D2" s="76"/>
@@ -12904,10 +12914,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="75"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13059,13 +13069,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -13073,13 +13083,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -13187,10 +13197,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -13248,36 +13258,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="78"/>
       <c r="AD1" s="78"/>
       <c r="AE1" s="78"/>
@@ -13286,10 +13296,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
@@ -13324,10 +13334,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="77"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13479,13 +13489,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -13493,13 +13503,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -13607,10 +13617,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -13669,36 +13679,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="84"/>
       <c r="AD1" s="84"/>
       <c r="AE1" s="84"/>
@@ -13707,10 +13717,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="84"/>
@@ -13745,10 +13755,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="83"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13900,13 +13910,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -13915,13 +13925,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -14019,14 +14029,14 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>49586</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -14131,36 +14141,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="41"/>
       <c r="AD1" s="41"/>
       <c r="AE1" s="41"/>
@@ -14169,10 +14179,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
@@ -14207,10 +14217,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="40"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -14362,7 +14372,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -14376,13 +14386,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -14394,7 +14404,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -14480,7 +14490,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -14493,7 +14503,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -14505,13 +14515,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -14523,7 +14533,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -14609,7 +14619,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -14622,7 +14632,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -14720,36 +14730,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
       <c r="AE1" s="82"/>
@@ -14758,10 +14768,10 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="82"/>
       <c r="D2" s="82"/>
@@ -14796,10 +14806,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="81"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -14951,13 +14961,13 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -14966,13 +14976,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15070,14 +15080,14 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AJ5" s="10">
         <v>4010101001</v>
@@ -15151,19 +15161,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15172,13 +15182,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15187,10 +15197,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D5" s="10">
         <v>40</v>
@@ -15221,19 +15231,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15242,13 +15252,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15257,10 +15267,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D5" s="10">
         <v>30</v>
@@ -15292,19 +15302,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15316,16 +15326,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -15333,19 +15343,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -15373,19 +15383,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15397,16 +15407,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -15414,19 +15424,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" s="114" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -15454,21 +15464,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:6" ht="18">
-      <c r="D2" s="112"/>
+      <c r="D2" s="119"/>
     </row>
     <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
     </row>
     <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
@@ -15478,16 +15488,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -15495,19 +15505,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>191</v>
-      </c>
       <c r="F5" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -15522,7 +15532,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15530,27 +15540,28 @@
     <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1">
+      <c r="A1" s="121" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+    </row>
+    <row r="2" spans="1:6" ht="18">
       <c r="D2" s="112"/>
     </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
+    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15558,30 +15569,36 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>188</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>62</v>
+      <c r="B5" s="114" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="114" t="s">
+        <v>195</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>191</v>
+      <c r="F5" s="10" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -15608,21 +15625,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="117"/>
+      <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
     </row>
     <row r="4" spans="1:5" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
@@ -15632,13 +15649,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
@@ -15646,16 +15663,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -15682,21 +15699,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="A1" s="121" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="109"/>
+      <c r="D2" s="117"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="108"/>
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
     </row>
     <row r="4" spans="1:5" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
@@ -15706,13 +15723,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
@@ -15720,16 +15737,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>146</v>
+        <v>199</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -15744,10 +15761,75 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A1" s="121" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+    </row>
+    <row r="2" spans="1:5" ht="18">
+      <c r="D2" s="109"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="120"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="108"/>
+    </row>
+    <row r="4" spans="1:5" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15796,36 +15878,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="44"/>
       <c r="AD1" s="44"/>
       <c r="AE1" s="44"/>
@@ -15834,10 +15916,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
@@ -15872,10 +15954,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="43"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -16027,7 +16109,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -16041,13 +16123,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -16059,7 +16141,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -16145,7 +16227,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16158,7 +16240,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -16170,13 +16252,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -16188,7 +16270,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -16274,7 +16356,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16287,7 +16369,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -16336,6 +16418,15 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -16384,36 +16475,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="46"/>
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
@@ -16422,10 +16513,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="46"/>
       <c r="D2" s="46"/>
@@ -16460,10 +16551,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="45"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -16615,7 +16706,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -16629,13 +16720,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -16647,7 +16738,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -16733,7 +16824,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16746,7 +16837,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -16758,13 +16849,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -16776,7 +16867,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -16862,7 +16953,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16875,7 +16966,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -16972,36 +17063,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
@@ -17010,10 +17101,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -17048,10 +17139,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="47"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -17203,7 +17294,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -17217,13 +17308,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -17235,7 +17326,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17321,7 +17412,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17334,7 +17425,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -17346,13 +17437,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -17364,7 +17455,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -17450,7 +17541,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17463,7 +17554,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -17560,36 +17651,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -17598,10 +17689,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
@@ -17636,10 +17727,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -17791,7 +17882,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -17805,13 +17896,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -17823,7 +17914,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17909,7 +18000,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17922,7 +18013,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -17934,13 +18025,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -17952,7 +18043,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -18038,7 +18129,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18051,7 +18142,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -18148,36 +18239,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -18186,10 +18277,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
@@ -18224,10 +18315,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -18379,7 +18470,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -18393,13 +18484,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -18411,7 +18502,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -18497,7 +18588,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18510,7 +18601,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -18522,13 +18613,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -18540,7 +18631,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -18626,7 +18717,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18639,7 +18730,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>
@@ -18736,36 +18827,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -18774,10 +18865,10 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="52"/>
       <c r="D2" s="52"/>
@@ -18812,10 +18903,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="120"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -18967,7 +19058,7 @@
         <v>37</v>
       </c>
       <c r="AJ4" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
         <v>35</v>
@@ -18981,13 +19072,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -18999,7 +19090,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -19085,7 +19176,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -19098,7 +19189,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL5" s="33">
         <f>AK5+G5</f>
@@ -19110,13 +19201,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -19128,7 +19219,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -19214,7 +19305,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -19227,7 +19318,7 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL6" s="33">
         <f>AK6+G6</f>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="31" activeTab="34"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="39" activeTab="40"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,13 @@
     <sheet name="DirectSCOSerialWithSO" sheetId="47" r:id="rId35"/>
     <sheet name="DirectSCOWithSOandConv" sheetId="44" r:id="rId36"/>
     <sheet name="DirectSCOWithConv" sheetId="42" r:id="rId37"/>
-    <sheet name="DirectSCOSerial" sheetId="46" r:id="rId38"/>
-    <sheet name="DirectSCO" sheetId="39" r:id="rId39"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId40"/>
+    <sheet name="DirectSCOSerialWithPrj" sheetId="48" r:id="rId38"/>
+    <sheet name="DirectSCOSerial" sheetId="46" r:id="rId39"/>
+    <sheet name="ProcCalculationLocalUnreg" sheetId="52" r:id="rId40"/>
+    <sheet name="ProcCalculationInterstateUnreg" sheetId="54" r:id="rId41"/>
+    <sheet name="ProcCalculationInterstateReg" sheetId="53" r:id="rId42"/>
+    <sheet name="ProcCalculationLocalReg" sheetId="51" r:id="rId43"/>
+    <sheet name="DirectSCO" sheetId="39" r:id="rId44"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -66,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="224">
   <si>
     <t>GST Sales</t>
   </si>
@@ -506,9 +510,6 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>19252.5</t>
   </si>
   <si>
@@ -678,14 +679,78 @@
   </si>
   <si>
     <t>FG40001-SERIAL-SO</t>
+  </si>
+  <si>
+    <t>Scenario  : Direct SCO Serial With BOM Standard Type With Project</t>
+  </si>
+  <si>
+    <t>FRYING</t>
+  </si>
+  <si>
+    <t>ConvFact</t>
+  </si>
+  <si>
+    <t>ProcQty</t>
+  </si>
+  <si>
+    <t>LineUnitCost</t>
+  </si>
+  <si>
+    <t>AsblVal</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>IGSTAmt</t>
+  </si>
+  <si>
+    <t>ContrPfx</t>
+  </si>
+  <si>
+    <t>ContrNo</t>
+  </si>
+  <si>
+    <t>OOS10</t>
+  </si>
+  <si>
+    <t>OOS10/00031/25-26</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>KGS</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>(1 - Registered, 2 - Unregistered)</t>
+  </si>
+  <si>
+    <t>Scenario  : Subcontract Process Calculation Local(Registered)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Scenario  : Subcontract Process Calculation Interstate(UnRegistered)</t>
+  </si>
+  <si>
+    <t>Scenario  : Subcontract Process Calculation Interstate(Registered)</t>
+  </si>
+  <si>
+    <t>Scenario  : Subcontract Process Calculation Local(UnRegistered)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -762,7 +827,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -802,6 +867,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -846,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1127,6 +1198,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1475,36 +1577,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1551,10 +1653,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -1720,13 +1822,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -1824,7 +1926,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -1953,7 +2055,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2063,36 +2165,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -2139,10 +2241,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -2408,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2532,7 +2634,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -2638,36 +2740,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="80"/>
       <c r="AD1" s="80"/>
       <c r="AE1" s="80"/>
@@ -2714,10 +2816,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="79"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -3101,36 +3203,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="86"/>
       <c r="AD1" s="86"/>
       <c r="AE1" s="86"/>
@@ -3177,10 +3279,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="85"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -3347,13 +3449,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3451,7 +3553,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -3729,36 +3831,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="88"/>
       <c r="AD1" s="88"/>
       <c r="AE1" s="88"/>
@@ -3805,10 +3907,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="87"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4079,7 +4181,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -4192,36 +4294,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="93"/>
       <c r="AD1" s="93"/>
       <c r="AE1" s="93"/>
@@ -4268,10 +4370,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="92"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -4438,13 +4540,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -6526,36 +6628,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -6602,10 +6704,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -6786,13 +6888,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -6890,7 +6992,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -7018,36 +7120,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="54"/>
       <c r="AD1" s="54"/>
       <c r="AE1" s="54"/>
@@ -7094,10 +7196,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="53"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -7259,13 +7361,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7363,7 +7465,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -7468,36 +7570,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7544,10 +7646,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -7709,13 +7811,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7813,7 +7915,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -7918,36 +8020,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -7994,10 +8096,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8159,13 +8261,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8263,7 +8365,7 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8368,36 +8470,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -8444,10 +8546,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -8713,7 +8815,7 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -8819,36 +8921,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="39"/>
       <c r="AD1" s="39"/>
       <c r="AE1" s="39"/>
@@ -8895,10 +8997,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="38"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -9067,13 +9169,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9171,7 +9273,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -9304,7 +9406,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -9418,36 +9520,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="56"/>
       <c r="AD1" s="56"/>
       <c r="AE1" s="56"/>
@@ -9494,10 +9596,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="55"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -9865,36 +9967,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -9941,10 +10043,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -10110,13 +10212,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10323,36 +10425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="62"/>
       <c r="AD1" s="62"/>
       <c r="AE1" s="62"/>
@@ -10399,10 +10501,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:37" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="61"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -10563,13 +10665,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10667,7 +10769,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -10771,36 +10873,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="65"/>
       <c r="AD1" s="65"/>
       <c r="AE1" s="65"/>
@@ -10847,10 +10949,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="64"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -11118,7 +11220,7 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -11140,13 +11242,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -11244,7 +11346,7 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -11316,36 +11418,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="69"/>
       <c r="AD1" s="69"/>
       <c r="AE1" s="69"/>
@@ -11392,10 +11494,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="68"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -11689,13 +11791,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -11867,36 +11969,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="71"/>
       <c r="AD1" s="71"/>
       <c r="AE1" s="71"/>
@@ -11943,10 +12045,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -12240,13 +12342,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12418,36 +12520,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="74"/>
       <c r="AD1" s="74"/>
       <c r="AE1" s="74"/>
@@ -12494,10 +12596,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="73"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -12838,36 +12940,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="76"/>
       <c r="AD1" s="76"/>
       <c r="AE1" s="76"/>
@@ -12914,10 +13016,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="75"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13258,36 +13360,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="78"/>
       <c r="AD1" s="78"/>
       <c r="AE1" s="78"/>
@@ -13334,10 +13436,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="77"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13679,36 +13781,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="84"/>
       <c r="AD1" s="84"/>
       <c r="AE1" s="84"/>
@@ -13755,10 +13857,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="83"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -13925,13 +14027,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -14029,7 +14131,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -14141,36 +14243,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="41"/>
       <c r="AD1" s="41"/>
       <c r="AE1" s="41"/>
@@ -14217,10 +14319,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="40"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -14490,7 +14592,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -14619,7 +14721,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -14730,36 +14832,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
       <c r="AE1" s="82"/>
@@ -14806,10 +14908,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:39" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="81"/>
       <c r="D3" s="3">
         <v>1</v>
@@ -14976,13 +15078,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15080,7 +15182,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
@@ -15161,19 +15263,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
+      <c r="A1" s="134" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15185,10 +15287,10 @@
         <v>142</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15200,7 +15302,7 @@
         <v>144</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D5" s="10">
         <v>40</v>
@@ -15231,19 +15333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
+      <c r="A1" s="134" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
@@ -15255,10 +15357,10 @@
         <v>142</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15270,7 +15372,7 @@
         <v>144</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="10">
         <v>30</v>
@@ -15289,7 +15391,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15298,27 +15400,31 @@
     <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="29"/>
+    <col min="7" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="9.140625" style="29"/>
+    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:6" ht="18">
+    <row r="1" spans="1:16" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:16" ht="18">
       <c r="D2" s="112"/>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+    <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
-    <row r="4" spans="1:6" s="31" customFormat="1">
+    <row r="4" spans="1:16" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15332,31 +15438,101 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="115" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>193</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>7.5</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>262.5</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>47.25</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="D12" s="115"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="D13" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15370,7 +15546,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15378,28 +15554,30 @@
     <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="29"/>
+    <col min="6" max="6" width="12" style="29" customWidth="1"/>
+    <col min="7" max="15" width="9.140625" style="29"/>
+    <col min="16" max="16" width="12.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:6" ht="18">
+    <row r="1" spans="1:16" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:16" ht="18">
       <c r="D2" s="112"/>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+    <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
-    <row r="4" spans="1:6" s="31" customFormat="1">
+    <row r="4" spans="1:16" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15413,31 +15591,101 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="115" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>197</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>12.5</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>437.5</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>78.75</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="D11" s="115"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="D12" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15451,7 +15699,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15459,28 +15707,32 @@
     <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="29"/>
+    <col min="6" max="6" width="11.5703125" style="29" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="9.140625" style="29"/>
+    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:6" ht="18">
+    <row r="1" spans="1:16" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:16" ht="18">
       <c r="D2" s="119"/>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+    <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="118"/>
       <c r="D3" s="118"/>
     </row>
-    <row r="4" spans="1:6" s="31" customFormat="1">
+    <row r="4" spans="1:16" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15494,31 +15746,101 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="115" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>202</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>12.5</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>437.5</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>78.75</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="D12" s="115"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="D13" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15532,7 +15854,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15540,28 +15862,32 @@
     <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="29"/>
+    <col min="6" max="6" width="13.140625" style="29" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="11.140625" style="29" customWidth="1"/>
+    <col min="11" max="15" width="9.140625" style="29"/>
+    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:6" ht="18">
+    <row r="1" spans="1:16" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:16" ht="18">
       <c r="D2" s="112"/>
     </row>
-    <row r="3" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+    <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
-    <row r="4" spans="1:6" s="31" customFormat="1">
+    <row r="4" spans="1:16" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15575,31 +15901,101 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="115" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="114" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="D5" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10">
+        <v>2</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>25</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>35</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>875</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>157.5</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
+      </c>
+      <c r="P5" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>196</v>
-      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="D11" s="115"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="D12" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15613,7 +16009,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15624,24 +16020,24 @@
     <col min="6" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="1" spans="1:15" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:15" ht="18">
       <c r="D2" s="112"/>
     </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
+    <row r="3" spans="1:15" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
     </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="4" spans="1:15" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15655,24 +16051,88 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>187</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>50</v>
+      </c>
+      <c r="H5" s="10">
+        <v>2</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>15</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>50</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>750</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>135</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
       </c>
     </row>
   </sheetData>
@@ -15687,35 +16147,40 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="6" max="6" width="12.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="11.7109375" style="29" customWidth="1"/>
+    <col min="11" max="15" width="9.140625" style="29"/>
+    <col min="16" max="16" width="12.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="117"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-    </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="1" spans="1:16" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:16" ht="18">
+      <c r="D2" s="121"/>
+    </row>
+    <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+    </row>
+    <row r="4" spans="1:16" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15729,25 +16194,101 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>187</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="115" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>189</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>7.5</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>262.5</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>47.25</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="D14" s="125"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="D15" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15761,7 +16302,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
@@ -15769,27 +16310,29 @@
     <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="6" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="11" style="29" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-    </row>
-    <row r="2" spans="1:5" ht="18">
-      <c r="D2" s="109"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="108"/>
-    </row>
-    <row r="4" spans="1:5" s="31" customFormat="1">
+    <row r="1" spans="1:15" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:15" ht="18">
+      <c r="D2" s="117"/>
+    </row>
+    <row r="3" spans="1:15" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+    </row>
+    <row r="4" spans="1:15" s="31" customFormat="1">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15803,24 +16346,88 @@
         <v>142</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+        <v>187</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>7.5</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>262.5</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>47.25</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
       </c>
     </row>
   </sheetData>
@@ -15878,36 +16485,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="44"/>
       <c r="AD1" s="44"/>
       <c r="AE1" s="44"/>
@@ -15954,10 +16561,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="43"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -16227,7 +16834,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16356,7 +16963,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -16423,10 +17030,1528 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:AL6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="27"/>
+    </row>
+    <row r="2" spans="1:38" ht="18">
+      <c r="A2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="27"/>
+    </row>
+    <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="30"/>
+    </row>
+    <row r="4" spans="1:38" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="130" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="130" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="131" t="s">
+        <v>215</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="58"/>
+    </row>
+    <row r="5" spans="1:38" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="10">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="29">
+        <v>2</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>10</v>
+      </c>
+      <c r="J5" s="10">
+        <f>I5*(G5/C5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>250</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="33">
+        <v>88363222</v>
+      </c>
+      <c r="N5" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="O5" s="132">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>22.5</v>
+      </c>
+      <c r="P5" s="132">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>22.5</v>
+      </c>
+      <c r="Q5" s="33">
+        <f>IF($D$3=2,ROUND((K5*N5),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="33">
+        <f>O5+P5+Q5</f>
+        <v>45</v>
+      </c>
+      <c r="S5" s="33">
+        <f>IF($J$3=1, K5+R5, K5)</f>
+        <v>250</v>
+      </c>
+      <c r="T5" s="59"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AL5" s="29"/>
+    </row>
+    <row r="6" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AL6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="27"/>
+    </row>
+    <row r="2" spans="1:38" ht="18">
+      <c r="A2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="27"/>
+    </row>
+    <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="30"/>
+    </row>
+    <row r="4" spans="1:38" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="130" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="130" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="131" t="s">
+        <v>215</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="58"/>
+    </row>
+    <row r="5" spans="1:38" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>10</v>
+      </c>
+      <c r="J5" s="10">
+        <f>I5*(G5/C5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>250</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="33">
+        <v>88363222</v>
+      </c>
+      <c r="N5" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="O5" s="33">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="33">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="33">
+        <f>IF($D$3=2,ROUND((K5*N5),2),0)</f>
+        <v>45</v>
+      </c>
+      <c r="R5" s="33">
+        <f>O5+P5+Q5</f>
+        <v>45</v>
+      </c>
+      <c r="S5" s="33">
+        <f>IF($J$3=1, K5+R5, K5)</f>
+        <v>250</v>
+      </c>
+      <c r="T5" s="59"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AL5" s="29"/>
+    </row>
+    <row r="6" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AL6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="27"/>
+    </row>
+    <row r="2" spans="1:38" ht="18">
+      <c r="A2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="27"/>
+    </row>
+    <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="30"/>
+    </row>
+    <row r="4" spans="1:38" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="130" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="130" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="131" t="s">
+        <v>215</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="58"/>
+    </row>
+    <row r="5" spans="1:38" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="10">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="29">
+        <v>2</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>10</v>
+      </c>
+      <c r="J5" s="10">
+        <f>I5*(G5/C5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>250</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="33">
+        <v>88363222</v>
+      </c>
+      <c r="N5" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="O5" s="33">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="33">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="33">
+        <f>IF($D$3=2,ROUND((K5*N5),2),0)</f>
+        <v>45</v>
+      </c>
+      <c r="R5" s="33">
+        <f>O5+P5+Q5</f>
+        <v>45</v>
+      </c>
+      <c r="S5" s="33">
+        <f>IF($J$3=1, K5+R5, K5)</f>
+        <v>295</v>
+      </c>
+      <c r="T5" s="59"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AL5" s="29"/>
+    </row>
+    <row r="6" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AL6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="27"/>
+    </row>
+    <row r="2" spans="1:38" ht="18">
+      <c r="A2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="127"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="27"/>
+    </row>
+    <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="30"/>
+    </row>
+    <row r="4" spans="1:38" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="130" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="130" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="131" t="s">
+        <v>215</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="58"/>
+    </row>
+    <row r="5" spans="1:38" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>10</v>
+      </c>
+      <c r="J5" s="10">
+        <f>I5*(G5/C5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>250</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="33">
+        <v>88363222</v>
+      </c>
+      <c r="N5" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="O5" s="132">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>22.5</v>
+      </c>
+      <c r="P5" s="132">
+        <f>IF($D$3=1,ROUND(((K5*N5)/2),2),0)</f>
+        <v>22.5</v>
+      </c>
+      <c r="Q5" s="33">
+        <f>IF($D$3=2,ROUND((K5*N5),2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="33">
+        <f>O5+P5+Q5</f>
+        <v>45</v>
+      </c>
+      <c r="S5" s="33">
+        <f>IF($J$3=1, K5+R5, K5)</f>
+        <v>295</v>
+      </c>
+      <c r="T5" s="59"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
+      <c r="AL5" s="29"/>
+    </row>
+    <row r="6" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="13" style="29" customWidth="1"/>
+    <col min="11" max="14" width="9.140625" style="29"/>
+    <col min="15" max="15" width="10.42578125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="29"/>
+    <col min="17" max="17" width="20.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="27.75" customHeight="1">
+      <c r="A1" s="134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+    </row>
+    <row r="2" spans="1:17" ht="18">
+      <c r="D2" s="109"/>
+    </row>
+    <row r="3" spans="1:17" ht="19.899999999999999" customHeight="1">
+      <c r="A3" s="133"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="108"/>
+    </row>
+    <row r="4" spans="1:17" s="31" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="115" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="115" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="M4" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N4" s="115" t="s">
+        <v>215</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="115" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q4" s="115" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>20</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <f>ROUND(C5*H5/F5,3)</f>
+        <v>20</v>
+      </c>
+      <c r="J5" s="122">
+        <f>I5*(G5/C5)</f>
+        <v>20</v>
+      </c>
+      <c r="K5" s="10">
+        <f>I5*G5</f>
+        <v>400</v>
+      </c>
+      <c r="L5" s="124">
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="10">
+        <f>K5*L5</f>
+        <v>72</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="123">
+        <v>88363222</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="L6" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16475,36 +18600,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="46"/>
       <c r="AD1" s="46"/>
       <c r="AE1" s="46"/>
@@ -16551,10 +18676,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="45"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -16824,7 +18949,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -16953,7 +19078,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17063,36 +19188,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="48"/>
       <c r="AE1" s="48"/>
@@ -17139,10 +19264,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="47"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -17412,7 +19537,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -17541,7 +19666,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -17651,36 +19776,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -17727,10 +19852,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -18000,7 +20125,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18129,7 +20254,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18239,36 +20364,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="50"/>
       <c r="AD1" s="50"/>
       <c r="AE1" s="50"/>
@@ -18315,10 +20440,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="49"/>
       <c r="D3" s="3">
         <v>3</v>
@@ -18588,7 +20713,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -18717,7 +20842,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -18827,36 +20952,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
       <c r="AC1" s="52"/>
       <c r="AD1" s="52"/>
       <c r="AE1" s="52"/>
@@ -18903,10 +21028,10 @@
       <c r="AG2" s="27"/>
     </row>
     <row r="3" spans="1:38" ht="19.899999999999999" customHeight="1">
-      <c r="A3" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="120"/>
+      <c r="A3" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="133"/>
       <c r="C3" s="51"/>
       <c r="D3" s="3">
         <v>2</v>
@@ -19176,7 +21301,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -19305,7 +21430,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="11" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15530" windowHeight="6540" firstSheet="21" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2285" uniqueCount="215">
   <si>
     <t>GST Sales</t>
   </si>
@@ -319,12 +319,6 @@
     <t>PROD 100</t>
   </si>
   <si>
-    <t>UD_Disimilar_Domestic_002-so100-SO100/00391/24-25-1</t>
-  </si>
-  <si>
-    <t>TVSFG004-so100-SO100/00670/24-25-1</t>
-  </si>
-  <si>
     <t>SO/Reference Domestic</t>
   </si>
   <si>
@@ -479,9 +473,6 @@
   </si>
   <si>
     <t>49091</t>
-  </si>
-  <si>
-    <t>63113</t>
   </si>
   <si>
     <t>49031</t>
@@ -712,9 +703,6 @@
     <t>CPC-10001</t>
   </si>
   <si>
-    <t>99671</t>
-  </si>
-  <si>
     <t>HK-CH-00002</t>
   </si>
   <si>
@@ -724,22 +712,13 @@
     <t>99656</t>
   </si>
   <si>
-    <t>99641</t>
+    <t>99566</t>
   </si>
   <si>
-    <t>99626</t>
+    <t>SORD-2526-00077</t>
   </si>
   <si>
-    <t>99611</t>
-  </si>
-  <si>
-    <t>99596</t>
-  </si>
-  <si>
-    <t>99581</t>
-  </si>
-  <si>
-    <t>99566</t>
+    <t>SORD-2526-00266</t>
   </si>
 </sst>
 </file>
@@ -1537,45 +1516,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="29" width="26.85546875"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="14.0"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="26.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -1615,7 +1594,7 @@
       <c r="AF1" s="1"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -1703,7 +1682,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -1819,18 +1798,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -1928,17 +1907,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>-15</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29">
         <v>87850</v>
@@ -2057,17 +2036,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9490</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -2125,45 +2104,45 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -2203,7 +2182,7 @@
       <c r="AF1" s="52"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -2291,7 +2270,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -2403,7 +2382,7 @@
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -2426,7 +2405,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -2512,22 +2491,22 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9775</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -2550,7 +2529,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -2636,17 +2615,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9890</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="59"/>
@@ -2699,46 +2678,46 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.453125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -2778,7 +2757,7 @@
       <c r="AF1" s="80"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -2866,7 +2845,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -2976,25 +2955,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3092,17 +3071,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>782</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -3162,46 +3141,46 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="18.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.453125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -3241,7 +3220,7 @@
       <c r="AF1" s="86"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -3329,7 +3308,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -3439,25 +3418,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3554,18 +3533,18 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>215</v>
+      <c r="AG5" s="36" t="s">
+        <v>211</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -3614,7 +3593,7 @@
     </row>
     <row r="9" spans="1:39">
       <c r="C9" s="89" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
@@ -3631,7 +3610,7 @@
     </row>
     <row r="10" spans="1:39">
       <c r="C10" s="90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>6</v>
@@ -3640,19 +3619,19 @@
         <v>7</v>
       </c>
       <c r="F10" s="90" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="90" t="s">
+      <c r="I10" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="H10" s="90" t="s">
+      <c r="J10" s="90" t="s">
         <v>95</v>
-      </c>
-      <c r="I10" s="90" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>97</v>
       </c>
       <c r="K10" s="90" t="s">
         <v>26</v>
@@ -3675,16 +3654,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H11" s="10">
         <v>20</v>
@@ -3716,16 +3695,16 @@
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
@@ -3757,7 +3736,7 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I13" s="10">
         <v>21477.41</v>
@@ -3790,46 +3769,46 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.453125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -3869,7 +3848,7 @@
       <c r="AF1" s="88"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -3957,7 +3936,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -4067,25 +4046,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4183,17 +4162,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -4253,46 +4232,46 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM36"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.453125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4332,7 +4311,7 @@
       <c r="AF1" s="93"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -4420,7 +4399,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -4530,25 +4509,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4646,17 +4625,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65248</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -4673,13 +4652,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="97" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="97" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -4777,17 +4756,17 @@
         <v>16</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
         <v>99984</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="34">
         <f>AH6</f>
@@ -4803,13 +4782,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="97" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
       </c>
       <c r="D7" s="97" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -4907,17 +4886,17 @@
         <v>17</v>
       </c>
       <c r="AG7" s="36" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AH7" s="34">
         <f t="shared" ref="AH7:AH14" si="20">AG7-AF7</f>
         <v>99983</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ7" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK7" s="34">
         <f t="shared" ref="AK7:AK14" si="21">AH7</f>
@@ -4933,13 +4912,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="97" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="97" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>32</v>
@@ -5037,17 +5016,17 @@
         <v>18</v>
       </c>
       <c r="AG8" s="36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AH8" s="34">
         <f t="shared" si="20"/>
         <v>99982</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK8" s="34">
         <f t="shared" si="21"/>
@@ -5063,13 +5042,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
       </c>
       <c r="D9" s="97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>32</v>
@@ -5167,17 +5146,17 @@
         <v>19</v>
       </c>
       <c r="AG9" s="36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AH9" s="34">
         <f t="shared" si="20"/>
         <v>99981</v>
       </c>
       <c r="AI9" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ9" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK9" s="34">
         <f t="shared" si="21"/>
@@ -5193,13 +5172,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="97" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>32</v>
@@ -5297,17 +5276,17 @@
         <v>20</v>
       </c>
       <c r="AG10" s="36" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AH10" s="34">
         <f t="shared" si="20"/>
         <v>99980</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ10" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK10" s="34">
         <f t="shared" si="21"/>
@@ -5323,13 +5302,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
       </c>
       <c r="D11" s="97" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>32</v>
@@ -5427,17 +5406,17 @@
         <v>21</v>
       </c>
       <c r="AG11" s="36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AH11" s="34">
         <f t="shared" si="20"/>
         <v>99979</v>
       </c>
       <c r="AI11" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ11" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK11" s="34">
         <f t="shared" si="21"/>
@@ -5453,13 +5432,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="100" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" s="99">
         <v>0</v>
       </c>
       <c r="D12" s="100" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E12" s="99" t="s">
         <v>32</v>
@@ -5557,17 +5536,17 @@
         <v>22</v>
       </c>
       <c r="AG12" s="36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AH12" s="102">
         <f t="shared" si="20"/>
         <v>99978</v>
       </c>
       <c r="AI12" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ12" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK12" s="102">
         <f t="shared" si="21"/>
@@ -5583,13 +5562,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>32</v>
@@ -5687,17 +5666,17 @@
         <v>23</v>
       </c>
       <c r="AG13" s="36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AH13" s="34">
         <f t="shared" si="20"/>
         <v>99977</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ13" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK13" s="34">
         <f t="shared" si="21"/>
@@ -5713,13 +5692,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>32</v>
@@ -5817,17 +5796,17 @@
         <v>24</v>
       </c>
       <c r="AG14" s="36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH14" s="34">
         <f t="shared" si="20"/>
         <v>99976</v>
       </c>
       <c r="AI14" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ14" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK14" s="34">
         <f t="shared" si="21"/>
@@ -6583,50 +6562,50 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AQ6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="28" width="36.0"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="41" customWidth="true" style="29" width="14.140625"/>
-    <col min="42" max="42" customWidth="true" style="29" width="15.0"/>
-    <col min="43" max="43" customWidth="true" style="29" width="16.5703125"/>
-    <col min="44" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="36" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="41" width="14.1796875" style="29" customWidth="1"/>
+    <col min="42" max="42" width="15" style="29" customWidth="1"/>
+    <col min="43" max="43" width="16.54296875" style="29" customWidth="1"/>
+    <col min="44" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -6666,7 +6645,7 @@
       <c r="AF1" s="54"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:43" ht="18">
+    <row r="2" spans="1:43" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -6754,7 +6733,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:43" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:43" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -6864,39 +6843,39 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN4" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="AO4" s="98" t="s">
+        <v>112</v>
+      </c>
+      <c r="AP4" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="AN4" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="AO4" s="98" t="s">
+      <c r="AQ4" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="AP4" s="98" t="s">
-        <v>115</v>
-      </c>
-      <c r="AQ4" s="98" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" ht="15">
+    </row>
+    <row r="5" spans="1:43" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -6993,18 +6972,18 @@
         <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>221</v>
+      <c r="AG5" s="36" t="s">
+        <v>212</v>
       </c>
       <c r="AH5" s="33">
         <f>AG5-AF5</f>
         <v>99656</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="33">
         <f>AH5</f>
@@ -7018,10 +6997,10 @@
         <v>69</v>
       </c>
       <c r="AN5" s="67" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AO5" s="29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7080,45 +7059,45 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="34.5703125"/>
-    <col min="8" max="8" customWidth="true" style="29" width="21.28515625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.54296875" style="29" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -7158,7 +7137,7 @@
       <c r="AF1" s="133"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -7207,7 +7186,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -7246,7 +7225,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -7356,22 +7335,22 @@
         <v>43</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7469,17 +7448,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>99861</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="7">
         <f>IF($D$3=4,ROUND(((U5*W5)/2),2),0)</f>
@@ -7535,45 +7514,45 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -7613,7 +7592,7 @@
       <c r="AF1" s="54"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -7701,7 +7680,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -7813,18 +7792,18 @@
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7922,17 +7901,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -7985,45 +7964,45 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -8063,7 +8042,7 @@
       <c r="AF1" s="56"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -8151,7 +8130,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -8263,18 +8242,18 @@
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8372,17 +8351,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -8435,45 +8414,45 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -8513,7 +8492,7 @@
       <c r="AF1" s="56"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -8601,7 +8580,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -8713,18 +8692,18 @@
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8822,17 +8801,17 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80704</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -8885,46 +8864,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -8964,7 +8943,7 @@
       <c r="AF1" s="39"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -9052,7 +9031,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -9168,21 +9147,21 @@
         <v>36</v>
       </c>
       <c r="AM4" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:39" ht="15">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9280,17 +9259,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>82574</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -9413,17 +9392,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9657.5</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -9485,45 +9464,45 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -9563,7 +9542,7 @@
       <c r="AF1" s="56"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -9651,7 +9630,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -9763,7 +9742,7 @@
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -9876,10 +9855,10 @@
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -9932,45 +9911,45 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -10010,7 +9989,7 @@
       <c r="AF1" s="56"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -10098,7 +10077,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -10210,7 +10189,7 @@
       <c r="AK4" s="57"/>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -10379,45 +10358,45 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -10457,7 +10436,7 @@
       <c r="AF1" s="62"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -10545,7 +10524,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -10661,18 +10640,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10777,10 +10756,10 @@
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="66">
         <v>5</v>
@@ -10838,44 +10817,44 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="15.42578125"/>
-    <col min="38" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.453125" style="29" customWidth="1"/>
+    <col min="38" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
@@ -10915,7 +10894,7 @@
       <c r="AF1" s="62"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:37" ht="18">
+    <row r="2" spans="1:37" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -11003,7 +10982,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:37" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:37" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -11114,18 +11093,18 @@
       </c>
       <c r="AK4" s="58"/>
     </row>
-    <row r="5" spans="1:37" ht="15">
+    <row r="5" spans="1:37" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11223,17 +11202,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>63733</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="59"/>
     </row>
@@ -11285,45 +11264,45 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -11363,7 +11342,7 @@
       <c r="AF1" s="65"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -11451,7 +11430,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -11565,7 +11544,7 @@
       </c>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -11674,35 +11653,35 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9630</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="66" t="s">
         <v>76</v>
       </c>
       <c r="AL5" s="59"/>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -11800,17 +11779,17 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>78219</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="66" t="s">
         <v>75</v>
@@ -11830,45 +11809,45 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.54296875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -11908,7 +11887,7 @@
       <c r="AF1" s="69"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -11996,7 +11975,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -12106,13 +12085,13 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL4" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="AL4" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" ht="15">
+    </row>
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -12234,24 +12213,24 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" ht="15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12362,10 +12341,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="AL6" s="66" t="s">
-        <v>84</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -12381,45 +12360,45 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.54296875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -12459,7 +12438,7 @@
       <c r="AF1" s="71"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -12547,7 +12526,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -12657,13 +12636,13 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL4" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="AL4" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" ht="15">
+    </row>
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -12785,24 +12764,24 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" ht="15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12913,10 +12892,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="AL6" s="66" t="s">
-        <v>84</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -12932,45 +12911,45 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.54296875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13010,7 +12989,7 @@
       <c r="AF1" s="74"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -13098,7 +13077,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -13208,13 +13187,13 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" ht="15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -13330,13 +13309,13 @@
         <v>38</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -13352,45 +13331,45 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.54296875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13430,7 +13409,7 @@
       <c r="AF1" s="76"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -13518,7 +13497,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -13628,13 +13607,13 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" ht="15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -13750,13 +13729,13 @@
         <v>38</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -13772,45 +13751,45 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="11.7109375"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
-    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="11.7265625" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="54.54296875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="34.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13850,7 +13829,7 @@
       <c r="AF1" s="78"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -13938,7 +13917,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -14048,13 +14027,13 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" ht="15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -14170,13 +14149,13 @@
         <v>38</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="72" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -14192,45 +14171,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -14270,7 +14249,7 @@
       <c r="AF1" s="41"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -14358,7 +14337,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -14474,7 +14453,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -14497,7 +14476,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -14583,17 +14562,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9645</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -14603,7 +14582,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -14626,7 +14605,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -14712,17 +14691,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9950.6589999999997</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -14780,46 +14759,46 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.453125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -14859,7 +14838,7 @@
       <c r="AF1" s="84"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -14947,7 +14926,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15057,25 +15036,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15173,17 +15152,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>49586</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -15243,46 +15222,46 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
-    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
-    <col min="40" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="29" customWidth="1"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="28" customWidth="1"/>
+    <col min="39" max="39" width="15.453125" style="29" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -15322,7 +15301,7 @@
       <c r="AF1" s="82"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -15410,7 +15389,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:39" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:39" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -15520,25 +15499,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15636,17 +15615,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -15706,25 +15685,25 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" ht="17.5">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
@@ -15738,25 +15717,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E4" s="58"/>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:5" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D5" s="10">
         <v>40</v>
@@ -15776,25 +15755,25 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" ht="17.5">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:5" ht="19.899999999999999" customHeight="1">
@@ -15808,25 +15787,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E4" s="58"/>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:5" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D5" s="10">
         <v>30</v>
@@ -15846,30 +15825,30 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="20.140625"/>
-    <col min="7" max="9" style="29" width="9.140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="11" max="15" style="29" width="9.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
-    <col min="17" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.1796875" style="29"/>
+    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="9.1796875" style="29"/>
+    <col min="16" max="16" width="20.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:16" ht="18">
+    <row r="2" spans="1:16" ht="17.5">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
@@ -15886,63 +15865,63 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -15979,7 +15958,7 @@
         <v>88363222</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16001,28 +15980,28 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="6" customWidth="true" style="29" width="12.0"/>
-    <col min="7" max="15" style="29" width="9.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="12.140625"/>
-    <col min="17" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="29" customWidth="1"/>
+    <col min="7" max="15" width="9.1796875" style="29"/>
+    <col min="16" max="16" width="12.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:16" ht="18">
+    <row r="2" spans="1:16" ht="17.5">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
@@ -16039,63 +16018,63 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16132,7 +16111,7 @@
         <v>88363222</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16154,30 +16133,30 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="6" customWidth="true" style="29" width="11.5703125"/>
-    <col min="7" max="9" style="29" width="9.140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="11" max="15" style="29" width="9.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
-    <col min="17" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="29" customWidth="1"/>
+    <col min="7" max="9" width="9.1796875" style="29"/>
+    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="9.1796875" style="29"/>
+    <col min="16" max="16" width="20.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:16" ht="18">
+    <row r="2" spans="1:16" ht="17.5">
       <c r="D2" s="119"/>
     </row>
     <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
@@ -16194,63 +16173,63 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16287,7 +16266,7 @@
         <v>88363222</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16309,30 +16288,30 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="6" customWidth="true" style="29" width="13.140625"/>
-    <col min="7" max="9" style="29" width="9.140625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="11.140625"/>
-    <col min="11" max="15" style="29" width="9.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
-    <col min="17" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" style="29" customWidth="1"/>
+    <col min="7" max="9" width="9.1796875" style="29"/>
+    <col min="10" max="10" width="11.1796875" style="29" customWidth="1"/>
+    <col min="11" max="15" width="9.1796875" style="29"/>
+    <col min="16" max="16" width="20.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:16" ht="18">
+    <row r="2" spans="1:16" ht="17.5">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
@@ -16349,63 +16328,63 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16436,13 +16415,13 @@
         <v>157.5</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O5" s="123">
         <v>88363222</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16464,25 +16443,25 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:15" ht="18">
+    <row r="2" spans="1:15" ht="17.5">
       <c r="D2" s="112"/>
     </row>
     <row r="3" spans="1:15" ht="19.899999999999999" customHeight="1">
@@ -16499,60 +16478,60 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16583,7 +16562,7 @@
         <v>135</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O5" s="123">
         <v>88363222</v>
@@ -16602,30 +16581,30 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="27.42578125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.140625"/>
-    <col min="7" max="9" style="29" width="9.140625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="11.7109375"/>
-    <col min="11" max="15" style="29" width="9.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="12.140625"/>
-    <col min="17" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="27.453125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.1796875" style="29"/>
+    <col min="10" max="10" width="11.7265625" style="29" customWidth="1"/>
+    <col min="11" max="15" width="9.1796875" style="29"/>
+    <col min="16" max="16" width="12.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:16" ht="18">
+    <row r="2" spans="1:16" ht="17.5">
       <c r="D2" s="121"/>
     </row>
     <row r="3" spans="1:16" ht="19.899999999999999" customHeight="1">
@@ -16642,63 +16621,63 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16735,7 +16714,7 @@
         <v>88363222</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -16757,45 +16736,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -16835,7 +16814,7 @@
       <c r="AF1" s="44"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -16923,7 +16902,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -17039,7 +17018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -17062,7 +17041,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17148,17 +17127,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9745</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -17168,7 +17147,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -17277,17 +17256,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9880</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -17345,27 +17324,27 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="9" style="29" width="9.140625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="11.0"/>
-    <col min="11" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="9.1796875" style="29"/>
+    <col min="10" max="10" width="11" style="29" customWidth="1"/>
+    <col min="11" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:15" ht="18">
+    <row r="2" spans="1:15" ht="17.5">
       <c r="D2" s="117"/>
     </row>
     <row r="3" spans="1:15" ht="19.899999999999999" customHeight="1">
@@ -17382,60 +17361,60 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -17485,52 +17464,52 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -17566,7 +17545,7 @@
       <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -17616,7 +17595,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -17626,7 +17605,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -17660,34 +17639,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -17705,7 +17684,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -17715,30 +17694,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -17839,52 +17818,52 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -17920,7 +17899,7 @@
       <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -17970,7 +17949,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -17980,7 +17959,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18014,34 +17993,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18059,7 +18038,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18069,30 +18048,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18193,52 +18172,52 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -18274,7 +18253,7 @@
       <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -18324,7 +18303,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -18334,7 +18313,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18368,34 +18347,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18413,7 +18392,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18423,30 +18402,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18547,52 +18526,52 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -18628,7 +18607,7 @@
       <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -18678,7 +18657,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -18688,7 +18667,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18722,34 +18701,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18767,7 +18746,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18777,30 +18756,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18901,52 +18880,52 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -18982,7 +18961,7 @@
       <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -19032,7 +19011,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19042,7 +19021,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19076,34 +19055,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19121,7 +19100,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19131,30 +19110,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -19255,52 +19234,52 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -19336,7 +19315,7 @@
       <c r="AG1" s="129"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -19386,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19396,7 +19375,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19430,34 +19409,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19475,7 +19454,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19485,30 +19464,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -19609,31 +19588,31 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
-    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
-    <col min="6" max="9" style="29" width="9.140625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="13.0"/>
-    <col min="11" max="14" style="29" width="9.140625"/>
-    <col min="15" max="15" customWidth="true" style="29" width="10.42578125"/>
-    <col min="16" max="16" style="29" width="9.140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="20.42578125"/>
-    <col min="18" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="9.1796875" style="29"/>
+    <col min="10" max="10" width="13" style="29" customWidth="1"/>
+    <col min="11" max="14" width="9.1796875" style="29"/>
+    <col min="15" max="15" width="10.453125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" style="29"/>
+    <col min="17" max="17" width="20.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
       <c r="D1" s="135"/>
     </row>
-    <row r="2" spans="1:17" ht="18">
+    <row r="2" spans="1:17" ht="17.5">
       <c r="D2" s="109"/>
     </row>
     <row r="3" spans="1:17" ht="19.899999999999999" customHeight="1">
@@ -19650,66 +19629,66 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="N4" s="115" t="s">
+        <v>171</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>95</v>
+      </c>
+      <c r="P4" s="115" t="s">
         <v>167</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="Q4" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>169</v>
-      </c>
-      <c r="N4" s="115" t="s">
-        <v>174</v>
-      </c>
-      <c r="O4" s="115" t="s">
-        <v>97</v>
-      </c>
-      <c r="P4" s="115" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q4" s="115" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15">
+    </row>
+    <row r="5" spans="1:17" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
@@ -19746,10 +19725,10 @@
         <v>88363222</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19768,52 +19747,52 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
-    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
-    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
-    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
-    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
-    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
-    <col min="41" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.7265625" style="29" customWidth="1"/>
+    <col min="19" max="19" width="9" style="29" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1796875" style="29" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.26953125" style="29" customWidth="1"/>
+    <col min="28" max="28" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7265625" style="29" customWidth="1"/>
+    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" style="29" customWidth="1"/>
+    <col min="33" max="33" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" style="36" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="28" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" style="29" customWidth="1"/>
+    <col min="37" max="37" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1796875" style="29" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="28" customWidth="1"/>
+    <col min="40" max="40" width="15.453125" style="29" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="135" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -19849,7 +19828,7 @@
       <c r="AG1" s="131"/>
       <c r="AH1" s="27"/>
     </row>
-    <row r="2" spans="1:39" ht="18">
+    <row r="2" spans="1:39" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -19899,7 +19878,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19909,7 +19888,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19943,34 +19922,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F4" s="126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G4" s="126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H4" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="J4" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="115" t="s">
-        <v>167</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19988,7 +19967,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19998,30 +19977,30 @@
       </c>
       <c r="U4" s="58"/>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="G5" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -20122,45 +20101,45 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -20200,7 +20179,7 @@
       <c r="AF1" s="46"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -20288,7 +20267,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -20404,7 +20383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -20513,17 +20492,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9717</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -20533,7 +20512,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -20556,7 +20535,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -20642,17 +20621,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9865</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -20710,45 +20689,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -20788,7 +20767,7 @@
       <c r="AF1" s="48"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -20876,7 +20855,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -20992,7 +20971,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -21015,7 +20994,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -21101,17 +21080,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9795</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -21121,7 +21100,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -21144,7 +21123,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -21230,17 +21209,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9900</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -21298,45 +21277,45 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -21376,7 +21355,7 @@
       <c r="AF1" s="50"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -21464,7 +21443,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -21580,7 +21559,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -21603,7 +21582,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -21689,17 +21668,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9703</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -21709,7 +21688,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -21732,7 +21711,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -21818,17 +21797,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9852.5</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -21886,45 +21865,45 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -21964,7 +21943,7 @@
       <c r="AF1" s="50"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -22052,7 +22031,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -22168,7 +22147,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -22277,17 +22256,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9805</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -22297,7 +22276,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -22406,17 +22385,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9905</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -22474,45 +22453,45 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
-    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
-    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
-    <col min="35" max="35" style="29" width="9.140625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
-    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
-    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
-    <col min="39" max="16384" style="29" width="9.140625"/>
+    <col min="1" max="1" width="5.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="29" customWidth="1"/>
+    <col min="10" max="11" width="8.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="14.7265625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.1796875" style="29" customWidth="1"/>
+    <col min="23" max="23" width="9.26953125" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.26953125" style="29" customWidth="1"/>
+    <col min="27" max="27" width="10.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="29" customWidth="1"/>
+    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.26953125" style="29" customWidth="1"/>
+    <col min="32" max="32" width="14.7265625" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.1796875" style="36" customWidth="1"/>
+    <col min="34" max="34" width="10.26953125" style="28" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="29"/>
+    <col min="36" max="36" width="13.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.26953125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="29" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -22552,7 +22531,7 @@
       <c r="AF1" s="52"/>
       <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:38" ht="18">
+    <row r="2" spans="1:38" ht="17.5">
       <c r="A2" s="29" t="s">
         <v>45</v>
       </c>
@@ -22640,7 +22619,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="30"/>
     </row>
-    <row r="4" spans="1:38" s="31" customFormat="1" ht="42.75">
+    <row r="4" spans="1:38" s="31" customFormat="1" ht="28">
       <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
@@ -22756,7 +22735,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="15">
+    <row r="5" spans="1:38" ht="14.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -22779,7 +22758,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -22865,17 +22844,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9805</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -22885,7 +22864,7 @@
         <v>87865</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="15">
+    <row r="6" spans="1:38" ht="14.5">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -22994,17 +22973,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9905</v>
       </c>
       <c r="AI6" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AJ6" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="21" activeTab="21"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="30" activeTab="32"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="233">
   <si>
     <t>GST Sales</t>
   </si>
@@ -300,9 +300,6 @@
   </si>
   <si>
     <t>9620</t>
-  </si>
-  <si>
-    <t>78104</t>
   </si>
   <si>
     <t>PROD 100</t>
@@ -704,12 +701,6 @@
     <t>SORD-2526-00266</t>
   </si>
   <si>
-    <t>PROC- 5140</t>
-  </si>
-  <si>
-    <t>PROC- 7766</t>
-  </si>
-  <si>
     <t>99775</t>
   </si>
   <si>
@@ -752,25 +743,37 @@
     <t>99767.5</t>
   </si>
   <si>
-    <t>95801</t>
-  </si>
-  <si>
     <t>95786</t>
   </si>
   <si>
-    <t>95731</t>
+    <t>95641</t>
   </si>
   <si>
-    <t>95716</t>
+    <t>30</t>
   </si>
   <si>
-    <t>95686</t>
+    <t>PROC- 0226</t>
   </si>
   <si>
-    <t>95671</t>
+    <t>PROC- 1797</t>
   </si>
   <si>
-    <t>95641</t>
+    <t>PROC- 5304</t>
+  </si>
+  <si>
+    <t>PROC- 6708</t>
+  </si>
+  <si>
+    <t>PROC- 9688</t>
+  </si>
+  <si>
+    <t>PROC- 8659</t>
+  </si>
+  <si>
+    <t>PROC- 1431</t>
+  </si>
+  <si>
+    <t>PROC- 1925</t>
   </si>
 </sst>
 </file>
@@ -1995,13 +1998,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2099,17 +2102,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>-15</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29">
         <v>87850</v>
@@ -2228,17 +2231,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9490</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -2597,7 +2600,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -2683,17 +2686,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9775</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -2721,7 +2724,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -2807,17 +2810,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9890</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="59"/>
@@ -3147,10 +3150,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -3159,13 +3162,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3263,17 +3266,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>782</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -3610,10 +3613,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -3622,13 +3625,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3726,17 +3729,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -3785,7 +3788,7 @@
     </row>
     <row r="9" spans="1:39">
       <c r="C9" s="89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
@@ -3802,7 +3805,7 @@
     </row>
     <row r="10" spans="1:39">
       <c r="C10" s="90" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>6</v>
@@ -3811,19 +3814,19 @@
         <v>7</v>
       </c>
       <c r="F10" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="90" t="s">
+      <c r="H10" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="90" t="s">
+      <c r="I10" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="I10" s="90" t="s">
+      <c r="J10" s="90" t="s">
         <v>90</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>91</v>
       </c>
       <c r="K10" s="90" t="s">
         <v>26</v>
@@ -3846,16 +3849,16 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="H11" s="10">
         <v>20</v>
@@ -3887,16 +3890,16 @@
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
@@ -3928,7 +3931,7 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" s="10">
         <v>21477.41</v>
@@ -4238,10 +4241,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -4250,13 +4253,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4354,17 +4357,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -4701,10 +4704,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -4713,13 +4716,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4817,17 +4820,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65248</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -4844,13 +4847,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -4948,17 +4951,17 @@
         <v>16</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH6" s="34">
         <f>AG6-AF6</f>
         <v>99984</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="34">
         <f>AH6</f>
@@ -4974,13 +4977,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
       </c>
       <c r="D7" s="97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -5078,17 +5081,17 @@
         <v>17</v>
       </c>
       <c r="AG7" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH7" s="34">
         <f t="shared" ref="AH7:AH14" si="20">AG7-AF7</f>
         <v>99983</v>
       </c>
       <c r="AI7" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ7" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ7" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK7" s="34">
         <f t="shared" ref="AK7:AK14" si="21">AH7</f>
@@ -5104,13 +5107,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>32</v>
@@ -5208,17 +5211,17 @@
         <v>18</v>
       </c>
       <c r="AG8" s="36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH8" s="34">
         <f t="shared" si="20"/>
         <v>99982</v>
       </c>
       <c r="AI8" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ8" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK8" s="34">
         <f t="shared" si="21"/>
@@ -5234,13 +5237,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
       </c>
       <c r="D9" s="97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>32</v>
@@ -5338,17 +5341,17 @@
         <v>19</v>
       </c>
       <c r="AG9" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AH9" s="34">
         <f t="shared" si="20"/>
         <v>99981</v>
       </c>
       <c r="AI9" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ9" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ9" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK9" s="34">
         <f t="shared" si="21"/>
@@ -5364,13 +5367,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="10">
         <v>0</v>
       </c>
       <c r="D10" s="97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>32</v>
@@ -5468,17 +5471,17 @@
         <v>20</v>
       </c>
       <c r="AG10" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AH10" s="34">
         <f t="shared" si="20"/>
         <v>99980</v>
       </c>
       <c r="AI10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ10" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ10" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK10" s="34">
         <f t="shared" si="21"/>
@@ -5494,13 +5497,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
       </c>
       <c r="D11" s="97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>32</v>
@@ -5598,17 +5601,17 @@
         <v>21</v>
       </c>
       <c r="AG11" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH11" s="34">
         <f t="shared" si="20"/>
         <v>99979</v>
       </c>
       <c r="AI11" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ11" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ11" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK11" s="34">
         <f t="shared" si="21"/>
@@ -5624,13 +5627,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="99">
         <v>0</v>
       </c>
       <c r="D12" s="100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="99" t="s">
         <v>32</v>
@@ -5728,17 +5731,17 @@
         <v>22</v>
       </c>
       <c r="AG12" s="36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AH12" s="102">
         <f t="shared" si="20"/>
         <v>99978</v>
       </c>
       <c r="AI12" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ12" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ12" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK12" s="102">
         <f t="shared" si="21"/>
@@ -5754,13 +5757,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>32</v>
@@ -5858,17 +5861,17 @@
         <v>23</v>
       </c>
       <c r="AG13" s="36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AH13" s="34">
         <f t="shared" si="20"/>
         <v>99977</v>
       </c>
       <c r="AI13" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ13" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ13" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK13" s="34">
         <f t="shared" si="21"/>
@@ -5884,13 +5887,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="10">
         <v>0</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>32</v>
@@ -5988,17 +5991,17 @@
         <v>24</v>
       </c>
       <c r="AG14" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH14" s="34">
         <f t="shared" si="20"/>
         <v>99976</v>
       </c>
       <c r="AI14" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ14" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ14" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK14" s="34">
         <f t="shared" si="21"/>
@@ -7035,25 +7038,25 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="AN4" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO4" s="98" t="s">
         <v>107</v>
       </c>
-      <c r="AN4" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO4" s="98" t="s">
+      <c r="AP4" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="AP4" s="98" t="s">
+      <c r="AQ4" s="98" t="s">
         <v>109</v>
-      </c>
-      <c r="AQ4" s="98" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="15">
@@ -7061,13 +7064,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7164,18 +7167,18 @@
         <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>231</v>
+      <c r="AG5" s="36" t="s">
+        <v>223</v>
       </c>
       <c r="AH5" s="33">
         <f>AG5-AF5</f>
         <v>99656</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="33">
         <f>AH5</f>
@@ -7189,10 +7192,10 @@
         <v>66</v>
       </c>
       <c r="AN5" s="67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO5" s="29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7378,7 +7381,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -7527,7 +7530,7 @@
         <v>43</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL4" s="58"/>
     </row>
@@ -7536,13 +7539,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7640,17 +7643,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>99861</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="7">
         <f>IF($D$3=4,ROUND(((U5*W5)/2),2),0)</f>
@@ -7989,13 +7992,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8093,17 +8096,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -8439,13 +8442,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8543,17 +8546,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -8889,13 +8892,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8993,17 +8996,17 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80704</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -9339,7 +9342,7 @@
         <v>36</v>
       </c>
       <c r="AM4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:39" ht="15">
@@ -9347,13 +9350,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9451,17 +9454,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>82574</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -9584,17 +9587,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9657.5</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -10047,10 +10050,10 @@
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -10494,10 +10497,10 @@
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -10837,13 +10840,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -10940,18 +10943,18 @@
         <f t="shared" ref="AF5" si="2">G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>226</v>
+      <c r="AG5" s="36" t="s">
+        <v>222</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="66">
         <v>5</v>
@@ -11290,13 +11293,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11394,17 +11397,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>63733</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="59"/>
     </row>
@@ -11845,17 +11848,17 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9630</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="66" t="s">
         <v>72</v>
@@ -11867,13 +11870,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -11971,17 +11974,17 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>78219</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="66" t="s">
         <v>71</v>
@@ -12277,10 +12280,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -12405,10 +12408,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL5" s="72" t="s">
         <v>207</v>
-      </c>
-      <c r="AL5" s="72" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -12416,13 +12419,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12533,10 +12536,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL6" s="66" t="s">
         <v>207</v>
-      </c>
-      <c r="AL6" s="66" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -12828,10 +12831,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -12956,10 +12959,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL5" s="72" t="s">
         <v>207</v>
-      </c>
-      <c r="AL5" s="72" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -12967,13 +12970,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -13084,10 +13087,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL6" s="66" t="s">
         <v>207</v>
-      </c>
-      <c r="AL6" s="66" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -13379,10 +13382,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -13498,16 +13501,16 @@
         <v>9612.5</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="AK5" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -13799,10 +13802,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -13918,16 +13921,16 @@
         <v>-10</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="AK5" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14219,10 +14222,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15">
@@ -14338,16 +14341,16 @@
         <v>-5</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="AK5" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AL5" s="72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14668,7 +14671,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -14754,17 +14757,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9645</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -14797,7 +14800,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -14883,17 +14886,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9950.6589999999997</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -15228,10 +15231,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -15240,13 +15243,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15344,17 +15347,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>49586</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -15691,10 +15694,10 @@
         <v>43</v>
       </c>
       <c r="AK4" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL4" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AM4" s="58"/>
     </row>
@@ -15703,13 +15706,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15807,17 +15810,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -15889,7 +15892,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -15909,13 +15912,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15923,11 +15926,11 @@
       <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>209</v>
+      <c r="B5" t="s" s="29">
+        <v>232</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" s="10">
         <v>40</v>
@@ -15959,7 +15962,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -15979,13 +15982,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -15994,10 +15997,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D5" s="10">
         <v>30</v>
@@ -16034,7 +16037,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -16057,46 +16060,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16104,16 +16107,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16147,10 +16150,10 @@
         <v>32</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16187,7 +16190,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -16210,46 +16213,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16257,16 +16260,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16300,10 +16303,10 @@
         <v>32</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16342,7 +16345,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -16365,46 +16368,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16412,16 +16415,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16455,10 +16458,10 @@
         <v>32</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16497,7 +16500,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -16520,46 +16523,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16567,16 +16570,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="114" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="114" t="s">
-        <v>145</v>
-      </c>
       <c r="D5" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16607,13 +16610,13 @@
         <v>157.5</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16647,7 +16650,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -16670,43 +16673,43 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15">
@@ -16714,16 +16717,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16754,10 +16757,10 @@
         <v>135</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
     </row>
   </sheetData>
@@ -16790,7 +16793,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -16813,46 +16816,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16860,16 +16863,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16903,10 +16906,10 @@
         <v>32</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -17233,7 +17236,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17319,17 +17322,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9745</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -17448,17 +17451,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9880</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -17530,7 +17533,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -17553,43 +17556,43 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>161</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O4" s="115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15">
@@ -17597,16 +17600,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -17640,7 +17643,7 @@
         <v>32</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
     </row>
   </sheetData>
@@ -17701,7 +17704,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -17787,7 +17790,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -17797,7 +17800,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -17831,34 +17834,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -17876,7 +17879,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -17891,25 +17894,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -17927,7 +17930,7 @@
         <v>32</v>
       </c>
       <c r="M5" s="33">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="N5" s="22">
         <v>0.18</v>
@@ -18055,7 +18058,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -18141,7 +18144,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -18151,7 +18154,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18185,34 +18188,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18230,7 +18233,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18245,25 +18248,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18281,7 +18284,7 @@
         <v>32</v>
       </c>
       <c r="M5" s="33">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="N5" s="22">
         <v>0.18</v>
@@ -18409,7 +18412,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -18495,7 +18498,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -18505,7 +18508,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18539,34 +18542,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18584,7 +18587,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18599,25 +18602,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18635,7 +18638,7 @@
         <v>32</v>
       </c>
       <c r="M5" s="33">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="N5" s="22">
         <v>0.18</v>
@@ -18763,7 +18766,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -18849,7 +18852,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -18859,7 +18862,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18893,34 +18896,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18938,7 +18941,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18953,25 +18956,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18989,7 +18992,7 @@
         <v>32</v>
       </c>
       <c r="M5" s="33">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="N5" s="22">
         <v>0.18</v>
@@ -19117,7 +19120,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -19203,7 +19206,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19213,7 +19216,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19247,34 +19250,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19292,7 +19295,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19307,25 +19310,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -19343,7 +19346,7 @@
         <v>32</v>
       </c>
       <c r="M5" s="33">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="N5" s="22">
         <v>0.18</v>
@@ -19471,7 +19474,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -19557,7 +19560,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19567,7 +19570,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19601,34 +19604,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19646,7 +19649,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19661,25 +19664,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -19697,7 +19700,7 @@
         <v>32</v>
       </c>
       <c r="M5" s="33">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="N5" s="22">
         <v>0.18</v>
@@ -19798,7 +19801,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -19821,49 +19824,49 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="115" t="s">
+      <c r="N4" s="115" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="115" t="s">
+        <v>90</v>
+      </c>
+      <c r="P4" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="N4" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="O4" s="115" t="s">
-        <v>91</v>
-      </c>
-      <c r="P4" s="115" t="s">
+      <c r="Q4" s="115" t="s">
         <v>162</v>
-      </c>
-      <c r="Q4" s="115" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15">
@@ -19871,16 +19874,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="10">
         <v>1</v>
@@ -19914,13 +19917,13 @@
         <v>32</v>
       </c>
       <c r="O5" s="123">
-        <v>88363222</v>
+        <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q5" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -19984,7 +19987,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="165"/>
       <c r="C1" s="165"/>
@@ -20070,7 +20073,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -20080,7 +20083,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -20114,34 +20117,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>131</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>159</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -20159,7 +20162,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -20174,25 +20177,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -20369,7 +20372,7 @@
     </row>
     <row r="2" spans="1:38" ht="18">
       <c r="A2" s="134" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B2" s="134"/>
       <c r="C2" s="134"/>
@@ -20413,7 +20416,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="140" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F3" s="141"/>
       <c r="G3" s="141"/>
@@ -20572,13 +20575,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="155">
         <v>0</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" s="155" t="s">
         <v>32</v>
@@ -20642,7 +20645,7 @@
         <v>11493.38</v>
       </c>
       <c r="V5" s="155" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="W5" s="156">
         <v>0.18</v>
@@ -20682,17 +20685,17 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>99896</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29">
         <v>87850</v>
@@ -20707,16 +20710,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C6" s="155">
         <v>0</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E6" s="155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F6" s="155" t="s">
         <v>32</v>
@@ -20777,7 +20780,7 @@
         <v>26656.080000000002</v>
       </c>
       <c r="V6" s="155" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="W6" s="156">
         <v>0.18</v>
@@ -20817,17 +20820,17 @@
         <v>3.3330000000000002</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>99966.667000000001</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -20855,7 +20858,7 @@
       <c r="O7" s="159"/>
       <c r="P7" s="161"/>
       <c r="Q7" s="161" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="R7" s="161"/>
       <c r="S7" s="161"/>
@@ -20866,7 +20869,7 @@
       <c r="X7" s="159"/>
       <c r="Y7" s="159"/>
       <c r="Z7" s="161" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AA7" s="161"/>
       <c r="AB7" s="162">
@@ -20874,7 +20877,7 @@
         <v>45016.36</v>
       </c>
       <c r="AC7" s="161" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AD7" s="162">
         <f>SUM(AD5:AD6)</f>
@@ -21324,17 +21327,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9717</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -21367,7 +21370,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -21453,17 +21456,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9865</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -21826,7 +21829,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -21912,17 +21915,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9795</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -21955,7 +21958,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -22041,17 +22044,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9900</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -22414,7 +22417,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -22500,17 +22503,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9703</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -22543,7 +22546,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -22629,17 +22632,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9852.5</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -23002,7 +23005,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -23088,17 +23091,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9805</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -23131,7 +23134,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -23217,17 +23220,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9905</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -23590,7 +23593,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -23676,17 +23679,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9805</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -23719,7 +23722,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -23805,17 +23808,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9905</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="34" activeTab="39"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="22" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="233">
   <si>
     <t>GST Sales</t>
   </si>
@@ -730,9 +730,6 @@
     <t>95786</t>
   </si>
   <si>
-    <t>95641</t>
-  </si>
-  <si>
     <t>SORD-2526-00764</t>
   </si>
   <si>
@@ -779,9 +776,6 @@
   </si>
   <si>
     <t>40</t>
-  </si>
-  <si>
-    <t>93041</t>
   </si>
   <si>
     <t>93026</t>
@@ -2126,7 +2120,7 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
@@ -2255,7 +2249,7 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
@@ -7191,8 +7185,8 @@
         <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>234</v>
+      <c r="AG5" s="36" t="s">
+        <v>232</v>
       </c>
       <c r="AH5" s="33">
         <f>AG5-AF5</f>
@@ -12703,7 +12697,7 @@
       <c r="B3" s="169"/>
       <c r="C3" s="70"/>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>1</v>
@@ -12945,15 +12939,15 @@
       </c>
       <c r="Z5" s="34">
         <f>IF($D$3=2,ROUND(((U5*W5)),2),0)</f>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="AA5" s="9">
         <f>X5+Y5+Z5</f>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="AB5" s="9">
         <f t="shared" ref="AB5:AB6" si="0">U5+AA5</f>
-        <v>2100</v>
+        <v>2478</v>
       </c>
       <c r="AC5" s="9">
         <v>120</v>
@@ -13073,15 +13067,15 @@
       </c>
       <c r="Z6" s="34">
         <f>IF($D$3=2,ROUND(((U6*W6)),2),0)</f>
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AA6" s="9">
         <f>X6+Y6+Z6</f>
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AB6" s="9">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>708</v>
       </c>
       <c r="AC6" s="9">
         <v>120</v>
@@ -15378,7 +15372,7 @@
         <v>49586</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AJ5" s="10" t="s">
         <v>175</v>
@@ -15834,14 +15828,14 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AJ5" s="10" t="s">
         <v>175</v>
@@ -15951,7 +15945,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>130</v>
@@ -16021,7 +16015,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>129</v>
@@ -16177,7 +16171,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16332,7 +16326,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16485,7 +16479,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16793,7 +16787,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="166" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16948,7 +16942,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -17691,7 +17685,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -17846,7 +17840,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -18706,7 +18700,7 @@
         <v>129</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H5" s="29" t="s">
         <v>162</v>
@@ -19060,7 +19054,7 @@
         <v>129</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H5" s="29" t="s">
         <v>162</v>
@@ -19414,7 +19408,7 @@
         <v>129</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H5" s="29" t="s">
         <v>162</v>
@@ -19768,7 +19762,7 @@
         <v>129</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H5" s="29" t="s">
         <v>162</v>
@@ -20698,7 +20692,7 @@
         <v>123</v>
       </c>
       <c r="C5" t="s" s="29">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>126</v>
@@ -20710,7 +20704,7 @@
         <v>129</v>
       </c>
       <c r="G5" t="s" s="29">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H5" t="s" s="29">
         <v>162</v>
@@ -21051,7 +21045,7 @@
       <c r="B5" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="C5" t="s" s="29">
+      <c r="C5" s="29" t="s">
         <v>141</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -21060,13 +21054,13 @@
       <c r="E5" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="F5" t="s" s="29">
+      <c r="F5" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="G5" t="s" s="29">
-        <v>232</v>
-      </c>
-      <c r="H5" t="s" s="29">
+      <c r="G5" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="29" t="s">
         <v>162</v>
       </c>
       <c r="I5" s="10">
@@ -21081,7 +21075,7 @@
         <f>I5*G5</f>
         <v>625</v>
       </c>
-      <c r="L5" t="s" s="29">
+      <c r="L5" s="29" t="s">
         <v>32</v>
       </c>
       <c r="M5" s="33">

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="251">
   <si>
     <t>GST Sales</t>
   </si>
@@ -813,6 +813,27 @@
   </si>
   <si>
     <t>99710</t>
+  </si>
+  <si>
+    <t>90931</t>
+  </si>
+  <si>
+    <t>90916</t>
+  </si>
+  <si>
+    <t>90901</t>
+  </si>
+  <si>
+    <t>90886</t>
+  </si>
+  <si>
+    <t>90871</t>
+  </si>
+  <si>
+    <t>90856</t>
+  </si>
+  <si>
+    <t>99830</t>
   </si>
 </sst>
 </file>
@@ -1780,43 +1801,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="26.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="29" width="26.85546875"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="14.0"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -2368,43 +2389,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -2942,44 +2963,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -3405,44 +3426,44 @@
   <dimension ref="A1:AM13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="18.85546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4033,44 +4054,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4496,44 +4517,44 @@
   <dimension ref="A1:AM36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -6826,48 +6847,48 @@
   <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="36" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="41" width="14.140625" style="29" customWidth="1"/>
-    <col min="42" max="42" width="15" style="29" customWidth="1"/>
-    <col min="43" max="43" width="16.5703125" style="29" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="28" width="36.0"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="41" customWidth="true" style="29" width="14.140625"/>
+    <col min="42" max="42" customWidth="true" style="29" width="15.0"/>
+    <col min="43" max="43" customWidth="true" style="29" width="16.5703125"/>
+    <col min="44" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -7234,8 +7255,8 @@
         <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>241</v>
+      <c r="AG5" t="s" s="36">
+        <v>249</v>
       </c>
       <c r="AH5" s="33">
         <f>AG5-AF5</f>
@@ -7255,14 +7276,14 @@
         <f>AK5+G5</f>
         <v>99671</v>
       </c>
-      <c r="AM5" s="28" t="s">
+      <c r="AM5" t="s" s="28">
         <v>66</v>
       </c>
       <c r="AN5" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="AO5" s="29" t="s">
-        <v>120</v>
+      <c r="AO5" t="s" s="29">
+        <v>250</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7323,43 +7344,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.5703125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="29" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="34.5703125"/>
+    <col min="8" max="8" customWidth="true" style="29" width="21.28515625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -7778,43 +7799,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -8228,43 +8249,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -8678,43 +8699,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -9128,44 +9149,44 @@
   <dimension ref="A1:AM7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -9728,43 +9749,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -10175,43 +10196,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -10622,43 +10643,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -11081,42 +11102,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.42578125" style="29" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="15.42578125"/>
+    <col min="38" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="27.75" customHeight="1">
@@ -11528,43 +11549,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -12073,43 +12094,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -12624,43 +12645,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13175,43 +13196,43 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -13595,43 +13616,43 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -14015,43 +14036,43 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="54.5703125" style="29" customWidth="1"/>
-    <col min="38" max="38" width="34.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="11.7109375"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="54.5703125"/>
+    <col min="38" max="38" customWidth="true" style="29" width="34.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -14435,43 +14456,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -15023,44 +15044,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -15486,44 +15507,44 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="29" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="28" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" style="29" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" customWidth="true" style="29" width="12.42578125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="28" width="12.5703125"/>
+    <col min="39" max="39" customWidth="true" style="29" width="15.42578125"/>
+    <col min="40" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -15949,12 +15970,12 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
@@ -16019,12 +16040,12 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.42578125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
@@ -16089,17 +16110,17 @@
   <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -16244,17 +16265,17 @@
   <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -16399,15 +16420,15 @@
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="29" customWidth="1"/>
-    <col min="7" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="14.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="12.0"/>
+    <col min="7" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="14.85546875"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -16552,15 +16573,15 @@
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="29" customWidth="1"/>
-    <col min="7" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="12.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="12.0"/>
+    <col min="7" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="12.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -16705,17 +16726,17 @@
   <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="29" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="11.5703125"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -16860,17 +16881,17 @@
   <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="29" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="11.5703125"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -17015,43 +17036,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -17603,17 +17624,17 @@
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="29" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="11.140625" style="29" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="13.140625"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="11.140625"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -17758,17 +17779,17 @@
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="29" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="11.140625" style="29" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="20.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="13.140625"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="11.140625"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="20.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -17913,12 +17934,12 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
@@ -18051,17 +18072,17 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="11.7109375" style="29" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="12.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="27.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.140625"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="11.7109375"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="12.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -18206,17 +18227,17 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="11.7109375" style="29" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" style="29"/>
-    <col min="16" max="16" width="12.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="27.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.140625"/>
+    <col min="7" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="11.7109375"/>
+    <col min="11" max="15" style="29" width="9.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="12.140625"/>
+    <col min="17" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
@@ -18361,14 +18382,14 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="11" style="29" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="11.0"/>
+    <col min="11" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
@@ -18501,45 +18522,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -18855,45 +18876,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -19209,45 +19230,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -19563,45 +19584,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -19917,43 +19938,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -20505,45 +20526,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -20859,45 +20880,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -21213,18 +21234,18 @@
   <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="9.140625" style="29"/>
-    <col min="10" max="10" width="13" style="29" customWidth="1"/>
-    <col min="11" max="14" width="9.140625" style="29"/>
-    <col min="15" max="15" width="10.42578125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="29"/>
-    <col min="17" max="17" width="20.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="21.7109375"/>
+    <col min="4" max="4" customWidth="true" style="29" width="24.28515625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="19.5703125"/>
+    <col min="6" max="9" style="29" width="9.140625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="13.0"/>
+    <col min="11" max="14" style="29" width="9.140625"/>
+    <col min="15" max="15" customWidth="true" style="29" width="10.42578125"/>
+    <col min="16" max="16" style="29" width="9.140625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="20.42578125"/>
+    <col min="18" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27.75" customHeight="1">
@@ -21372,13 +21393,13 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="15.28515625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="15.140625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="14.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="15.5703125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="7" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
@@ -21463,45 +21484,45 @@
   <dimension ref="A1:AM6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" style="29" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="29" customWidth="1"/>
-    <col min="19" max="19" width="9" style="29" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="29" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="29" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="29" customWidth="1"/>
-    <col min="30" max="30" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" style="36" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="28" customWidth="1"/>
-    <col min="36" max="36" width="12.42578125" style="29" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.140625" style="29" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="28" customWidth="1"/>
-    <col min="40" max="40" width="15.42578125" style="29" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" customWidth="true" style="29" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.28515625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="14.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="10" customWidth="true" style="29" width="13.5703125"/>
+    <col min="11" max="11" customWidth="true" style="29" width="12.28515625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.7109375"/>
+    <col min="19" max="19" customWidth="true" style="29" width="9.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="23" max="23" customWidth="true" style="29" width="16.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="27" max="27" customWidth="true" style="29" width="11.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="29" max="29" customWidth="true" style="29" width="11.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="32" max="32" customWidth="true" style="29" width="12.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="34" max="34" customWidth="true" style="36" width="14.140625"/>
+    <col min="35" max="35" customWidth="true" style="28" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="29" width="12.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="13.140625"/>
+    <col min="39" max="39" customWidth="true" style="28" width="12.5703125"/>
+    <col min="40" max="40" customWidth="true" style="29" width="15.42578125"/>
+    <col min="41" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -21817,40 +21838,40 @@
   <dimension ref="A1:AL8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="137" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="137" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="137" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="137" customWidth="1"/>
-    <col min="5" max="5" width="10" style="137" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="137" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="137" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="137" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="137" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="137" customWidth="1"/>
-    <col min="12" max="12" width="8" style="137" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="137" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="137" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="137" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="137" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="137" customWidth="1"/>
-    <col min="18" max="18" width="9" style="137" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="137" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="137" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="137" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="137" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="137" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="137" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="137" customWidth="1"/>
-    <col min="27" max="27" width="12" style="137" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="137" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="137" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="163" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="163" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.5703125" style="163" customWidth="1"/>
-    <col min="33" max="33" width="15.7109375" style="136" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="137" customWidth="1"/>
-    <col min="35" max="35" width="12.7109375" style="137" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="137"/>
+    <col min="1" max="1" customWidth="true" style="137" width="5.7109375"/>
+    <col min="2" max="2" customWidth="true" style="137" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="137" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="137" width="28.85546875"/>
+    <col min="5" max="5" customWidth="true" style="137" width="10.0"/>
+    <col min="6" max="6" customWidth="true" style="137" width="12.5703125"/>
+    <col min="7" max="7" customWidth="true" style="137" width="14.7109375"/>
+    <col min="8" max="8" customWidth="true" style="137" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="137" width="13.5703125"/>
+    <col min="10" max="11" customWidth="true" style="137" width="8.140625"/>
+    <col min="12" max="12" customWidth="true" style="137" width="8.0"/>
+    <col min="13" max="13" customWidth="true" style="137" width="13.85546875"/>
+    <col min="14" max="14" customWidth="true" style="137" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="137" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="137" width="14.7109375"/>
+    <col min="17" max="17" customWidth="true" style="137" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="137" width="9.0"/>
+    <col min="19" max="19" customWidth="true" style="137" width="10.85546875"/>
+    <col min="20" max="20" customWidth="true" style="137" width="17.85546875"/>
+    <col min="21" max="21" customWidth="true" style="137" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="137" width="11.5703125"/>
+    <col min="23" max="23" customWidth="true" style="137" width="9.28515625"/>
+    <col min="24" max="25" customWidth="true" style="137" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="137" width="11.28515625"/>
+    <col min="27" max="27" customWidth="true" style="137" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="137" width="12.28515625"/>
+    <col min="29" max="29" customWidth="true" style="137" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="163" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="163" width="13.5703125"/>
+    <col min="32" max="32" customWidth="true" style="163" width="13.5703125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="136" width="15.7109375"/>
+    <col min="34" max="34" customWidth="true" style="137" width="13.5703125"/>
+    <col min="35" max="35" customWidth="true" style="137" width="12.7109375"/>
+    <col min="36" max="16384" style="137" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -22457,43 +22478,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -23045,43 +23066,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -23633,43 +23654,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">
@@ -24221,43 +24242,43 @@
   <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="29" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="29" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="29" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="29" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="29" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="29" customWidth="1"/>
-    <col min="29" max="29" width="16" style="29" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="29" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="29" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.140625" style="36" customWidth="1"/>
-    <col min="34" max="34" width="10.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="29"/>
-    <col min="36" max="36" width="13.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="29" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="29" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="29" width="30.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="29" width="4.5703125"/>
+    <col min="4" max="4" customWidth="true" style="29" width="29.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="29" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="29" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="29" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="29" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="29" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="29" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="29" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="29" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="29" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="29" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="29" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="29" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="29" width="16.140625"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="29" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="29" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="29" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="29" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="29" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="29" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="29" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="29" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="36" width="14.140625"/>
+    <col min="34" max="34" customWidth="true" style="28" width="10.28515625"/>
+    <col min="35" max="35" style="29" width="9.140625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="29" width="13.140625"/>
+    <col min="37" max="37" customWidth="true" style="29" width="14.28515625"/>
+    <col min="38" max="38" customWidth="true" style="29" width="15.42578125"/>
+    <col min="39" max="16384" style="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="27.75" customHeight="1">

--- a/testdata/DBSales.xlsx
+++ b/testdata/DBSales.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="44" activeTab="47"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15525" windowHeight="6540" firstSheet="36" activeTab="33"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic S&amp;D" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="245">
   <si>
     <t>GST Sales</t>
   </si>
@@ -441,9 +441,6 @@
   </si>
   <si>
     <t>105596</t>
-  </si>
-  <si>
-    <t>100001867</t>
   </si>
   <si>
     <t>Process</t>
@@ -806,34 +803,19 @@
     <t>PROC- 5049</t>
   </si>
   <si>
-    <t>91316</t>
-  </si>
-  <si>
     <t>99725</t>
   </si>
   <si>
     <t>99710</t>
   </si>
   <si>
-    <t>90931</t>
-  </si>
-  <si>
-    <t>90916</t>
-  </si>
-  <si>
-    <t>90901</t>
-  </si>
-  <si>
-    <t>90886</t>
-  </si>
-  <si>
-    <t>90871</t>
-  </si>
-  <si>
     <t>90856</t>
   </si>
   <si>
     <t>99830</t>
+  </si>
+  <si>
+    <t>PROC- 0744</t>
   </si>
 </sst>
 </file>
@@ -2086,13 +2068,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2190,17 +2172,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>-15</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="29">
         <v>87850</v>
@@ -2319,17 +2301,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9490</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -2688,7 +2670,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -2774,17 +2756,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9775</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -2812,7 +2794,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -2898,17 +2880,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9890</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="59"/>
@@ -3361,10 +3343,10 @@
         <v>782</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -3713,13 +3695,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -3817,17 +3799,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -3937,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
@@ -3978,7 +3960,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
@@ -4445,17 +4427,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -4804,13 +4786,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -4915,10 +4897,10 @@
         <v>65248</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -5046,10 +5028,10 @@
         <v>99984</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="34">
         <f>AH6</f>
@@ -5176,10 +5158,10 @@
         <v>99983</v>
       </c>
       <c r="AI7" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ7" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ7" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK7" s="34">
         <f t="shared" ref="AK7:AK14" si="21">AH7</f>
@@ -5306,10 +5288,10 @@
         <v>99982</v>
       </c>
       <c r="AI8" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ8" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK8" s="34">
         <f t="shared" si="21"/>
@@ -5436,10 +5418,10 @@
         <v>99981</v>
       </c>
       <c r="AI9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ9" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ9" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK9" s="34">
         <f t="shared" si="21"/>
@@ -5566,10 +5548,10 @@
         <v>99980</v>
       </c>
       <c r="AI10" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ10" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ10" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK10" s="34">
         <f t="shared" si="21"/>
@@ -5696,10 +5678,10 @@
         <v>99979</v>
       </c>
       <c r="AI11" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ11" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ11" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK11" s="34">
         <f t="shared" si="21"/>
@@ -5826,10 +5808,10 @@
         <v>99978</v>
       </c>
       <c r="AI12" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ12" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ12" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK12" s="102">
         <f t="shared" si="21"/>
@@ -5956,10 +5938,10 @@
         <v>99977</v>
       </c>
       <c r="AI13" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ13" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ13" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK13" s="34">
         <f t="shared" si="21"/>
@@ -6086,10 +6068,10 @@
         <v>99976</v>
       </c>
       <c r="AI14" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ14" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ14" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK14" s="34">
         <f t="shared" si="21"/>
@@ -7152,13 +7134,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7255,18 +7237,18 @@
         <f>G5/AE5</f>
         <v>15</v>
       </c>
-      <c r="AG5" t="s" s="36">
-        <v>249</v>
+      <c r="AG5" s="36" t="s">
+        <v>242</v>
       </c>
       <c r="AH5" s="33">
         <f>AG5-AF5</f>
         <v>99656</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="33">
         <f>AH5</f>
@@ -7276,14 +7258,14 @@
         <f>AK5+G5</f>
         <v>99671</v>
       </c>
-      <c r="AM5" t="s" s="28">
+      <c r="AM5" s="28" t="s">
         <v>66</v>
       </c>
       <c r="AN5" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO5" t="s" s="29">
-        <v>250</v>
+        <v>175</v>
+      </c>
+      <c r="AO5" s="29" t="s">
+        <v>243</v>
       </c>
       <c r="AP5" s="34">
         <f>AO5+AF5</f>
@@ -7469,7 +7451,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -7618,7 +7600,7 @@
         <v>43</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL4" s="58"/>
     </row>
@@ -7627,13 +7609,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -7731,17 +7713,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>99861</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="7">
         <f>IF($D$3=4,ROUND(((U5*W5)/2),2),0)</f>
@@ -8080,13 +8062,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8184,17 +8166,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -8530,13 +8512,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -8634,17 +8616,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -8980,13 +8962,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9084,17 +9066,17 @@
         <v>10</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80704</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -9438,13 +9420,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -9542,17 +9524,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>82574</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -9675,17 +9657,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9657.5</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -10138,10 +10120,10 @@
         <v>80704</v>
       </c>
       <c r="AI5" s="63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -10588,7 +10570,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AK5" s="7"/>
       <c r="AL5" s="59"/>
@@ -10928,13 +10910,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11032,17 +11014,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>80699</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="66">
         <v>5</v>
@@ -11381,13 +11363,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -11485,17 +11467,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>63733</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="59"/>
     </row>
@@ -11936,17 +11918,17 @@
         <v>7.5</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9630</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="66" t="s">
         <v>72</v>
@@ -11958,13 +11940,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12062,17 +12044,17 @@
         <v>15</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>78219</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="66" t="s">
         <v>71</v>
@@ -12496,10 +12478,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL5" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AL5" s="72" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -12507,13 +12489,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -12624,10 +12606,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL6" s="66" t="s">
         <v>200</v>
-      </c>
-      <c r="AL6" s="66" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -13047,10 +13029,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK5" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL5" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AL5" s="72" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="15">
@@ -13058,13 +13040,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>32</v>
@@ -13175,10 +13157,10 @@
         <v>4010101001</v>
       </c>
       <c r="AK6" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL6" s="66" t="s">
         <v>200</v>
-      </c>
-      <c r="AL6" s="66" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -13589,13 +13571,13 @@
         <v>9612.5</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
-      </c>
       <c r="AK5" s="72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AL5" s="72" t="s">
         <v>77</v>
@@ -14009,13 +13991,13 @@
         <v>-10</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
-      </c>
       <c r="AK5" s="72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AL5" s="72" t="s">
         <v>77</v>
@@ -14429,13 +14411,13 @@
         <v>-5</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
-      </c>
       <c r="AK5" s="72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AL5" s="72" t="s">
         <v>77</v>
@@ -14759,7 +14741,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -14845,17 +14827,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9645</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -14888,7 +14870,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -14974,17 +14956,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9950.6589999999997</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -15331,13 +15313,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15435,17 +15417,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>49586</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -15794,13 +15776,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -15898,17 +15880,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH5" s="34">
         <f>AG5-AF5</f>
         <v>65983</v>
       </c>
       <c r="AI5" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AJ5" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AK5" s="34">
         <f>AH5</f>
@@ -15980,7 +15962,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16000,13 +15982,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -16014,11 +15996,11 @@
       <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>219</v>
+      <c r="B5" t="s" s="29">
+        <v>244</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" s="10">
         <v>40</v>
@@ -16050,7 +16032,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16070,13 +16052,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="E4" s="58"/>
     </row>
@@ -16085,10 +16067,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" s="10">
         <v>30</v>
@@ -16125,7 +16107,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16148,46 +16130,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16195,16 +16177,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16241,7 +16223,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16280,7 +16262,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16303,46 +16285,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16350,16 +16332,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16396,7 +16378,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16433,7 +16415,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16456,46 +16438,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16503,16 +16485,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16549,7 +16531,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16586,7 +16568,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16609,46 +16591,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16656,16 +16638,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16702,7 +16684,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -16741,7 +16723,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16764,46 +16746,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16811,16 +16793,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -16857,7 +16839,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="166" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -16896,7 +16878,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -16919,46 +16901,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -16966,16 +16948,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -17012,7 +16994,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -17339,7 +17321,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
@@ -17425,17 +17407,17 @@
         <v>15</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AH5" s="9">
         <f>AG5-AF5</f>
         <v>9745</v>
       </c>
       <c r="AI5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK5" s="29" t="s">
         <v>46</v>
@@ -17554,17 +17536,17 @@
         <v>5</v>
       </c>
       <c r="AG6" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH6" s="9">
         <f>AG6-AF6</f>
         <v>9880</v>
       </c>
       <c r="AI6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AK6" s="29" t="s">
         <v>46</v>
@@ -17639,7 +17621,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -17662,46 +17644,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -17709,16 +17691,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="114" t="s">
-        <v>140</v>
-      </c>
       <c r="D5" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -17749,13 +17731,13 @@
         <v>157.5</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O5" s="123">
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -17794,7 +17776,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -17817,46 +17799,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -17864,16 +17846,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="114" t="s">
-        <v>140</v>
-      </c>
       <c r="D5" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -17904,13 +17886,13 @@
         <v>157.5</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O5" s="123">
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -17944,7 +17926,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -17967,40 +17949,40 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
@@ -18011,16 +17993,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -18051,7 +18033,7 @@
         <v>135</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O5" s="123">
         <v>88363221</v>
@@ -18087,7 +18069,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -18110,46 +18092,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -18157,16 +18139,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -18203,7 +18185,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -18242,7 +18224,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -18265,46 +18247,46 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
@@ -18312,16 +18294,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -18358,7 +18340,7 @@
         <v>88363221</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -18394,7 +18376,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -18417,40 +18399,40 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="115" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
+      <c r="L4" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="L4" s="115" t="s">
+      <c r="M4" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="M4" s="115" t="s">
-        <v>154</v>
-      </c>
       <c r="N4" s="115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O4" s="115" t="s">
         <v>89</v>
@@ -18461,16 +18443,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
@@ -18565,7 +18547,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -18651,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -18661,7 +18643,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -18695,34 +18677,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>152</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -18740,7 +18722,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -18755,25 +18737,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -18919,7 +18901,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -19005,7 +18987,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19015,7 +18997,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19049,34 +19031,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>152</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19094,7 +19076,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19109,25 +19091,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -19273,7 +19255,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       <c r="A1" s="171" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -19359,7 +19341,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -19369,7 +19351,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -19403,34 +19385,34 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="126" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="126" t="s">
-        <v>127</v>
-      </c>
       <c r="H4" s="126" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="J4" s="115" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="K4" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="K4" s="115" t="s">
-        <v>152</v>
-      </c>
       <c r="L4" s="127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>25</v>
@@ -19448,7 +19430,7 @@
         <v>29</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>30</v>
@@ -19463,25 +19445,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5" s="67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>226</v>
+        <v>54</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I5" s="10">
         <f>ROUND(C5*H5/F5,3)</f>
@@ -19627,7 +19609,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
       